--- a/mapa_interactivo_Fiberwork.xlsx
+++ b/mapa_interactivo_Fiberwork.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R147"/>
+  <dimension ref="A1:R149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1711,27 +1711,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>S00431877</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4/23/2025</t>
+          <t>4/8/2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>COCHABAMBA 2207</t>
+          <t>SARMIENTO 4290</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1741,12 +1741,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>804903806</t>
+          <t>804569065</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>picada</t>
+          <t>Columna corroída en su base entro tambien como caso 7049</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1765,17 +1765,17 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>-58.396135</v>
+        <v>-58.425764</v>
       </c>
       <c r="N16" t="n">
-        <v>-34.624285</v>
+        <v>-34.604359</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>CON-C</t>
+          <t>ALM-L</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1797,17 +1797,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4/29/2025</t>
+          <t>4/23/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>República Bolivariana de Venezuela 2701</t>
+          <t>COCHABAMBA 2207</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>805507294</t>
+          <t>804903806</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>picada</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1842,26 +1842,26 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-58.404913</v>
+        <v>-58.396135</v>
       </c>
       <c r="N17" t="n">
-        <v>-34.615857</v>
+        <v>-34.624285</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>CON-C</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1883,17 +1883,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5/1/2025</t>
+          <t>4/29/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RIOBAMBA 659</t>
+          <t>República Bolivariana de Venezuela 2701</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>805579188</t>
+          <t>805507294</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pendiente de traspaso nodo entro tambien como 7100</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1933,17 +1933,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L18" t="n">
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>-58.394118</v>
+        <v>-58.404913</v>
       </c>
       <c r="N18" t="n">
-        <v>-34.601416</v>
+        <v>-34.615857</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>RET-H</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1969,17 +1969,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5/19/2025</t>
+          <t>5/1/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AYACUCHO 267</t>
+          <t>RIOBAMBA 659</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>806926385</t>
+          <t>805579188</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Colocar columna y dar aviso para traspaso de nodo teco</t>
+          <t>Pendiente de traspaso nodo entro tambien como 7100</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2026,10 +2026,10 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>-58.395063</v>
+        <v>-58.394118</v>
       </c>
       <c r="N19" t="n">
-        <v>-34.606257</v>
+        <v>-34.601416</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>RET-H</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2055,22 +2055,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5/26/2025</t>
+          <t>5/19/2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>COCHABAMBA 4090</t>
+          <t>AYACUCHO 267</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2085,12 +2085,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>806926861</t>
+          <t>806926385</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Columna base podrida colocar r400 para pedir traspaso de fuente</t>
+          <t>Colocar columna y dar aviso para traspaso de nodo teco</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2112,14 +2112,14 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>-58.422268</v>
+        <v>-58.395063</v>
       </c>
       <c r="N20" t="n">
-        <v>-34.627754</v>
+        <v>-34.606257</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>807187860</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6/4/2025</t>
+          <t>5/26/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Juan 3960</t>
+          <t>COCHABAMBA 4090</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>807187860</t>
+          <t>806926861</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Colocar columna contactar a Matias Tapia 1171744701 por si hay alguna duda o problema que surja en el momento ya que es para posterior tendido de ftth</t>
+          <t>Columna base podrida colocar r400 para pedir traspaso de fuente</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2198,10 +2198,10 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>-58.420909</v>
+        <v>-58.422268</v>
       </c>
       <c r="N21" t="n">
-        <v>-34.626221</v>
+        <v>-34.627754</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>PPT-R</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2227,17 +2227,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>807187860</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6/5/2025</t>
+          <t>6/4/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MAZA 181</t>
+          <t>San Juan 3960</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>807215439</t>
+          <t>807187860</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar columna contactar a Matias Tapia 1171744701 por si hay alguna duda o problema que surja en el momento ya que es para posterior tendido de ftth</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2284,14 +2284,14 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>-58.416477</v>
+        <v>-58.420909</v>
       </c>
       <c r="N22" t="n">
-        <v>-34.61303</v>
+        <v>-34.626221</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>PPT-R</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2313,7 +2313,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 771</t>
+          <t>MAZA 181</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>807215458</t>
+          <t>807215439</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Picada y mal ubicada ver con Pedro</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2370,10 +2370,10 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-58.425478</v>
+        <v>-58.416477</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.601865</v>
+        <v>-34.61303</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2399,22 +2399,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6/9/2025</t>
+          <t>6/5/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ALBERTI 191</t>
+          <t>ESTADO DE PALESTINA 771</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>810533286</t>
+          <t>807215458</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Desmontar PRFV 400</t>
+          <t>Picada y mal ubicada ver con Pedro</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2456,10 +2456,10 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.401624</v>
+        <v>-58.425478</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.612001</v>
+        <v>-34.601865</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2485,17 +2485,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6/24/2025</t>
+          <t>6/9/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MATHEU 727</t>
+          <t>ALBERTI 191</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2515,10 +2515,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ICD31456940</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>810533286</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Desmontar PRFV 400</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -2526,7 +2530,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Nodo TLC</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2538,10 +2542,10 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.400169</v>
+        <v>-58.401624</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.617784</v>
+        <v>-34.612001</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2555,7 +2559,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>CEN-N</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2567,17 +2571,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6/30/2025</t>
+          <t>6/24/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CHILE 2561</t>
+          <t>MATHEU 727</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2597,7 +2601,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>807851584</t>
+          <t>ICD31456940</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -2608,7 +2612,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Nodo TLC</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2620,10 +2624,10 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.401827</v>
+        <v>-58.400169</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.617667</v>
+        <v>-34.617784</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2637,7 +2641,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>CEN-N</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2649,17 +2653,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>-510</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7/14/2025</t>
+          <t>6/30/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Larrea 590</t>
+          <t>CHILE 2561</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2669,7 +2673,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2679,14 +2683,10 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>808194254</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Picada</t>
-        </is>
-      </c>
+          <t>807851584</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2706,10 +2706,10 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.402353</v>
+        <v>-58.401827</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.602205</v>
+        <v>-34.617667</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>CLI-E</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2735,7 +2735,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>-510</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CASTELLI 304</t>
+          <t>Larrea 590</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>808194260</t>
+          <t>808194254</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2792,10 +2792,10 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.404696</v>
+        <v>-58.402353</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.606337</v>
+        <v>-34.602205</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CLI-E</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2821,17 +2821,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7/15/2025</t>
+          <t>7/14/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TUCUMAN 3253</t>
+          <t>CASTELLI 304</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>808373657</t>
+          <t>808194260</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2878,10 +2878,10 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.411609</v>
+        <v>-58.404696</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.600329</v>
+        <v>-34.606337</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>CLI-F</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2907,17 +2907,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7/29/2025</t>
+          <t>7/15/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CALLAO AV. 316</t>
+          <t>TUCUMAN 3253</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>808579773</t>
+          <t>808373657</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2964,14 +2964,14 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.39231</v>
+        <v>-58.411609</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.605507</v>
+        <v>-34.600329</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>CEN-E</t>
+          <t>CLI-F</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2993,17 +2993,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8/4/2025</t>
+          <t>7/29/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MITRE, BARTOLOME 2482</t>
+          <t>CALLAO AV. 316</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>808703866</t>
+          <t>808579773</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3050,14 +3050,14 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.40161</v>
+        <v>-58.39231</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.608641</v>
+        <v>-34.605507</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CEN-E</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3079,27 +3079,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8/12/2025</t>
+          <t>8/4/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MARMOL, JOSE 228</t>
+          <t>MITRE, BARTOLOME 2482</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3109,12 +3109,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>808918687</t>
+          <t>808703866</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Se deriva directamente a traspaso de fuente ya que hay una columna existente</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3133,13 +3133,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.425858</v>
+        <v>-58.40161</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.61629</v>
+        <v>-34.608641</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3165,27 +3165,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8/26/2025</t>
+          <t>8/12/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SARANDI 1011</t>
+          <t>MARMOL, JOSE 228</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>809195660</t>
+          <t>808918687</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Picada entro tambien como caso 7209</t>
+          <t>Se deriva directamente a traspaso de fuente ya que hay una columna existente</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3219,17 +3219,17 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.394543</v>
+        <v>-58.425858</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.620732</v>
+        <v>-34.61629</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3251,7 +3251,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7050</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PRINGLES 788</t>
+          <t>SARANDI 1011</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>809195664</t>
+          <t>809195660</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada entro tambien como caso 7209</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3301,21 +3301,21 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L34" t="n">
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.427206</v>
+        <v>-58.394543</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.602914</v>
+        <v>-34.620732</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3337,17 +3337,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>-596</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>9/14/2025</t>
+          <t>8/26/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Humahuaca 3866</t>
+          <t>PRINGLES 788</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>809732190</t>
+          <t>809195664</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L35" t="n">
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.418823</v>
+        <v>-58.427206</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.602148</v>
+        <v>-34.602914</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3423,22 +3423,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>-597</t>
+          <t>-596</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/14/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>La Rioja 1261</t>
+          <t>Humahuaca 3866</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>809800215</t>
+          <t>809732190</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3480,14 +3480,14 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.407029</v>
+        <v>-58.418823</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.62526</v>
+        <v>-34.602148</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3509,17 +3509,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>-603</t>
+          <t>-597</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>9/22/2025</t>
+          <t>9/16/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ANCHORENA, TOMAS MANUEL DE, DR. 821</t>
+          <t>La Rioja 1261</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>809910086</t>
+          <t>809800215</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Columna chocada pendiente para instalar un corporativo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3566,14 +3566,14 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.408551</v>
+        <v>-58.407029</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.599265</v>
+        <v>-34.62526</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>CLI-F</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3595,22 +3595,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>-603</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>9/25/2025</t>
+          <t>9/22/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MARMOL, JOSE 588</t>
+          <t>ANCHORENA, TOMAS MANUEL DE, DR. 821</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>809979740</t>
+          <t>809910086</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna chocada pendiente para instalar un corporativo</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3652,10 +3652,10 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.425357</v>
+        <v>-58.408551</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.620223</v>
+        <v>-34.599265</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>ALM-B</t>
+          <t>CLI-F</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3681,22 +3681,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>-628</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10/1/2025</t>
+          <t>9/25/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hipolito Yrigoyen 3250</t>
+          <t>MARMOL, JOSE 588</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>810093628</t>
+          <t>809979740</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3738,10 +3738,10 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.412606</v>
+        <v>-58.425357</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.612353</v>
+        <v>-34.620223</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>ALM-B</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3767,17 +3767,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6404</t>
+          <t>-628</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10/6/2025</t>
+          <t>10/1/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LARREA 320</t>
+          <t>Hipolito Yrigoyen 3250</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>810244454</t>
+          <t>810093628</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3824,10 +3824,10 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.402105</v>
+        <v>-58.412606</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.606071</v>
+        <v>-34.612353</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3853,7 +3853,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7713</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>RINCON 781</t>
+          <t>LARREA 320</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>810244458</t>
+          <t>810244454</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3910,10 +3910,10 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.396055</v>
+        <v>-58.402105</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.618126</v>
+        <v>-34.606071</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3939,17 +3939,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>-633</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10/8/2025</t>
+          <t>10/6/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Junin 74</t>
+          <t>RINCON 781</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3969,12 +3969,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ICD31464881</t>
+          <t>810244458</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Colocar R400</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3993,13 +3993,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.39641</v>
+        <v>-58.396055</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.608561</v>
+        <v>-34.618126</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>CLI-C</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4025,22 +4025,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>-633</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>10/8/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 4256</t>
+          <t>Junin 74</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>810394752</t>
+          <t>ICD31464881</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R400</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4079,17 +4079,17 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.424867</v>
+        <v>-58.39641</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.626806</v>
+        <v>-34.608561</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>CLI-C</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4111,17 +4111,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10/20/2025</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CORRIENTES AV. 4515</t>
+          <t>SAN JUAN AV. 4256</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>810398934</t>
+          <t>810394752</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4168,14 +4168,14 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.428907</v>
+        <v>-58.424867</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.602301</v>
+        <v>-34.626806</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4197,17 +4197,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/20/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1923</t>
+          <t>CORRIENTES AV. 4515</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>810416656</t>
+          <t>810398934</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4254,14 +4254,14 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.411426</v>
+        <v>-58.428907</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.633266</v>
+        <v>-34.602301</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4283,17 +4283,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3762</t>
+          <t>SANCHEZ DE LORIA 1923</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4313,12 +4313,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>810451584</t>
+          <t>810416656</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>cambiar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4340,14 +4340,14 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.418542</v>
+        <v>-58.411426</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.624609</v>
+        <v>-34.633266</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4369,22 +4369,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ALSINA, ADOLFO 2499</t>
+          <t>CALVO, CARLOS 3762</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>810487023</t>
+          <t>810451584</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4426,14 +4426,14 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.40129</v>
+        <v>-58.418542</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.612123</v>
+        <v>-34.624609</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4455,7 +4455,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1142</t>
+          <t>ALSINA, ADOLFO 2499</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4485,12 +4485,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>810487035</t>
+          <t>810487023</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4512,14 +4512,14 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.413563</v>
+        <v>-58.40129</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.624645</v>
+        <v>-34.612123</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4541,17 +4541,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 3741</t>
+          <t>LINIERS VIRREY 1142</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>810712796</t>
+          <t>810487035</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4598,10 +4598,10 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.418108</v>
+        <v>-58.413563</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.62564</v>
+        <v>-34.624645</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4627,22 +4627,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Paso 280</t>
+          <t>SAN JUAN AV. 3741</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>810787612</t>
+          <t>810712796</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>base picada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4684,14 +4684,14 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.403566</v>
+        <v>-58.418108</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.606691</v>
+        <v>-34.62564</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4713,22 +4713,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11/14/2025</t>
+          <t>11/17/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV. 3485</t>
+          <t>Paso 280</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>810787513</t>
+          <t>810787612</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>base picada</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4770,10 +4770,10 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.415838</v>
+        <v>-58.403566</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.608469</v>
+        <v>-34.606691</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>CLI-J</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4799,17 +4799,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S00110420</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>11/14/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>YATAY 760</t>
+          <t>DIAZ VELEZ AV. 3485</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>810804303</t>
+          <t>810787513</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4856,10 +4856,10 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.428752</v>
+        <v>-58.415838</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.603273</v>
+        <v>-34.608469</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>ALM-M</t>
+          <t>CLI-J</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4885,17 +4885,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S00921590</t>
+          <t>S00110420</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CASEROS AV. 3621</t>
+          <t>YATAY 760</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4915,12 +4915,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>810804462</t>
+          <t>810804303</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4942,14 +4942,14 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.416134</v>
+        <v>-58.428752</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.638879</v>
+        <v>-34.603273</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>ALM-M</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4971,7 +4971,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S00921597</t>
+          <t>S00921590</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CASEROS AV. 3507</t>
+          <t>CASEROS AV. 3621</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>810804451</t>
+          <t>810804462</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5028,10 +5028,10 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.414769</v>
+        <v>-58.416134</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.638638</v>
+        <v>-34.638879</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S00921602</t>
+          <t>S00921597</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CASEROS AV. 3411</t>
+          <t>CASEROS AV. 3507</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>810804383</t>
+          <t>810804451</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Nodo TLC</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5114,10 +5114,10 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.413499</v>
+        <v>-58.414769</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.638416</v>
+        <v>-34.638638</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S00942399</t>
+          <t>S00921602</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ESTADOS UNIDOS 4030</t>
+          <t>CASEROS AV. 3411</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5173,12 +5173,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">01503983 </t>
+          <t>810804383</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>base corroida Colocar PRFV 400</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Nodo TLC</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5200,14 +5200,14 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.422536</v>
+        <v>-58.413499</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.623094</v>
+        <v>-34.638416</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5229,7 +5229,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>01110546</t>
+          <t>S00942399</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ALSINA, ADOLFO 2490</t>
+          <t>ESTADOS UNIDOS 4030</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>810804369</t>
+          <t xml:space="preserve">01503983 </t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>columna inclinada  base corroida</t>
+          <t>base corroida Colocar PRFV 400</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5286,14 +5286,14 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.401266</v>
+        <v>-58.422536</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.612194</v>
+        <v>-34.623094</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5315,17 +5315,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>01110546</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SAN LUIS 2488</t>
+          <t>ALSINA, ADOLFO 2490</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>810820592</t>
+          <t>810804369</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>base muy picada</t>
+          <t>columna inclinada  base corroida</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5372,10 +5372,10 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.402179</v>
+        <v>-58.401266</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.600152</v>
+        <v>-34.612194</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>CLI-E</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5401,17 +5401,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>-687</t>
+          <t>7874</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Junin 722</t>
+          <t>SAN LUIS 2488</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>810862729</t>
+          <t>810820592</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base muy picada</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5458,10 +5458,10 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.397171</v>
+        <v>-58.402179</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.600729</v>
+        <v>-34.600152</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -5475,34 +5475,34 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>RET-J</t>
+          <t>CLI-E</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>900008882010</t>
+          <t>-687</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PAVON AV. 3707 </t>
+          <t>Junin 722</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>810984598</t>
+          <t>810862729</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5544,14 +5544,14 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.416724</v>
+        <v>-58.397171</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.630181</v>
+        <v>-34.600729</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5561,29 +5561,29 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>PPT-R</t>
+          <t>RET-J</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>900008882010</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Querandíes 4220</t>
+          <t xml:space="preserve"> PAVON AV. 3707 </t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5603,12 +5603,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>810984700</t>
+          <t>810984598</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>correr, obstaculiza acceso a garage</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5623,21 +5623,21 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L61" t="n">
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.426168</v>
+        <v>-58.416724</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.611095</v>
+        <v>-34.630181</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>ALM-E</t>
+          <t>PPT-R</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5659,22 +5659,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">URQUIZA, GRAL. 779 </t>
+          <t>Querandíes 4220</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>811198737</t>
+          <t>810984700</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>correr, obstaculiza acceso a garage</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5709,17 +5709,17 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L62" t="n">
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.409318</v>
+        <v>-58.426168</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.619842</v>
+        <v>-34.611095</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>ALM-E</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5745,7 +5745,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUMAHUACA 4298 </t>
+          <t xml:space="preserve">URQUIZA, GRAL. 779 </t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>811198696</t>
+          <t>811198737</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5802,10 +5802,10 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.425302</v>
+        <v>-58.409318</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.601502</v>
+        <v>-34.619842</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5831,17 +5831,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S01199412</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ACUÑA DE FIGUEROA, FRANCISCO 1028</t>
+          <t xml:space="preserve">HUMAHUACA 4298 </t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>811198676</t>
+          <t>811198696</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5888,10 +5888,10 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.422033</v>
+        <v>-58.425302</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.598976</v>
+        <v>-34.601502</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>CLI-L</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5917,22 +5917,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>-705</t>
+          <t>S01199412</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12/22/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Larrea 370</t>
+          <t>ACUÑA DE FIGUEROA, FRANCISCO 1028</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>02013924</t>
+          <t>811198676</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -5974,10 +5974,10 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.402154</v>
+        <v>-58.422033</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.605295</v>
+        <v>-34.598976</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CLI-L</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6003,22 +6003,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>-705</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>12/22/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BRAVO, MARIO 478</t>
+          <t>Larrea 370</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>811299416</t>
+          <t>02013924</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6060,10 +6060,10 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.416901</v>
+        <v>-58.402154</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.604236</v>
+        <v>-34.605295</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6089,17 +6089,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>-711</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>México 3306</t>
+          <t>BRAVO, MARIO 478</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>811299443</t>
+          <t>811299416</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6146,10 +6146,10 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.412865</v>
+        <v>-58.416901</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.619484</v>
+        <v>-34.604236</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6175,17 +6175,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>-711</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LAMBARE 864</t>
+          <t>México 3306</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>811453866</t>
+          <t>811299443</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6232,10 +6232,10 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.430579</v>
+        <v>-58.412865</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.604908</v>
+        <v>-34.619484</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>ALM-M</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6261,17 +6261,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S00941232</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TARIJA 3323</t>
+          <t>LAMBARE 864</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6291,12 +6291,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>811453904</t>
+          <t>811453866</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6318,14 +6318,14 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.412204</v>
+        <v>-58.430579</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.628609</v>
+        <v>-34.604908</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>ALM-M</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6347,22 +6347,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>S00941232</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Catamarca 236</t>
+          <t>TARIJA 3323</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6377,12 +6377,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">02511385 </t>
+          <t>811453904</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6404,14 +6404,14 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.406807</v>
+        <v>-58.412204</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.612902</v>
+        <v>-34.628609</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6433,7 +6433,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DIAZ VELEZ AV. 4421</t>
+          <t>Catamarca 236</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>811454440</t>
+          <t xml:space="preserve">02511385 </t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6490,10 +6490,10 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.429481</v>
+        <v>-58.406807</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.608647</v>
+        <v>-34.612902</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>ALM-K</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6519,22 +6519,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S01432754</t>
+          <t>8124</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1/16/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MISIONES 242</t>
+          <t xml:space="preserve"> DIAZ VELEZ AV. 4421</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>811454538</t>
+          <t>811454440</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6576,10 +6576,10 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.404243</v>
+        <v>-58.429481</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.612859</v>
+        <v>-34.608647</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>ALM-K</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6605,7 +6605,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>S01432754</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Castelli 60</t>
+          <t>MISIONES 242</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6635,25 +6635,37 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>811454538</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>traspaso propio tlc coloco columna</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+          <t>corroida</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
       <c r="L73" t="n">
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.404691</v>
+        <v>-58.404243</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.609194</v>
+        <v>-34.612859</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -6667,7 +6679,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6679,17 +6691,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S01408162</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/16/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARAY, JUAN DE AV. 2871 </t>
+          <t>Castelli 60</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6699,7 +6711,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6709,41 +6721,29 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>812439895</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+          <t>traspaso propio tlc coloco columna</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="n">
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.4048</v>
+        <v>-58.404691</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.629021</v>
+        <v>-34.609194</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6765,17 +6765,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S00034481</t>
+          <t>S01408162</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">MITRE, BARTOLOME 2294 </t>
+          <t xml:space="preserve">GARAY, JUAN DE AV. 2871 </t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>811626888</t>
+          <t>812439895</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6822,14 +6822,14 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.399059</v>
+        <v>-58.4048</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.608499</v>
+        <v>-34.629021</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>CLI-C</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6851,17 +6851,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S01314715</t>
+          <t>S00034481</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CATAMARCA 919</t>
+          <t xml:space="preserve">MITRE, BARTOLOME 2294 </t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6881,12 +6881,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>811626986</t>
+          <t>811626888</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6908,14 +6908,14 @@
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.404766</v>
+        <v>-58.399059</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.620521</v>
+        <v>-34.608499</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>CEN-K</t>
+          <t>CLI-C</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6937,7 +6937,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>8125</t>
+          <t>S01314715</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
+          <t xml:space="preserve"> CATAMARCA 919</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>811626981</t>
+          <t>811626986</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Corroida</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6994,14 +6994,14 @@
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.423058</v>
+        <v>-58.404766</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.608916</v>
+        <v>-34.620521</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>ALM-E</t>
+          <t>CEN-K</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7023,22 +7023,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>COMBATE DE LOS POZOS 1103</t>
+          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>811627014</t>
+          <t>811626981</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7080,14 +7080,14 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.393145</v>
+        <v>-58.423058</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.621778</v>
+        <v>-34.608916</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>ALM-E</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7109,17 +7109,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S00022862</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO 2395</t>
+          <t>COMBATE DE LOS POZOS 1103</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>811627077</t>
+          <t>811627014</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7166,14 +7166,14 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.400243</v>
+        <v>-58.393145</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.610864</v>
+        <v>-34.621778</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7195,7 +7195,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>S00022862</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PICHINCHA 89</t>
+          <t>YRIGOYEN, HIPOLITO 2395</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7225,12 +7225,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>811627062</t>
+          <t>811627077</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7252,10 +7252,10 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.399124</v>
+        <v>-58.400243</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.610705</v>
+        <v>-34.610864</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -7281,22 +7281,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>8296</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2/6/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GALLO 77</t>
+          <t>PICHINCHA 89</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>811627128</t>
+          <t>811627062</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>tensor roto inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7331,17 +7331,17 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L81" t="n">
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.413979</v>
+        <v>-58.399124</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.607475</v>
+        <v>-34.610705</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7367,22 +7367,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>8329</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/6/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>RINCON 1109</t>
+          <t>GALLO 77</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>812439968</t>
+          <t>811627128</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>tensor roto inclinada</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7417,21 +7417,21 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L82" t="n">
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.395668</v>
+        <v>-58.413979</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.621926</v>
+        <v>-34.607475</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>CEN-N</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7453,17 +7453,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALBERTI 1055 </t>
+          <t>RINCON 1109</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7483,12 +7483,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>812440156</t>
+          <t>812439968</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7510,10 +7510,10 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.400774</v>
+        <v>-58.395668</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.621503</v>
+        <v>-34.621926</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -7539,17 +7539,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S00136365</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PERON, JUAN DOMINGO, TTE. GENERAL 2697</t>
+          <t xml:space="preserve">ALBERTI 1055 </t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7569,7 +7569,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>812440173</t>
+          <t>812440156</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7596,14 +7596,14 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.404576</v>
+        <v>-58.400774</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.607569</v>
+        <v>-34.621503</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CEN-N</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -7625,7 +7625,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S00144805</t>
+          <t>S00136365</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>VIAMONTE 1990</t>
+          <t>PERON, JUAN DOMINGO, TTE. GENERAL 2697</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>812440165</t>
+          <t>812440173</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7682,10 +7682,10 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.395384</v>
+        <v>-58.404576</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.600962</v>
+        <v>-34.607569</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -7699,29 +7699,29 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>RET-J</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>-749</t>
+          <t>S00144805</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Moreno 2965</t>
+          <t>VIAMONTE 1990</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>812440614</t>
+          <t>812440165</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7768,10 +7768,10 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.407758</v>
+        <v>-58.395384</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.613793</v>
+        <v>-34.600962</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -7785,19 +7785,19 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>RET-J</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>-760</t>
+          <t>-749</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MAZA 1615</t>
+          <t>Moreno 2965</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7827,12 +7827,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>812440354</t>
+          <t>812440614</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>base corroida e inclinada</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7854,14 +7854,14 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.414586</v>
+        <v>-58.407758</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.630095</v>
+        <v>-34.613793</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7883,7 +7883,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S00519068</t>
+          <t>-760</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3747</t>
+          <t>MAZA 1615</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>812440282</t>
+          <t>812440354</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base corroida e inclinada</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7940,10 +7940,10 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.41859</v>
+        <v>-58.414586</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.624508</v>
+        <v>-34.630095</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7969,17 +7969,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>S00519068</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2/27/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRAVO, MARIO 836 </t>
+          <t>CALVO, CARLOS 3747</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>812503638</t>
+          <t>812440282</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8026,14 +8026,14 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.416187</v>
+        <v>-58.41859</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.600138</v>
+        <v>-34.624508</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>CLI-G</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8055,17 +8055,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S00100362</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>3/4/2026</t>
+          <t>2/27/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO 901</t>
+          <t xml:space="preserve">BRAVO, MARIO 836 </t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812503638</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8112,10 +8112,10 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.431406</v>
+        <v>-58.416187</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.605009</v>
+        <v>-34.600138</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>ALM-M</t>
+          <t>CLI-G</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8141,17 +8141,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>-774</t>
+          <t>S00100362</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/4/2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CASEROS AV. 4131</t>
+          <t>RIO DE JANEIRO 901</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>mover a 4111</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8198,14 +8198,14 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.422741</v>
+        <v>-58.431406</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.639999</v>
+        <v>-34.605009</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>ALM-M</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8227,17 +8227,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>00050599</t>
+          <t>-774</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">BELGRANO AV 3689 </t>
+          <t>CASEROS AV. 4131</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>812879940</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>mover a 4111</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8284,14 +8284,14 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.418254</v>
+        <v>-58.422741</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.615692</v>
+        <v>-34.639999</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8313,7 +8313,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>00223191</t>
+          <t>00050599</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CATAMARCA 254</t>
+          <t xml:space="preserve">BELGRANO AV 3689 </t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>812879982</t>
+          <t>812879940</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -8370,10 +8370,10 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.406734</v>
+        <v>-58.418254</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.613107</v>
+        <v>-34.615692</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8399,7 +8399,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>00223191</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8409,12 +8409,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CORRIENTES AV 4073</t>
+          <t>CATAMARCA 254</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>812880406</t>
+          <t>812879982</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -8456,10 +8456,10 @@
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.422076</v>
+        <v>-58.406734</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.60298</v>
+        <v>-34.613107</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8485,7 +8485,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>00223023</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 2201</t>
+          <t>CORRIENTES AV 4073</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8515,14 +8515,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
+          <t>812880406</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
           <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
       <c r="I95" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -8542,14 +8542,14 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.396491</v>
+        <v>-58.422076</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.622986</v>
+        <v>-34.60298</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8571,22 +8571,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>00317296</t>
+          <t>00223023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3/23/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AGRELO 3620</t>
+          <t>SAN JUAN AV. 2201</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>812880625</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -8628,14 +8628,14 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.417002</v>
+        <v>-58.396491</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.618613</v>
+        <v>-34.622986</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>ALM-B</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8657,7 +8657,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>00322642</t>
+          <t>00317296</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 727</t>
+          <t>AGRELO 3620</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>812880655</t>
+          <t>812880625</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -8714,10 +8714,10 @@
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.425539</v>
+        <v>-58.417002</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.602286</v>
+        <v>-34.618613</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>ALM-B</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8743,7 +8743,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>00322642</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MEXICO 3306</t>
+          <t>ESTADO DE PALESTINA 727</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>812880662</t>
+          <t>812880655</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -8800,10 +8800,10 @@
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.412865</v>
+        <v>-58.425539</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.619484</v>
+        <v>-34.602286</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8829,7 +8829,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>HUMBERTO 1 1999</t>
+          <t>MEXICO 3306</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>812880685</t>
+          <t>812880662</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -8886,14 +8886,14 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.394304</v>
+        <v>-58.412865</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.621645</v>
+        <v>-34.619484</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8915,17 +8915,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>8265</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>3/28/2026</t>
+          <t>3/23/2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>RIVADAVIA AV 1985</t>
+          <t>HUMBERTO 1 1999</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8945,17 +8945,17 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>812880736</t>
+          <t>812880685</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>APLOMAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -8972,14 +8972,14 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.394609</v>
+        <v>-58.394304</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.609304</v>
+        <v>-34.621645</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9001,22 +9001,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>M881</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>4/1/2026</t>
+          <t>3/28/2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AV LA PLATA 2288</t>
+          <t>RIVADAVIA AV 1985</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9031,22 +9031,22 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>813046342</t>
+          <t>812880736</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>DESMONTAR COLUMNA Y  DESPLAZAR PCALOGERO</t>
+          <t>APLOMAR COLUMNA</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -9058,14 +9058,14 @@
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.423203</v>
+        <v>-58.394609</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.640909</v>
+        <v>-34.609304</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9087,22 +9087,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>8802</t>
+          <t>M881</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/1/2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>RINCON 731</t>
+          <t>AV LA PLATA 2288</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>813046658</t>
+          <t>813046342</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>DESMONTAR COLUMNA Y  DESPLAZAR PCALOGERO</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9144,14 +9144,14 @@
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.396088</v>
+        <v>-58.423203</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.617527</v>
+        <v>-34.640909</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9173,7 +9173,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S00374917</t>
+          <t>8802</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>24 DE NOVIEMBRE 695</t>
+          <t>RINCON 731</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>813046791</t>
+          <t>813046658</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9230,10 +9230,10 @@
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.411053</v>
+        <v>-58.396088</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.618979</v>
+        <v>-34.617527</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9259,7 +9259,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S00379764</t>
+          <t>S00374917</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>JAURES JEAN 491</t>
+          <t>24 DE NOVIEMBRE 695</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>813046795</t>
+          <t>813046791</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -9316,10 +9316,10 @@
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.408934</v>
+        <v>-58.411053</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.604273</v>
+        <v>-34.618979</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>CLI-H</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9345,7 +9345,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S00379996</t>
+          <t>S00379764</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SARANDI 1439</t>
+          <t>JAURES JEAN 491</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>813046806</t>
+          <t>813046795</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -9402,14 +9402,14 @@
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.393455</v>
+        <v>-58.408934</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.625779</v>
+        <v>-34.604273</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -9419,7 +9419,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>CON-C</t>
+          <t>CLI-H</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9431,7 +9431,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>S00379996</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SARMIENTO 2108</t>
+          <t>SARANDI 1439</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>813046819</t>
+          <t>813046806</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -9488,14 +9488,14 @@
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.39675</v>
+        <v>-58.393455</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.605996</v>
+        <v>-34.625779</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>CON-C</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9517,7 +9517,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9527,12 +9527,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SANCHEZ DE BUSTAMANTE 633</t>
+          <t>SARMIENTO 2108</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>813046866</t>
+          <t>813046819</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -9574,10 +9574,10 @@
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.414203</v>
+        <v>-58.39675</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.602602</v>
+        <v>-34.605996</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>CLI-G</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9603,7 +9603,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>RIVADAVIA AV 4245</t>
+          <t>SANCHEZ DE BUSTAMANTE 633</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>813046970</t>
+          <t>813046866</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -9660,10 +9660,10 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.425567</v>
+        <v>-58.414203</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.613382</v>
+        <v>-34.602602</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>CLI-G</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9689,7 +9689,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV 4449</t>
+          <t>RIVADAVIA AV 4245</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>813046971</t>
+          <t>813046970</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -9746,10 +9746,10 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.429714</v>
+        <v>-58.425567</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.608645</v>
+        <v>-34.613382</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>ALM-K</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9775,7 +9775,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>8851</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>LAS CASAS 3989</t>
+          <t>DIAZ VELEZ AV 4449</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>813046994</t>
+          <t>813046971</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -9832,14 +9832,14 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.421676</v>
+        <v>-58.429714</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.635878</v>
+        <v>-34.608645</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>PPT-R</t>
+          <t>ALM-K</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9861,7 +9861,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>8852</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SALCEDO 3541</t>
+          <t>LAS CASAS 3989</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>813047007</t>
+          <t>813046994</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -9918,10 +9918,10 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.415121</v>
+        <v>-58.421676</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.633772</v>
+        <v>-34.635878</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>PPT-R</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9947,7 +9947,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>8853</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TARIJA 4079</t>
+          <t>SALCEDO 3541</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>813047012</t>
+          <t>813047007</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -10004,10 +10004,10 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.421804</v>
+        <v>-58.415121</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.629558</v>
+        <v>-34.633772</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>PPT-R</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10033,7 +10033,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TIMBUES 2086</t>
+          <t>TARIJA 4079</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>813047017</t>
+          <t>813047012</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -10090,10 +10090,10 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.421835</v>
+        <v>-58.421804</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.63863</v>
+        <v>-34.629558</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>PPT-R</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10119,7 +10119,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>GOMEZ VALENTIN 3684</t>
+          <t>TIMBUES 2086</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>813047019</t>
+          <t>813047017</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -10176,14 +10176,14 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.416726</v>
+        <v>-58.421835</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.604773</v>
+        <v>-34.63863</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10205,7 +10205,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S00390896</t>
+          <t>8855</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10215,12 +10215,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>AV INDEPENDENCIA 2018</t>
+          <t>GOMEZ VALENTIN 3684</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>813047657</t>
+          <t>813047019</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -10262,10 +10262,10 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.39469</v>
+        <v>-58.416726</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.618394</v>
+        <v>-34.604773</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10291,22 +10291,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>RB00001</t>
+          <t>S00390896</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/11/2026</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BELGRANO AV. 3715</t>
+          <t>AV INDEPENDENCIA 2018</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>813304903</t>
+          <t>813047657</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -10348,10 +10348,10 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.418851</v>
+        <v>-58.39469</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.615716</v>
+        <v>-34.618394</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10377,7 +10377,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AM00039</t>
+          <t>RB00001</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CASTRO BARROS 852</t>
+          <t>BELGRANO AV. 3715</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>813304915</t>
+          <t>813304903</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -10434,14 +10434,14 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.419281</v>
+        <v>-58.418851</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.62215</v>
+        <v>-34.615716</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10463,7 +10463,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>AM00039</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ALSINA, ADOLFO 3293</t>
+          <t>CASTRO BARROS 852</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>813350607</t>
+          <t>813304915</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -10520,14 +10520,14 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.412936</v>
+        <v>-58.419281</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.613332</v>
+        <v>-34.62215</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10549,7 +10549,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S00423738</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CATAMARCA 568</t>
+          <t>ALSINA, ADOLFO 3293</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -10579,7 +10579,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>813350620</t>
+          <t>813350607</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -10606,10 +10606,10 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.405541</v>
+        <v>-58.412936</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.616959</v>
+        <v>-34.613332</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10635,22 +10635,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S00299569</t>
+          <t>S00423738</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>4/21/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO AV. 4156</t>
+          <t>CATAMARCA 568</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>813350953</t>
+          <t>813350620</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -10692,10 +10692,10 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.425213</v>
+        <v>-58.405541</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.614924</v>
+        <v>-34.616959</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10721,7 +10721,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S004318770</t>
+          <t>S00299569</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SARMIENTO 4290</t>
+          <t>YRIGOYEN, HIPOLITO AV. 4156</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>813351576</t>
+          <t>813350953</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -10778,10 +10778,10 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.425764</v>
+        <v>-58.425213</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.604359</v>
+        <v>-34.614924</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>ALM-L</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10807,7 +10807,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S00431893</t>
+          <t>S004318770</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MUÑIZ 1151</t>
+          <t>SARMIENTO 4290</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>GENERADOR DE OT NO ENCUENTRA DIRECCION</t>
+          <t>813351576</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -10864,14 +10864,14 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.425442</v>
+        <v>-58.425764</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.627634</v>
+        <v>-34.604359</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>ALM-L</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10893,7 +10893,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9009 </t>
+          <t>S00431893</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1913</t>
+          <t>MUÑIZ 1151</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>813352473</t>
+          <t>GENERADOR DE OT NO ENCUENTRA DIRECCION</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -10950,14 +10950,14 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.411474</v>
+        <v>-58.425442</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.633143</v>
+        <v>-34.627634</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10979,7 +10979,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9011 </t>
+          <t>S00434849</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1583</t>
+          <t>YRIGOYEN, HIPOLITO AV. 3484</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>813352481</t>
+          <t>813352212</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -11036,14 +11036,14 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.411926</v>
+        <v>-58.416028</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.628861</v>
+        <v>-34.613538</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11065,7 +11065,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9012 </t>
+          <t xml:space="preserve">9009 </t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINIERS VIRREY 2315 </t>
+          <t>SANCHEZ DE LORIA 1913</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>813352482</t>
+          <t>813352473</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -11122,10 +11122,10 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.41191</v>
+        <v>-58.411474</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.637333</v>
+        <v>-34.633143</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9014 </t>
+          <t xml:space="preserve">9011 </t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 896</t>
+          <t>SANCHEZ DE LORIA 1583</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>813352486</t>
+          <t>813352481</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -11208,10 +11208,10 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.413645</v>
+        <v>-58.411926</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.621935</v>
+        <v>-34.628861</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11237,7 +11237,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9016 </t>
+          <t xml:space="preserve">9012 </t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>HUMBERTO 1° 3368</t>
+          <t xml:space="preserve">LINIERS VIRREY 2315 </t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11267,7 +11267,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>813352494</t>
+          <t>813352482</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -11294,14 +11294,14 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.413189</v>
+        <v>-58.41191</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.624187</v>
+        <v>-34.637333</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11323,7 +11323,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9017 </t>
+          <t xml:space="preserve">9014 </t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MUÑIZ 1237</t>
+          <t>LINIERS VIRREY 896</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>GENERADOR DE OT NO ENCUENTRA DIRECCION</t>
+          <t>813352486</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -11380,10 +11380,10 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.425206</v>
+        <v>-58.413645</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.628705</v>
+        <v>-34.621935</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11409,7 +11409,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9020 </t>
+          <t xml:space="preserve">9016 </t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>TARIJA 3497</t>
+          <t>HUMBERTO 1° 3368</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11439,7 +11439,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>813352497</t>
+          <t>813352494</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -11466,10 +11466,10 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.414424</v>
+        <v>-58.413189</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.628778</v>
+        <v>-34.624187</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11495,17 +11495,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t xml:space="preserve">9017 </t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/21/2026</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>BRAVO, MARIO 740</t>
+          <t>MUÑIZ 1237</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11525,7 +11525,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>813352774</t>
+          <t>GENERADOR DE OT NO ENCUENTRA DIRECCION</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -11552,14 +11552,14 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.416308</v>
+        <v>-58.425206</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.601047</v>
+        <v>-34.628705</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>CLI-G</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11581,22 +11581,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S00413025</t>
+          <t xml:space="preserve">9020 </t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/21/2026</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CHILE 2550</t>
+          <t>TARIJA 3497</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11611,7 +11611,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>813352855</t>
+          <t>813352497</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -11638,14 +11638,14 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.40174</v>
+        <v>-58.414424</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.617754</v>
+        <v>-34.628778</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11667,7 +11667,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S00429731</t>
+          <t>9028</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11677,12 +11677,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALSINA, ADOLFO 2291 </t>
+          <t>BRAVO, MARIO 740</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>813352873</t>
+          <t>813352774</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -11724,10 +11724,10 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.398771</v>
+        <v>-58.416308</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.611932</v>
+        <v>-34.601047</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>CLI-G</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11753,22 +11753,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t>S00413025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>4/29/2026</t>
+          <t>4/24/2026</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALLEGOS 3443 </t>
+          <t>CHILE 2550</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>813353299</t>
+          <t>813352855</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -11810,14 +11810,14 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.413647</v>
+        <v>-58.40174</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.631434</v>
+        <v>-34.617754</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11839,22 +11839,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">9045 </t>
+          <t>S00429731</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>4/24/2026</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1793</t>
+          <t xml:space="preserve">ALSINA, ADOLFO 2291 </t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>813631423</t>
+          <t>813352873</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -11896,14 +11896,14 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.413025</v>
+        <v>-58.398771</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.631929</v>
+        <v>-34.611932</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11925,17 +11925,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>4/29/2026</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BATHURST 3377</t>
+          <t xml:space="preserve">GALLEGOS 3443 </t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>813631424</t>
+          <t>813353299</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -11982,14 +11982,14 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.411896</v>
+        <v>-58.413647</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.636028</v>
+        <v>-34.631434</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -12011,22 +12011,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S00215089</t>
+          <t xml:space="preserve">9045 </t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>LARREA 122</t>
+          <t>LINIERS VIRREY 1793</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>813631550</t>
+          <t>813631423</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -12068,14 +12068,14 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.401972</v>
+        <v>-58.413025</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.608317</v>
+        <v>-34.631929</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -12085,7 +12085,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12097,22 +12097,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S00401648</t>
+          <t>9049</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>JUNIN 312</t>
+          <t>BATHURST 3377</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>813632251</t>
+          <t>813631424</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -12154,14 +12154,14 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.396676</v>
+        <v>-58.411896</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.605753</v>
+        <v>-34.636028</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12183,7 +12183,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S00465940</t>
+          <t>S00215089</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BELGRANO AV. 3669</t>
+          <t>LARREA 122</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>813632257</t>
+          <t>813631550</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -12240,10 +12240,10 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.417949</v>
+        <v>-58.401972</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.615674</v>
+        <v>-34.608317</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12269,7 +12269,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>S00401648</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>JAURES, JEAN 309</t>
+          <t>JUNIN 312</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>813632439</t>
+          <t>813632251</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -12314,7 +12314,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -12326,10 +12326,10 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.409868</v>
+        <v>-58.396676</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.606562</v>
+        <v>-34.605753</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>CLI-H</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12355,17 +12355,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S00364775</t>
+          <t>S00465940</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>CASTRO 511</t>
+          <t>BELGRANO AV. 3669</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -12383,15 +12383,19 @@
           <t>FIBERWORK</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>813632257</t>
+        </is>
+      </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>NORMALIZAR RIENDA A PIQUE</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Tensor</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -12401,17 +12405,17 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.420597</v>
+        <v>-58.417949</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.617818</v>
+        <v>-34.615674</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -12425,7 +12429,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>ALM-B</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12437,17 +12441,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S00493114</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ARENALES 3648</t>
+          <t>JAURES, JEAN 309</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -12465,7 +12469,11 @@
           <t>FIBERWORK</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>813632439</t>
+        </is>
+      </c>
       <c r="H141" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -12490,14 +12498,14 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.413656</v>
+        <v>-58.409868</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.585464</v>
+        <v>-34.606562</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -12507,7 +12515,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>CLI-H</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12519,7 +12527,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">7880 </t>
+          <t>S00364775</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12529,7 +12537,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>MUÑIZ 16</t>
+          <t>CASTRO 511</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -12550,12 +12558,12 @@
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>NORMALIZAR RIENDA A PIQUE</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Tensor</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -12565,17 +12573,17 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L142" t="n">
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.427498</v>
+        <v>-58.420597</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.614599</v>
+        <v>-34.617818</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -12589,7 +12597,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>ALM-B</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12601,7 +12609,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">9923 </t>
+          <t>S00493114</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12611,12 +12619,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>PRINGLES 1094</t>
+          <t>ARENALES 3648</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12654,14 +12662,14 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.426722</v>
+        <v>-58.413656</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.599427</v>
+        <v>-34.585464</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -12671,7 +12679,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12683,17 +12691,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9019 </t>
+          <t xml:space="preserve">7880 </t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CASTRO BARROS AV. 338</t>
+          <t>MUÑIZ 16</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -12736,10 +12744,10 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.419864</v>
+        <v>-58.427498</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.616375</v>
+        <v>-34.614599</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -12753,7 +12761,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12765,22 +12773,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9031 </t>
+          <t xml:space="preserve">9923 </t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO 1938</t>
+          <t>PRINGLES 1094</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12806,7 +12814,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -12818,10 +12826,10 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.394079</v>
+        <v>-58.426722</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.61051</v>
+        <v>-34.599427</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -12835,7 +12843,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12847,7 +12855,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">9088 </t>
+          <t xml:space="preserve">9019 </t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12857,7 +12865,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>HUMAHUACA 4296</t>
+          <t>CASTRO BARROS AV. 338</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12900,10 +12908,10 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.425282</v>
+        <v>-58.419864</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.601504</v>
+        <v>-34.616375</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -12917,7 +12925,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12929,7 +12937,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">10059 </t>
+          <t xml:space="preserve">9031 </t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12939,7 +12947,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALGUERO, JERONIMO 2296 </t>
+          <t>YRIGOYEN, HIPOLITO 1938</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12960,49 +12968,213 @@
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Nodo/Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>1</v>
+      </c>
+      <c r="M147" t="n">
+        <v>-58.394079</v>
+      </c>
+      <c r="N147" t="n">
+        <v>-34.61051</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>CEN-G</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9088 </t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>5/14/2026</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>HUMAHUACA 4296</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>FIBERWORK</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" t="n">
+        <v>-58.425282</v>
+      </c>
+      <c r="N148" t="n">
+        <v>-34.601504</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>CLI-M</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10059 </t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>5/14/2026</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SALGUERO, JERONIMO 2296 </t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>FIBERWORK</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
           <t>COLUMNA INCLINADA</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
+      <c r="I149" t="inlineStr">
         <is>
           <t>Aplomo</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr">
+      <c r="J149" t="inlineStr">
         <is>
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L147" t="n">
-        <v>1</v>
-      </c>
-      <c r="M147" t="n">
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="n">
         <v>-58.411132</v>
       </c>
-      <c r="N147" t="n">
+      <c r="N149" t="n">
         <v>-34.585267</v>
       </c>
-      <c r="O147" t="inlineStr">
+      <c r="O149" t="inlineStr">
         <is>
           <t>Palermo</t>
         </is>
       </c>
-      <c r="P147" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q147" t="inlineStr">
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
         <is>
           <t>AGU-K</t>
         </is>
       </c>
-      <c r="R147" t="inlineStr">
+      <c r="R149" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_Fiberwork.xlsx
+++ b/mapa_interactivo_Fiberwork.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R149"/>
+  <dimension ref="A1:R148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -851,17 +851,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>-109</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7/8/2024</t>
+          <t>1/9/2025</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>YRIGOYEN HIPOLITO /ALT/ 1938</t>
+          <t>PASCO 10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>790175801</t>
+          <t>802438793</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>RELEVO INDICA QUE NO HAY COLUMNA</t>
+          <t>PIcada</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -896,22 +896,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>-58.394079</v>
+        <v>-58.397512</v>
       </c>
       <c r="N6" t="n">
-        <v>-34.61051</v>
+        <v>-34.609923</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -937,22 +937,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1/9/2025</t>
+          <t>1/16/2025</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PASCO 10</t>
+          <t>BARCO CENTENERA DEL 545</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -967,12 +967,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>802438793</t>
+          <t>802774521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>PIcada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -982,26 +982,26 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>-58.397512</v>
+        <v>-58.440625</v>
       </c>
       <c r="N7" t="n">
-        <v>-34.609923</v>
+        <v>-34.625499</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>PCH-C</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1023,27 +1023,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>-275</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1/16/2025</t>
+          <t>2/3/2025</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BARCO CENTENERA DEL 545</t>
+          <t>DEAN FUNES /ALT/ 481</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1053,12 +1053,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>802774521</t>
+          <t>803039902</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t xml:space="preserve">Propia diámetro 114mm </t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1080,14 +1080,14 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>-58.440625</v>
+        <v>-58.407076</v>
       </c>
       <c r="N8" t="n">
-        <v>-34.625499</v>
+        <v>-34.616016</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>PCH-C</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1109,17 +1109,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>-275</t>
+          <t>803666441</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2/3/2025</t>
+          <t>2/28/2025</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DEAN FUNES /ALT/ 481</t>
+          <t>Pichincha 1160</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>803039902</t>
+          <t>803666441</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Propia diámetro 114mm </t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1163,17 +1163,17 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-58.407076</v>
+        <v>-58.397946</v>
       </c>
       <c r="N9" t="n">
-        <v>-34.616016</v>
+        <v>-34.622625</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>CEN-N</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1195,22 +1195,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>803666441</t>
+          <t>8849</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2/28/2025</t>
+          <t>3/18/2025</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pichincha 1160</t>
+          <t>Av. Hipólito Yrigoyen 3451</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>803666441</t>
+          <t>804161204</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1249,17 +1249,17 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>-58.397946</v>
+        <v>-58.415566</v>
       </c>
       <c r="N10" t="n">
-        <v>-34.622625</v>
+        <v>-34.613244</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>CEN-N</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8849</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Av. Hipólito Yrigoyen 3451</t>
+          <t>TREINTA Y TRES ORIENTALES 965</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>804161204</t>
+          <t>804161231</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1338,14 +1338,14 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>-58.415566</v>
+        <v>-58.423042</v>
       </c>
       <c r="N11" t="n">
-        <v>-34.613244</v>
+        <v>-34.625868</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1367,17 +1367,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>804270064</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3/18/2025</t>
+          <t>3/21/2025</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TREINTA Y TRES ORIENTALES 965</t>
+          <t>Colombres 636</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>804161231</t>
+          <t>804270064</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1421,17 +1421,17 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-58.423042</v>
+        <v>-58.418089</v>
       </c>
       <c r="N12" t="n">
-        <v>-34.625868</v>
+        <v>-34.620313</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>ALM-B</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1453,7 +1453,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>804270064</t>
+          <t>804270068</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Colombres 636</t>
+          <t>Quito 4292</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>804270064</t>
+          <t>804270068</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1510,10 +1510,10 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-58.418089</v>
+        <v>-58.427201</v>
       </c>
       <c r="N13" t="n">
-        <v>-34.620313</v>
+        <v>-34.617131</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ALM-B</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1539,7 +1539,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>804270068</t>
+          <t>804270074</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Quito 4292</t>
+          <t>Maza 836</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>804270068</t>
+          <t>804270074</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1596,14 +1596,14 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-58.427201</v>
+        <v>-58.414984</v>
       </c>
       <c r="N14" t="n">
-        <v>-34.617131</v>
+        <v>-34.621386</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1625,17 +1625,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>804270074</t>
+          <t>S00431877</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3/21/2025</t>
+          <t>4/8/2025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Maza 836</t>
+          <t>SARMIENTO 4290</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>804270074</t>
+          <t>804569065</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna corroída en su base entro tambien como caso 7049</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1679,17 +1679,17 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>-58.414984</v>
+        <v>-58.425764</v>
       </c>
       <c r="N15" t="n">
-        <v>-34.621386</v>
+        <v>-34.604359</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>ALM-L</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1711,27 +1711,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S00431877</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4/8/2025</t>
+          <t>4/23/2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SARMIENTO 4290</t>
+          <t>COCHABAMBA 2207</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1741,12 +1741,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>804569065</t>
+          <t>804903806</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Columna corroída en su base entro tambien como caso 7049</t>
+          <t>picada</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1765,17 +1765,17 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-58.425764</v>
+        <v>-58.396135</v>
       </c>
       <c r="N16" t="n">
-        <v>-34.604359</v>
+        <v>-34.624285</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>ALM-L</t>
+          <t>CON-C</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1797,17 +1797,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4/23/2025</t>
+          <t>4/29/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>COCHABAMBA 2207</t>
+          <t>República Bolivariana de Venezuela 2701</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>804903806</t>
+          <t>805507294</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>picada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1842,26 +1842,26 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>-58.396135</v>
+        <v>-58.404913</v>
       </c>
       <c r="N17" t="n">
-        <v>-34.624285</v>
+        <v>-34.615857</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CON-C</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1883,17 +1883,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4/29/2025</t>
+          <t>5/1/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>República Bolivariana de Venezuela 2701</t>
+          <t>RIOBAMBA 659</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>805507294</t>
+          <t>805579188</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Pendiente de traspaso nodo entro tambien como 7100</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1933,17 +1933,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L18" t="n">
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>-58.404913</v>
+        <v>-58.394118</v>
       </c>
       <c r="N18" t="n">
-        <v>-34.615857</v>
+        <v>-34.601416</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>RET-H</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1969,17 +1969,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5/1/2025</t>
+          <t>5/19/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RIOBAMBA 659</t>
+          <t>AYACUCHO 267</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>805579188</t>
+          <t>806926385</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pendiente de traspaso nodo entro tambien como 7100</t>
+          <t>Colocar columna y dar aviso para traspaso de nodo teco</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2026,10 +2026,10 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>-58.394118</v>
+        <v>-58.395063</v>
       </c>
       <c r="N19" t="n">
-        <v>-34.601416</v>
+        <v>-34.606257</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>RET-H</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2055,22 +2055,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5/19/2025</t>
+          <t>5/26/2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AYACUCHO 267</t>
+          <t>COCHABAMBA 4090</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2085,12 +2085,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>806926385</t>
+          <t>806926861</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Colocar columna y dar aviso para traspaso de nodo teco</t>
+          <t>Columna base podrida colocar r400 para pedir traspaso de fuente</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2112,14 +2112,14 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>-58.395063</v>
+        <v>-58.422268</v>
       </c>
       <c r="N20" t="n">
-        <v>-34.606257</v>
+        <v>-34.627754</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>807187860</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5/26/2025</t>
+          <t>6/4/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>COCHABAMBA 4090</t>
+          <t>San Juan 3960</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>806926861</t>
+          <t>807187860</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Columna base podrida colocar r400 para pedir traspaso de fuente</t>
+          <t>Colocar columna contactar a Matias Tapia 1171744701 por si hay alguna duda o problema que surja en el momento ya que es para posterior tendido de ftth</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2198,10 +2198,10 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>-58.422268</v>
+        <v>-58.420909</v>
       </c>
       <c r="N21" t="n">
-        <v>-34.627754</v>
+        <v>-34.626221</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>PPT-R</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2227,17 +2227,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>807187860</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6/4/2025</t>
+          <t>6/5/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Juan 3960</t>
+          <t>MAZA 181</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>807187860</t>
+          <t>807215439</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Colocar columna contactar a Matias Tapia 1171744701 por si hay alguna duda o problema que surja en el momento ya que es para posterior tendido de ftth</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2284,14 +2284,14 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>-58.420909</v>
+        <v>-58.416477</v>
       </c>
       <c r="N22" t="n">
-        <v>-34.626221</v>
+        <v>-34.61303</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>PPT-R</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2313,7 +2313,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MAZA 181</t>
+          <t>ESTADO DE PALESTINA 771</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>807215439</t>
+          <t>807215458</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada y mal ubicada ver con Pedro</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2370,10 +2370,10 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-58.416477</v>
+        <v>-58.425478</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.61303</v>
+        <v>-34.601865</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2399,22 +2399,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6/5/2025</t>
+          <t>6/9/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 771</t>
+          <t>ALBERTI 191</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>807215458</t>
+          <t>810533286</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Picada y mal ubicada ver con Pedro</t>
+          <t>Desmontar PRFV 400</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2456,10 +2456,10 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.425478</v>
+        <v>-58.401624</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.601865</v>
+        <v>-34.612001</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2485,17 +2485,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6/9/2025</t>
+          <t>6/24/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ALBERTI 191</t>
+          <t>MATHEU 727</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2515,14 +2515,10 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>810533286</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Desmontar PRFV 400</t>
-        </is>
-      </c>
+          <t>ICD31456940</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -2530,7 +2526,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Nodo TLC</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2542,10 +2538,10 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.401624</v>
+        <v>-58.400169</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.612001</v>
+        <v>-34.617784</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2559,7 +2555,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>CEN-N</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2571,17 +2567,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6/24/2025</t>
+          <t>6/30/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MATHEU 727</t>
+          <t>CHILE 2561</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2601,7 +2597,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ICD31456940</t>
+          <t>807851584</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -2612,7 +2608,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Nodo TLC</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2624,10 +2620,10 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.400169</v>
+        <v>-58.401827</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.617784</v>
+        <v>-34.617667</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2641,7 +2637,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>CEN-N</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2653,17 +2649,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>-510</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6/30/2025</t>
+          <t>7/14/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CHILE 2561</t>
+          <t>Larrea 590</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2673,7 +2669,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2683,10 +2679,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>807851584</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>808194254</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Picada</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2706,10 +2706,10 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.401827</v>
+        <v>-58.402353</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.617667</v>
+        <v>-34.602205</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>CLI-E</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2735,7 +2735,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>-510</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Larrea 590</t>
+          <t>CASTELLI 304</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>808194254</t>
+          <t>808194260</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2792,10 +2792,10 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.402353</v>
+        <v>-58.404696</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.602205</v>
+        <v>-34.606337</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>CLI-E</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2821,17 +2821,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7/14/2025</t>
+          <t>7/15/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CASTELLI 304</t>
+          <t>TUCUMAN 3253</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>808194260</t>
+          <t>808373657</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2878,10 +2878,10 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.404696</v>
+        <v>-58.411609</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.606337</v>
+        <v>-34.600329</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CLI-F</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2907,17 +2907,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7/15/2025</t>
+          <t>7/29/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TUCUMAN 3253</t>
+          <t>CALLAO AV. 316</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>808373657</t>
+          <t>808579773</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2964,14 +2964,14 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.411609</v>
+        <v>-58.39231</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.600329</v>
+        <v>-34.605507</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>CLI-F</t>
+          <t>CEN-E</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2993,17 +2993,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7/29/2025</t>
+          <t>8/4/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CALLAO AV. 316</t>
+          <t>MITRE, BARTOLOME 2482</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>808579773</t>
+          <t>808703866</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3050,14 +3050,14 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.39231</v>
+        <v>-58.40161</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.605507</v>
+        <v>-34.608641</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>CEN-E</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3079,27 +3079,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8/4/2025</t>
+          <t>8/12/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MITRE, BARTOLOME 2482</t>
+          <t>MARMOL, JOSE 228</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3109,12 +3109,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>808703866</t>
+          <t>808918687</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Se deriva directamente a traspaso de fuente ya que hay una columna existente</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3133,13 +3133,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.40161</v>
+        <v>-58.425858</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.608641</v>
+        <v>-34.61629</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3165,27 +3165,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8/12/2025</t>
+          <t>8/26/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MARMOL, JOSE 228</t>
+          <t>SARANDI 1011</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>808918687</t>
+          <t>809195660</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Se deriva directamente a traspaso de fuente ya que hay una columna existente</t>
+          <t>Picada entro tambien como caso 7209</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3219,17 +3219,17 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.425858</v>
+        <v>-58.394543</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.61629</v>
+        <v>-34.620732</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3251,7 +3251,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SARANDI 1011</t>
+          <t>PRINGLES 788</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>809195660</t>
+          <t>809195664</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Picada entro tambien como caso 7209</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3301,21 +3301,21 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L34" t="n">
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.394543</v>
+        <v>-58.427206</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.620732</v>
+        <v>-34.602914</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3337,17 +3337,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7050</t>
+          <t>-596</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>8/26/2025</t>
+          <t>9/14/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PRINGLES 788</t>
+          <t>Humahuaca 3866</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>809195664</t>
+          <t>809732190</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L35" t="n">
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.427206</v>
+        <v>-58.418823</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.602914</v>
+        <v>-34.602148</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3423,22 +3423,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>-596</t>
+          <t>-597</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>9/14/2025</t>
+          <t>9/16/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Humahuaca 3866</t>
+          <t>La Rioja 1261</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>809732190</t>
+          <t>809800215</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3480,14 +3480,14 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.418823</v>
+        <v>-58.407029</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.602148</v>
+        <v>-34.62526</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3509,17 +3509,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>-597</t>
+          <t>-603</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/22/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>La Rioja 1261</t>
+          <t>ANCHORENA, TOMAS MANUEL DE, DR. 821</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>809800215</t>
+          <t>809910086</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna chocada pendiente para instalar un corporativo</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3566,14 +3566,14 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.407029</v>
+        <v>-58.408551</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.62526</v>
+        <v>-34.599265</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>CLI-F</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3595,22 +3595,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>-603</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>9/22/2025</t>
+          <t>9/25/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ANCHORENA, TOMAS MANUEL DE, DR. 821</t>
+          <t>MARMOL, JOSE 588</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>809910086</t>
+          <t>809979740</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Columna chocada pendiente para instalar un corporativo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3652,10 +3652,10 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.408551</v>
+        <v>-58.425357</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.599265</v>
+        <v>-34.620223</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>CLI-F</t>
+          <t>ALM-B</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3681,22 +3681,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>-628</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>9/25/2025</t>
+          <t>10/1/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MARMOL, JOSE 588</t>
+          <t>Hipolito Yrigoyen 3250</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>809979740</t>
+          <t>810093628</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3738,10 +3738,10 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.425357</v>
+        <v>-58.412606</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.620223</v>
+        <v>-34.612353</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>ALM-B</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3767,17 +3767,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>-628</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10/1/2025</t>
+          <t>10/6/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hipolito Yrigoyen 3250</t>
+          <t>LARREA 320</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>810093628</t>
+          <t>810244454</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3824,10 +3824,10 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.412606</v>
+        <v>-58.402105</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.612353</v>
+        <v>-34.606071</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3853,7 +3853,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6404</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LARREA 320</t>
+          <t>RINCON 781</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>810244454</t>
+          <t>810244458</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3910,10 +3910,10 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.402105</v>
+        <v>-58.396055</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.606071</v>
+        <v>-34.618126</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3939,17 +3939,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>7713</t>
+          <t>-633</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10/6/2025</t>
+          <t>10/8/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>RINCON 781</t>
+          <t>Junin 74</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3969,12 +3969,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>810244458</t>
+          <t>ICD31464881</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R400</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3993,13 +3993,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.396055</v>
+        <v>-58.39641</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.618126</v>
+        <v>-34.608561</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>CLI-C</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4025,22 +4025,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>-633</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10/8/2025</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Junin 74</t>
+          <t>SAN JUAN AV. 4256</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ICD31464881</t>
+          <t>810394752</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Colocar R400</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4079,17 +4079,17 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.39641</v>
+        <v>-58.424867</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.608561</v>
+        <v>-34.626806</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>CLI-C</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4111,17 +4111,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>10/20/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 4256</t>
+          <t>CORRIENTES AV. 4515</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>810394752</t>
+          <t>810398934</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4168,14 +4168,14 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.424867</v>
+        <v>-58.428907</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.626806</v>
+        <v>-34.602301</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4197,17 +4197,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10/20/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CORRIENTES AV. 4515</t>
+          <t>SANCHEZ DE LORIA 1923</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>810398934</t>
+          <t>810416656</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>cambiar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4254,14 +4254,14 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.428907</v>
+        <v>-58.411426</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.602301</v>
+        <v>-34.633266</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4283,17 +4283,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1923</t>
+          <t>CALVO, CARLOS 3762</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4313,12 +4313,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>810416656</t>
+          <t>810451584</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4340,14 +4340,14 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.411426</v>
+        <v>-58.418542</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.633266</v>
+        <v>-34.624609</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4369,22 +4369,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3762</t>
+          <t>ALSINA, ADOLFO 2499</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>810451584</t>
+          <t>810487023</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4426,14 +4426,14 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.418542</v>
+        <v>-58.40129</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.624609</v>
+        <v>-34.612123</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4455,7 +4455,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ALSINA, ADOLFO 2499</t>
+          <t>LINIERS VIRREY 1142</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4485,12 +4485,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>810487023</t>
+          <t>810487035</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4512,14 +4512,14 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.40129</v>
+        <v>-58.413563</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.612123</v>
+        <v>-34.624645</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4541,17 +4541,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1142</t>
+          <t>SAN JUAN AV. 3741</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>810487035</t>
+          <t>810712796</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4598,10 +4598,10 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.413563</v>
+        <v>-58.418108</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.624645</v>
+        <v>-34.62564</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4627,22 +4627,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/17/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 3741</t>
+          <t>Paso 280</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>810712796</t>
+          <t>810787612</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>base picada</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4684,14 +4684,14 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.418108</v>
+        <v>-58.403566</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.62564</v>
+        <v>-34.606691</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4713,22 +4713,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>11/14/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Paso 280</t>
+          <t>DIAZ VELEZ AV. 3485</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>810787612</t>
+          <t>810787513</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>base picada</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4770,10 +4770,10 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.403566</v>
+        <v>-58.415838</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.606691</v>
+        <v>-34.608469</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CLI-J</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4799,17 +4799,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>S00110420</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11/14/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV. 3485</t>
+          <t>YATAY 760</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>810787513</t>
+          <t>810804303</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4856,10 +4856,10 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.415838</v>
+        <v>-58.428752</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.608469</v>
+        <v>-34.603273</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>CLI-J</t>
+          <t>ALM-M</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4885,17 +4885,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S00110420</t>
+          <t>S00921590</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>YATAY 760</t>
+          <t>CASEROS AV. 3621</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4915,12 +4915,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>810804303</t>
+          <t>810804462</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4942,14 +4942,14 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.428752</v>
+        <v>-58.416134</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.603273</v>
+        <v>-34.638879</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>ALM-M</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4971,7 +4971,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S00921590</t>
+          <t>S00921597</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CASEROS AV. 3621</t>
+          <t>CASEROS AV. 3507</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>810804462</t>
+          <t>810804451</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5028,10 +5028,10 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.416134</v>
+        <v>-58.414769</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.638879</v>
+        <v>-34.638638</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S00921597</t>
+          <t>S00921602</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CASEROS AV. 3507</t>
+          <t>CASEROS AV. 3411</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>810804451</t>
+          <t>810804383</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo TLC</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5114,10 +5114,10 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.414769</v>
+        <v>-58.413499</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.638638</v>
+        <v>-34.638416</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S00921602</t>
+          <t>S00942399</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CASEROS AV. 3411</t>
+          <t>ESTADOS UNIDOS 4030</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5173,12 +5173,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>810804383</t>
+          <t xml:space="preserve">01503983 </t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>base corroida Colocar PRFV 400</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Nodo TLC</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5200,14 +5200,14 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.413499</v>
+        <v>-58.422536</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.638416</v>
+        <v>-34.623094</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5229,7 +5229,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S00942399</t>
+          <t>01110546</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ESTADOS UNIDOS 4030</t>
+          <t>ALSINA, ADOLFO 2490</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">01503983 </t>
+          <t>810804369</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>base corroida Colocar PRFV 400</t>
+          <t>columna inclinada  base corroida</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5286,14 +5286,14 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.422536</v>
+        <v>-58.401266</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.623094</v>
+        <v>-34.612194</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5315,17 +5315,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>01110546</t>
+          <t>7874</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ALSINA, ADOLFO 2490</t>
+          <t>SAN LUIS 2488</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>810804369</t>
+          <t>810820592</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>columna inclinada  base corroida</t>
+          <t>base muy picada</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5372,10 +5372,10 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.401266</v>
+        <v>-58.402179</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.612194</v>
+        <v>-34.600152</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>CLI-E</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5401,17 +5401,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>-687</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SAN LUIS 2488</t>
+          <t>Junin 722</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>810820592</t>
+          <t>810862729</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>base muy picada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5458,10 +5458,10 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.402179</v>
+        <v>-58.397171</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.600152</v>
+        <v>-34.600729</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -5475,34 +5475,34 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>CLI-E</t>
+          <t>RET-J</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>-687</t>
+          <t>900008882010</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Junin 722</t>
+          <t xml:space="preserve"> PAVON AV. 3707 </t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>810862729</t>
+          <t>810984598</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5544,14 +5544,14 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.397171</v>
+        <v>-58.416724</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.600729</v>
+        <v>-34.630181</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5561,29 +5561,29 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>RET-J</t>
+          <t>PPT-R</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>900008882010</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PAVON AV. 3707 </t>
+          <t>Querandíes 4220</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5603,12 +5603,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>810984598</t>
+          <t>810984700</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>correr, obstaculiza acceso a garage</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5623,21 +5623,21 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L61" t="n">
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.416724</v>
+        <v>-58.426168</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.630181</v>
+        <v>-34.611095</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>PPT-R</t>
+          <t>ALM-E</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5659,22 +5659,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Querandíes 4220</t>
+          <t xml:space="preserve">URQUIZA, GRAL. 779 </t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>810984700</t>
+          <t>811198737</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>correr, obstaculiza acceso a garage</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5709,17 +5709,17 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L62" t="n">
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.426168</v>
+        <v>-58.409318</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.611095</v>
+        <v>-34.619842</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>ALM-E</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5745,7 +5745,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">URQUIZA, GRAL. 779 </t>
+          <t xml:space="preserve">HUMAHUACA 4298 </t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>811198737</t>
+          <t>811198696</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5802,10 +5802,10 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.409318</v>
+        <v>-58.425302</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.619842</v>
+        <v>-34.601502</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5831,17 +5831,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>S01199412</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUMAHUACA 4298 </t>
+          <t>ACUÑA DE FIGUEROA, FRANCISCO 1028</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>811198696</t>
+          <t>811198676</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5888,10 +5888,10 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.425302</v>
+        <v>-58.422033</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.601502</v>
+        <v>-34.598976</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>CLI-L</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5917,22 +5917,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S01199412</t>
+          <t>-705</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/22/2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ACUÑA DE FIGUEROA, FRANCISCO 1028</t>
+          <t>Larrea 370</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>811198676</t>
+          <t>02013924</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -5974,10 +5974,10 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.422033</v>
+        <v>-58.402154</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.598976</v>
+        <v>-34.605295</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>CLI-L</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6003,22 +6003,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>-705</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12/22/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Larrea 370</t>
+          <t>BRAVO, MARIO 478</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>02013924</t>
+          <t>811299416</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6060,10 +6060,10 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.402154</v>
+        <v>-58.416901</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.605295</v>
+        <v>-34.604236</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6089,17 +6089,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>-711</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BRAVO, MARIO 478</t>
+          <t>México 3306</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>811299416</t>
+          <t>811299443</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6146,10 +6146,10 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.416901</v>
+        <v>-58.412865</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.604236</v>
+        <v>-34.619484</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6175,17 +6175,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>-711</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>México 3306</t>
+          <t>LAMBARE 864</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>811299443</t>
+          <t>811453866</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6232,10 +6232,10 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.412865</v>
+        <v>-58.430579</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.619484</v>
+        <v>-34.604908</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>ALM-M</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6261,17 +6261,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>S00941232</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>LAMBARE 864</t>
+          <t>TARIJA 3323</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6291,12 +6291,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>811453866</t>
+          <t>811453904</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6318,14 +6318,14 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.430579</v>
+        <v>-58.412204</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.604908</v>
+        <v>-34.628609</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>ALM-M</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6347,22 +6347,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S00941232</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TARIJA 3323</t>
+          <t>Catamarca 236</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6377,12 +6377,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>811453904</t>
+          <t xml:space="preserve">02511385 </t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6404,14 +6404,14 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.412204</v>
+        <v>-58.406807</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.628609</v>
+        <v>-34.612902</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6433,7 +6433,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>8124</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Catamarca 236</t>
+          <t xml:space="preserve"> DIAZ VELEZ AV. 4421</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">02511385 </t>
+          <t>811454440</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6490,10 +6490,10 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.406807</v>
+        <v>-58.429481</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.612902</v>
+        <v>-34.608647</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>ALM-K</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6519,22 +6519,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>S01432754</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/16/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DIAZ VELEZ AV. 4421</t>
+          <t>MISIONES 242</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>811454440</t>
+          <t>811454538</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6576,10 +6576,10 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.429481</v>
+        <v>-58.404243</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.608647</v>
+        <v>-34.612859</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>ALM-K</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6605,7 +6605,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S01432754</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MISIONES 242</t>
+          <t>Castelli 60</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6635,37 +6635,25 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>811454538</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>corroida</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+          <t>traspaso propio tlc coloco columna</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="n">
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.404243</v>
+        <v>-58.404691</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.612859</v>
+        <v>-34.609194</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -6679,7 +6667,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6691,17 +6679,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>S01408162</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1/16/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Castelli 60</t>
+          <t xml:space="preserve">GARAY, JUAN DE AV. 2871 </t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6711,7 +6699,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6721,29 +6709,41 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812439895</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>traspaso propio tlc coloco columna</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
       <c r="L74" t="n">
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.404691</v>
+        <v>-58.4048</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.609194</v>
+        <v>-34.629021</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6765,17 +6765,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S01408162</t>
+          <t>S00034481</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARAY, JUAN DE AV. 2871 </t>
+          <t xml:space="preserve">MITRE, BARTOLOME 2294 </t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>812439895</t>
+          <t>811626888</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6822,14 +6822,14 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.4048</v>
+        <v>-58.399059</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.629021</v>
+        <v>-34.608499</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>CLI-C</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6851,17 +6851,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S00034481</t>
+          <t>S01314715</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">MITRE, BARTOLOME 2294 </t>
+          <t xml:space="preserve"> CATAMARCA 919</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6881,12 +6881,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>811626888</t>
+          <t>811626986</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Corroida</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6908,14 +6908,14 @@
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.399059</v>
+        <v>-58.404766</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.608499</v>
+        <v>-34.620521</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>CLI-C</t>
+          <t>CEN-K</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6937,7 +6937,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S01314715</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CATAMARCA 919</t>
+          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>811626986</t>
+          <t>811626981</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6994,14 +6994,14 @@
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.404766</v>
+        <v>-58.423058</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.620521</v>
+        <v>-34.608916</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>CEN-K</t>
+          <t>ALM-E</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7023,22 +7023,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8125</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
+          <t>COMBATE DE LOS POZOS 1103</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>811626981</t>
+          <t>811627014</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7080,14 +7080,14 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.423058</v>
+        <v>-58.393145</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.608916</v>
+        <v>-34.621778</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>ALM-E</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7109,17 +7109,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>S00022862</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>COMBATE DE LOS POZOS 1103</t>
+          <t>YRIGOYEN, HIPOLITO 2395</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>811627014</t>
+          <t>811627077</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7166,14 +7166,14 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.393145</v>
+        <v>-58.400243</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.621778</v>
+        <v>-34.610864</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7195,7 +7195,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S00022862</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO 2395</t>
+          <t>PICHINCHA 89</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7225,12 +7225,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>811627077</t>
+          <t>811627062</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7252,10 +7252,10 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.400243</v>
+        <v>-58.399124</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.610864</v>
+        <v>-34.610705</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -7281,22 +7281,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/6/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PICHINCHA 89</t>
+          <t>GALLO 77</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>811627062</t>
+          <t>811627128</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>tensor roto inclinada</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7331,17 +7331,17 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L81" t="n">
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.399124</v>
+        <v>-58.413979</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.610705</v>
+        <v>-34.607475</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7367,22 +7367,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>8296</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2/6/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GALLO 77</t>
+          <t>RINCON 1109</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>811627128</t>
+          <t>812439968</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>tensor roto inclinada</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7417,21 +7417,21 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L82" t="n">
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.413979</v>
+        <v>-58.395668</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.607475</v>
+        <v>-34.621926</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>CEN-N</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7453,17 +7453,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>8329</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>RINCON 1109</t>
+          <t xml:space="preserve">ALBERTI 1055 </t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7483,12 +7483,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>812439968</t>
+          <t>812440156</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7510,10 +7510,10 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.395668</v>
+        <v>-58.400774</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.621926</v>
+        <v>-34.621503</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -7539,17 +7539,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>S00136365</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALBERTI 1055 </t>
+          <t>PERON, JUAN DOMINGO, TTE. GENERAL 2697</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7569,7 +7569,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>812440156</t>
+          <t>812440173</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7596,14 +7596,14 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.400774</v>
+        <v>-58.404576</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.621503</v>
+        <v>-34.607569</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>CEN-N</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -7625,7 +7625,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S00136365</t>
+          <t>S00144805</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PERON, JUAN DOMINGO, TTE. GENERAL 2697</t>
+          <t>VIAMONTE 1990</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>812440173</t>
+          <t>812440165</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7682,10 +7682,10 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.404576</v>
+        <v>-58.395384</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.607569</v>
+        <v>-34.600962</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -7699,29 +7699,29 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>RET-J</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S00144805</t>
+          <t>-749</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>VIAMONTE 1990</t>
+          <t>Moreno 2965</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>812440165</t>
+          <t>812440614</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7768,10 +7768,10 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.395384</v>
+        <v>-58.407758</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.600962</v>
+        <v>-34.613793</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -7785,19 +7785,19 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>RET-J</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>-749</t>
+          <t>-760</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Moreno 2965</t>
+          <t>MAZA 1615</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7827,12 +7827,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>812440614</t>
+          <t>812440354</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>base corroida e inclinada</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7854,14 +7854,14 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.407758</v>
+        <v>-58.414586</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.613793</v>
+        <v>-34.630095</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7883,7 +7883,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>-760</t>
+          <t>S00519068</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MAZA 1615</t>
+          <t>CALVO, CARLOS 3747</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>812440354</t>
+          <t>812440282</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>base corroida e inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7940,10 +7940,10 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.414586</v>
+        <v>-58.41859</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.630095</v>
+        <v>-34.624508</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7969,17 +7969,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S00519068</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/27/2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3747</t>
+          <t xml:space="preserve">BRAVO, MARIO 836 </t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>812440282</t>
+          <t>812503638</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8026,14 +8026,14 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.41859</v>
+        <v>-58.416187</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.624508</v>
+        <v>-34.600138</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CLI-G</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8055,17 +8055,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>S00100362</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2/27/2026</t>
+          <t>3/4/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRAVO, MARIO 836 </t>
+          <t>RIO DE JANEIRO 901</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>812503638</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8112,10 +8112,10 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.416187</v>
+        <v>-58.431406</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.600138</v>
+        <v>-34.605009</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>CLI-G</t>
+          <t>ALM-M</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8141,17 +8141,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S00100362</t>
+          <t>-774</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>3/4/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO 901</t>
+          <t>CASEROS AV. 4131</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>mover a 4111</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8198,14 +8198,14 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.431406</v>
+        <v>-58.422741</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.605009</v>
+        <v>-34.639999</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>ALM-M</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8227,17 +8227,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>-774</t>
+          <t>00050599</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CASEROS AV. 4131</t>
+          <t xml:space="preserve">BELGRANO AV 3689 </t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812879940</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>mover a 4111</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8284,14 +8284,14 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.422741</v>
+        <v>-58.418254</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.639999</v>
+        <v>-34.615692</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8313,7 +8313,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>00050599</t>
+          <t>00223191</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">BELGRANO AV 3689 </t>
+          <t>CATAMARCA 254</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>812879940</t>
+          <t>812879982</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -8370,10 +8370,10 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.418254</v>
+        <v>-58.406734</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.615692</v>
+        <v>-34.613107</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8399,7 +8399,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>00223191</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8409,12 +8409,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CATAMARCA 254</t>
+          <t>CORRIENTES AV 4073</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>812879982</t>
+          <t>812880406</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -8456,10 +8456,10 @@
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.406734</v>
+        <v>-58.422076</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.613107</v>
+        <v>-34.60298</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8485,7 +8485,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>00223023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CORRIENTES AV 4073</t>
+          <t>SAN JUAN AV. 2201</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>812880406</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -8542,14 +8542,14 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.422076</v>
+        <v>-58.396491</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.60298</v>
+        <v>-34.622986</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8571,22 +8571,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>00223023</t>
+          <t>00317296</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/23/2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 2201</t>
+          <t>AGRELO 3620</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8601,14 +8601,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
+          <t>812880625</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
           <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
       <c r="I96" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -8628,14 +8628,14 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.396491</v>
+        <v>-58.417002</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.622986</v>
+        <v>-34.618613</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>ALM-B</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8657,7 +8657,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>00317296</t>
+          <t>00322642</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AGRELO 3620</t>
+          <t>ESTADO DE PALESTINA 727</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>812880625</t>
+          <t>812880655</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -8714,10 +8714,10 @@
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.417002</v>
+        <v>-58.425539</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.618613</v>
+        <v>-34.602286</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>ALM-B</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8743,7 +8743,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>00322642</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 727</t>
+          <t>MEXICO 3306</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>812880655</t>
+          <t>812880662</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -8800,10 +8800,10 @@
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.425539</v>
+        <v>-58.412865</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.602286</v>
+        <v>-34.619484</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8829,7 +8829,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>8265</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MEXICO 3306</t>
+          <t>HUMBERTO 1 1999</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>812880662</t>
+          <t>812880685</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -8886,14 +8886,14 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.412865</v>
+        <v>-58.394304</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.619484</v>
+        <v>-34.621645</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8915,17 +8915,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>3/23/2026</t>
+          <t>3/28/2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HUMBERTO 1 1999</t>
+          <t>RIVADAVIA AV 1985</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8945,17 +8945,17 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>812880685</t>
+          <t>812880736</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>APLOMAR COLUMNA</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -8972,14 +8972,14 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.394304</v>
+        <v>-58.394609</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.621645</v>
+        <v>-34.609304</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9001,22 +9001,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>M881</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>3/28/2026</t>
+          <t>4/1/2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>RIVADAVIA AV 1985</t>
+          <t>AV LA PLATA 2288</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9031,22 +9031,22 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>812880736</t>
+          <t>813046342</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>APLOMAR COLUMNA</t>
+          <t>DESMONTAR COLUMNA Y  DESPLAZAR PCALOGERO</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -9058,14 +9058,14 @@
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.394609</v>
+        <v>-58.423203</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.609304</v>
+        <v>-34.640909</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9087,22 +9087,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>M881</t>
+          <t>8802</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>4/1/2026</t>
+          <t>4/11/2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AV LA PLATA 2288</t>
+          <t>RINCON 731</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>813046342</t>
+          <t>813046658</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>DESMONTAR COLUMNA Y  DESPLAZAR PCALOGERO</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9144,14 +9144,14 @@
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.423203</v>
+        <v>-58.396088</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.640909</v>
+        <v>-34.617527</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9173,7 +9173,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>8802</t>
+          <t>S00374917</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>RINCON 731</t>
+          <t>24 DE NOVIEMBRE 695</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>813046658</t>
+          <t>813046791</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9230,10 +9230,10 @@
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.396088</v>
+        <v>-58.411053</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.617527</v>
+        <v>-34.618979</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9259,7 +9259,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S00374917</t>
+          <t>S00379764</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>24 DE NOVIEMBRE 695</t>
+          <t>JAURES JEAN 491</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>813046791</t>
+          <t>813046795</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -9316,10 +9316,10 @@
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.411053</v>
+        <v>-58.408934</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.618979</v>
+        <v>-34.604273</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>CLI-H</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9345,7 +9345,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S00379764</t>
+          <t>S00379996</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>JAURES JEAN 491</t>
+          <t>SARANDI 1439</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>813046795</t>
+          <t>813046806</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -9402,14 +9402,14 @@
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.408934</v>
+        <v>-58.393455</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.604273</v>
+        <v>-34.625779</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -9419,7 +9419,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>CLI-H</t>
+          <t>CON-C</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9431,7 +9431,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S00379996</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SARANDI 1439</t>
+          <t>SARMIENTO 2108</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>813046806</t>
+          <t>813046819</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -9488,14 +9488,14 @@
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.393455</v>
+        <v>-58.39675</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.625779</v>
+        <v>-34.605996</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>CON-C</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9517,7 +9517,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9527,12 +9527,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SARMIENTO 2108</t>
+          <t>SANCHEZ DE BUSTAMANTE 633</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>813046819</t>
+          <t>813046866</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -9574,10 +9574,10 @@
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.39675</v>
+        <v>-58.414203</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.605996</v>
+        <v>-34.602602</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>CLI-G</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9603,7 +9603,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SANCHEZ DE BUSTAMANTE 633</t>
+          <t>RIVADAVIA AV 4245</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>813046866</t>
+          <t>813046970</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -9660,10 +9660,10 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.414203</v>
+        <v>-58.425567</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.602602</v>
+        <v>-34.613382</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>CLI-G</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9689,7 +9689,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>RIVADAVIA AV 4245</t>
+          <t>DIAZ VELEZ AV 4449</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>813046970</t>
+          <t>813046971</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -9746,10 +9746,10 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.425567</v>
+        <v>-58.429714</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.613382</v>
+        <v>-34.608645</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>ALM-K</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9775,7 +9775,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV 4449</t>
+          <t>LAS CASAS 3989</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>813046971</t>
+          <t>813046994</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -9832,14 +9832,14 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.429714</v>
+        <v>-58.421676</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.608645</v>
+        <v>-34.635878</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>ALM-K</t>
+          <t>PPT-R</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9861,7 +9861,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>8851</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>LAS CASAS 3989</t>
+          <t>SALCEDO 3541</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>813046994</t>
+          <t>813047007</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -9918,10 +9918,10 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.421676</v>
+        <v>-58.415121</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.635878</v>
+        <v>-34.633772</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>PPT-R</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9947,7 +9947,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>8852</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SALCEDO 3541</t>
+          <t>TARIJA 4079</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>813047007</t>
+          <t>813047012</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -10004,10 +10004,10 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.415121</v>
+        <v>-58.421804</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.633772</v>
+        <v>-34.629558</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>PPT-R</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10033,7 +10033,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>8853</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TARIJA 4079</t>
+          <t>TIMBUES 2086</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>813047012</t>
+          <t>813047017</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -10090,10 +10090,10 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.421804</v>
+        <v>-58.421835</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.629558</v>
+        <v>-34.63863</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>PPT-R</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10119,7 +10119,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>8855</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TIMBUES 2086</t>
+          <t>GOMEZ VALENTIN 3684</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>813047017</t>
+          <t>813047019</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -10176,14 +10176,14 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.421835</v>
+        <v>-58.416726</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.63863</v>
+        <v>-34.604773</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10205,7 +10205,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>S00390896</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10215,12 +10215,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>GOMEZ VALENTIN 3684</t>
+          <t>AV INDEPENDENCIA 2018</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>813047019</t>
+          <t>813047657</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -10262,10 +10262,10 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.416726</v>
+        <v>-58.39469</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.604773</v>
+        <v>-34.618394</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10291,22 +10291,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S00390896</t>
+          <t>RB00001</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AV INDEPENDENCIA 2018</t>
+          <t>BELGRANO AV. 3715</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>813047657</t>
+          <t>813304903</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -10348,10 +10348,10 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.39469</v>
+        <v>-58.418851</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.618394</v>
+        <v>-34.615716</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10377,7 +10377,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RB00001</t>
+          <t>AM00039</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BELGRANO AV. 3715</t>
+          <t>CASTRO BARROS 852</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>813304903</t>
+          <t>813304915</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -10434,14 +10434,14 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.418851</v>
+        <v>-58.419281</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.615716</v>
+        <v>-34.62215</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10463,7 +10463,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AM00039</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CASTRO BARROS 852</t>
+          <t>ALSINA, ADOLFO 3293</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>813304915</t>
+          <t>813350607</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -10520,14 +10520,14 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.419281</v>
+        <v>-58.412936</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.62215</v>
+        <v>-34.613332</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10549,7 +10549,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>S00423738</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ALSINA, ADOLFO 3293</t>
+          <t>CATAMARCA 568</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -10579,7 +10579,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>813350607</t>
+          <t>813350620</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -10606,10 +10606,10 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.412936</v>
+        <v>-58.405541</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.613332</v>
+        <v>-34.616959</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10635,22 +10635,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S00423738</t>
+          <t>S00299569</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/21/2026</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CATAMARCA 568</t>
+          <t>YRIGOYEN, HIPOLITO AV. 4156</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>813350620</t>
+          <t>813350953</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -10692,10 +10692,10 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.405541</v>
+        <v>-58.425213</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.616959</v>
+        <v>-34.614924</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10721,7 +10721,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S00299569</t>
+          <t>S004318770</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO AV. 4156</t>
+          <t>SARMIENTO 4290</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>813350953</t>
+          <t>813351576</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -10778,10 +10778,10 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.425213</v>
+        <v>-58.425764</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.614924</v>
+        <v>-34.604359</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>ALM-L</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10807,7 +10807,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S004318770</t>
+          <t>S00431893</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SARMIENTO 4290</t>
+          <t>MUÑIZ 1151</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>813351576</t>
+          <t>GENERADOR DE OT NO ENCUENTRA DIRECCION</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -10864,14 +10864,14 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.425764</v>
+        <v>-58.425442</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.604359</v>
+        <v>-34.627634</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>ALM-L</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10893,7 +10893,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S00431893</t>
+          <t>S00434849</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MUÑIZ 1151</t>
+          <t>YRIGOYEN, HIPOLITO AV. 3484</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>GENERADOR DE OT NO ENCUENTRA DIRECCION</t>
+          <t>813352212</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -10950,14 +10950,14 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.425442</v>
+        <v>-58.416028</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.627634</v>
+        <v>-34.613538</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10979,7 +10979,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S00434849</t>
+          <t xml:space="preserve">9009 </t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO AV. 3484</t>
+          <t>SANCHEZ DE LORIA 1913</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>813352212</t>
+          <t>813352473</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -11036,14 +11036,14 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.416028</v>
+        <v>-58.411474</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.613538</v>
+        <v>-34.633143</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11065,7 +11065,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9009 </t>
+          <t xml:space="preserve">9011 </t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1913</t>
+          <t>SANCHEZ DE LORIA 1583</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>813352473</t>
+          <t>813352481</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -11122,14 +11122,14 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.411474</v>
+        <v>-58.411926</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.633143</v>
+        <v>-34.628861</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11151,7 +11151,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9011 </t>
+          <t xml:space="preserve">9012 </t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1583</t>
+          <t xml:space="preserve">LINIERS VIRREY 2315 </t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>813352481</t>
+          <t>813352482</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -11208,14 +11208,14 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.411926</v>
+        <v>-58.41191</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.628861</v>
+        <v>-34.637333</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -11225,7 +11225,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11237,7 +11237,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9012 </t>
+          <t xml:space="preserve">9014 </t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINIERS VIRREY 2315 </t>
+          <t>LINIERS VIRREY 896</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11267,7 +11267,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>813352482</t>
+          <t>813352486</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -11294,14 +11294,14 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.41191</v>
+        <v>-58.413645</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.637333</v>
+        <v>-34.621935</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11323,7 +11323,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9014 </t>
+          <t xml:space="preserve">9016 </t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 896</t>
+          <t>HUMBERTO 1° 3368</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>813352486</t>
+          <t>813352494</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -11380,10 +11380,10 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.413645</v>
+        <v>-58.413189</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.621935</v>
+        <v>-34.624187</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9016 </t>
+          <t xml:space="preserve">9017 </t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>HUMBERTO 1° 3368</t>
+          <t>MUÑIZ 1237</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11439,7 +11439,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>813352494</t>
+          <t>GENERADOR DE OT NO ENCUENTRA DIRECCION</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -11466,10 +11466,10 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.413189</v>
+        <v>-58.425206</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.624187</v>
+        <v>-34.628705</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11495,7 +11495,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">9017 </t>
+          <t xml:space="preserve">9020 </t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MUÑIZ 1237</t>
+          <t>TARIJA 3497</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11525,7 +11525,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>GENERADOR DE OT NO ENCUENTRA DIRECCION</t>
+          <t>813352497</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -11552,10 +11552,10 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.425206</v>
+        <v>-58.414424</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.628705</v>
+        <v>-34.628778</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11581,17 +11581,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">9020 </t>
+          <t>9028</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>4/21/2026</t>
+          <t>4/24/2026</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>TARIJA 3497</t>
+          <t>BRAVO, MARIO 740</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11611,7 +11611,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>813352497</t>
+          <t>813352774</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -11638,14 +11638,14 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.414424</v>
+        <v>-58.416308</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.628778</v>
+        <v>-34.601047</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>CLI-G</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11667,7 +11667,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t>S00413025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11677,12 +11677,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>BRAVO, MARIO 740</t>
+          <t>CHILE 2550</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>813352774</t>
+          <t>813352855</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -11724,10 +11724,10 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.416308</v>
+        <v>-58.40174</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.601047</v>
+        <v>-34.617754</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>CLI-G</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11753,7 +11753,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S00413025</t>
+          <t>S00429731</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>CHILE 2550</t>
+          <t xml:space="preserve">ALSINA, ADOLFO 2291 </t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>813352855</t>
+          <t>813352873</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -11810,10 +11810,10 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.40174</v>
+        <v>-58.398771</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.617754</v>
+        <v>-34.611932</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11839,22 +11839,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S00429731</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/29/2026</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALSINA, ADOLFO 2291 </t>
+          <t xml:space="preserve">GALLEGOS 3443 </t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>813352873</t>
+          <t>813353299</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -11896,14 +11896,14 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.398771</v>
+        <v>-58.413647</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.611932</v>
+        <v>-34.631434</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11925,17 +11925,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t xml:space="preserve">9045 </t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>4/29/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALLEGOS 3443 </t>
+          <t>LINIERS VIRREY 1793</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>813353299</t>
+          <t>813631423</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -11982,14 +11982,14 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.413647</v>
+        <v>-58.413025</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.631434</v>
+        <v>-34.631929</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -12011,7 +12011,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">9045 </t>
+          <t>9049</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1793</t>
+          <t>BATHURST 3377</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>813631423</t>
+          <t>813631424</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -12068,10 +12068,10 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.413025</v>
+        <v>-58.411896</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.631929</v>
+        <v>-34.636028</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -12097,22 +12097,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>S00215089</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>BATHURST 3377</t>
+          <t>LARREA 122</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>813631424</t>
+          <t>813631550</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -12154,14 +12154,14 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.411896</v>
+        <v>-58.401972</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.636028</v>
+        <v>-34.608317</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12183,7 +12183,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S00215089</t>
+          <t>S00401648</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12193,7 +12193,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>LARREA 122</t>
+          <t>JUNIN 312</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>813631550</t>
+          <t>813632251</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -12240,10 +12240,10 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.401972</v>
+        <v>-58.396676</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.608317</v>
+        <v>-34.605753</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12269,7 +12269,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S00401648</t>
+          <t>S00465940</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12279,12 +12279,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>JUNIN 312</t>
+          <t>BELGRANO AV. 3669</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>813632251</t>
+          <t>813632257</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -12314,7 +12314,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -12326,10 +12326,10 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.396676</v>
+        <v>-58.417949</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.605753</v>
+        <v>-34.615674</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12355,7 +12355,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S00465940</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12365,12 +12365,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>BELGRANO AV. 3669</t>
+          <t>JAURES, JEAN 309</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12385,7 +12385,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>813632257</t>
+          <t>813632439</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -12412,10 +12412,10 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.417949</v>
+        <v>-58.409868</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.615674</v>
+        <v>-34.606562</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>CLI-H</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12441,22 +12441,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>S00364775</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>JAURES, JEAN 309</t>
+          <t>CASTRO 511</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12469,19 +12469,15 @@
           <t>FIBERWORK</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>813632439</t>
-        </is>
-      </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>NORMALIZAR RIENDA A PIQUE</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Tensor</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -12491,17 +12487,17 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L141" t="n">
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.409868</v>
+        <v>-58.420597</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.606562</v>
+        <v>-34.617818</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -12515,7 +12511,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>CLI-H</t>
+          <t>ALM-B</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12527,7 +12523,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S00364775</t>
+          <t>S00493114</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12537,12 +12533,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CASTRO 511</t>
+          <t>ARENALES 3648</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12555,39 +12551,43 @@
           <t>FIBERWORK</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>813352547</t>
+        </is>
+      </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>NORMALIZAR RIENDA A PIQUE</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Tensor</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L142" t="n">
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.420597</v>
+        <v>-58.413656</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.617818</v>
+        <v>-34.585464</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>ALM-B</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12609,7 +12609,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S00493114</t>
+          <t xml:space="preserve">7880 </t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ARENALES 3648</t>
+          <t>MUÑIZ 16</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12637,11 +12637,7 @@
           <t>FIBERWORK</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>813352547</t>
-        </is>
-      </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -12654,7 +12650,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -12666,14 +12662,14 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.413656</v>
+        <v>-58.427498</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.585464</v>
+        <v>-34.614599</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -12683,7 +12679,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12695,7 +12691,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">7880 </t>
+          <t xml:space="preserve">9923 </t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12705,7 +12701,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MUÑIZ 16</t>
+          <t>PRINGLES 1094</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -12748,10 +12744,10 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.427498</v>
+        <v>-58.426722</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.614599</v>
+        <v>-34.599427</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -12765,7 +12761,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12777,17 +12773,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9923 </t>
+          <t xml:space="preserve">9019 </t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>PRINGLES 1094</t>
+          <t>CASTRO BARROS AV. 338</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -12830,10 +12826,10 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.426722</v>
+        <v>-58.419864</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.599427</v>
+        <v>-34.616375</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -12847,7 +12843,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12859,7 +12855,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">9019 </t>
+          <t xml:space="preserve">9031 </t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12869,12 +12865,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CASTRO BARROS AV. 338</t>
+          <t>YRIGOYEN, HIPOLITO 1938</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -12900,7 +12896,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -12912,10 +12908,10 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.419864</v>
+        <v>-58.394079</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.616375</v>
+        <v>-34.61051</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -12929,7 +12925,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12941,7 +12937,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">9031 </t>
+          <t xml:space="preserve">9088 </t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12951,12 +12947,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO 1938</t>
+          <t>HUMAHUACA 4296</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -12982,7 +12978,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -12994,10 +12990,10 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.394079</v>
+        <v>-58.425282</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.61051</v>
+        <v>-34.601504</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -13011,7 +13007,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -13023,7 +13019,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">9088 </t>
+          <t xml:space="preserve">10059 </t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13033,12 +13029,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>HUMAHUACA 4296</t>
+          <t xml:space="preserve">SALGUERO, JERONIMO 2296 </t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13054,12 +13050,12 @@
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -13076,14 +13072,14 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.425282</v>
+        <v>-58.411132</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.601504</v>
+        <v>-34.585267</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -13093,92 +13089,10 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>AGU-K</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10059 </t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>5/14/2026</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SALGUERO, JERONIMO 2296 </t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>FIBERWORK</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>COLUMNA INCLINADA</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Aplomo</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L149" t="n">
-        <v>1</v>
-      </c>
-      <c r="M149" t="n">
-        <v>-58.411132</v>
-      </c>
-      <c r="N149" t="n">
-        <v>-34.585267</v>
-      </c>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P149" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>AGU-K</t>
-        </is>
-      </c>
-      <c r="R149" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_Fiberwork.xlsx
+++ b/mapa_interactivo_Fiberwork.xlsx
@@ -8085,7 +8085,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814105603</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>814107131</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>GENERADOR DE OT NO ENCUENTRA DIRECCION</t>
+          <t>814105853</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -11439,7 +11439,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>GENERADOR DE OT NO ENCUENTRA DIRECCION</t>
+          <t>814105864</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -12801,7 +12801,11 @@
           <t>FIBERWORK</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>814108068</t>
+        </is>
+      </c>
       <c r="H145" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -12965,7 +12969,11 @@
           <t>FIBERWORK</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>814108086</t>
+        </is>
+      </c>
       <c r="H147" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>

--- a/mapa_interactivo_Fiberwork.xlsx
+++ b/mapa_interactivo_Fiberwork.xlsx
@@ -8515,7 +8515,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>814109847</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -12637,7 +12637,11 @@
           <t>FIBERWORK</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>814109709</t>
+        </is>
+      </c>
       <c r="H143" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -12719,7 +12723,11 @@
           <t>FIBERWORK</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>814109753</t>
+        </is>
+      </c>
       <c r="H144" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>

--- a/mapa_interactivo_Fiberwork.xlsx
+++ b/mapa_interactivo_Fiberwork.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R148"/>
+  <dimension ref="A1:R154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,17 +439,17 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>OT</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Proveedor Asignado</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>OT</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -531,17 +531,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>798385574</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>FIBERWORK</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>798385574</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>798513095</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>FIBERWORK</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>798513095</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -699,17 +699,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>798894281</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>798894281</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>789151020</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>789151020</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>802438793</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>FIBERWORK</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>802438793</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -957,17 +957,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>802774521</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>FIBERWORK</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>802774521</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1043,17 +1043,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>803039902</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>803039902</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1129,17 +1129,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>803666441</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>803666441</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1215,17 +1215,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>804161204</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>804161204</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>804161231</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>804161231</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1387,17 +1387,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>804270064</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>804270064</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>804270068</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>804270068</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1559,17 +1559,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>804270074</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>804270074</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1645,17 +1645,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>804569065</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>804569065</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1731,17 +1731,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>804903806</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>FIBERWORK</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>804903806</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1817,17 +1817,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>805507294</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>FIBERWORK</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>805507294</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>805579188</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>FIBERWORK</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>805579188</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1989,17 +1989,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>806926385</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>806926385</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2075,17 +2075,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>806926861</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>806926861</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2161,17 +2161,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>807187860</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>807187860</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2247,17 +2247,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>807215439</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>FIBERWORK</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>807215439</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2333,17 +2333,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>807215458</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>807215458</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2419,17 +2419,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810533286</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>810533286</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2505,17 +2505,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>ICD31456940</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>FIBERWORK</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ICD31456940</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -2587,17 +2587,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>807851584</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>FIBERWORK</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>807851584</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -2669,17 +2669,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>808194254</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>808194254</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2755,17 +2755,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>808194260</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>808194260</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2841,17 +2841,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>808373657</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>808373657</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2927,17 +2927,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>808579773</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>808579773</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3013,17 +3013,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>808703866</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>808703866</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3099,17 +3099,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>808918687</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>FIBERWORK</t>
-        </is>
-      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>808918687</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3185,17 +3185,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>809195660</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>809195660</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>809195664</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>809195664</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3357,17 +3357,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>809732190</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>809732190</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3443,17 +3443,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>809800215</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>809800215</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3529,17 +3529,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>809910086</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>809910086</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3615,17 +3615,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>809979740</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>809979740</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3701,17 +3701,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810093628</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>810093628</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3787,17 +3787,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810244454</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>810244454</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3873,17 +3873,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810244458</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>810244458</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3959,17 +3959,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>ICD31464881</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ICD31464881</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810394752</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>810394752</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4131,17 +4131,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810398934</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>810398934</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4217,17 +4217,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810416656</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>810416656</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4303,17 +4303,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810451584</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>810451584</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4389,17 +4389,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810487023</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>810487023</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4475,17 +4475,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810487035</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>810487035</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4561,17 +4561,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810712796</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>810712796</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4647,17 +4647,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810787612</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>810787612</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4733,17 +4733,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810787513</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>810787513</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4819,17 +4819,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810804303</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>810804303</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4905,17 +4905,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810804462</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>810804462</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4991,17 +4991,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810804451</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>810804451</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5077,17 +5077,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810804383</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>810804383</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5163,17 +5163,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t xml:space="preserve">01503983 </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">01503983 </t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5249,17 +5249,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810804369</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>810804369</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5335,17 +5335,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810820592</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>810820592</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5421,17 +5421,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810862729</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>810862729</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5507,17 +5507,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810984598</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>810984598</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5593,17 +5593,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>810984700</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>810984700</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5679,17 +5679,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811198737</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>811198737</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5765,17 +5765,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811198696</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>811198696</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5851,17 +5851,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811198676</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>811198676</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5937,17 +5937,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>02013924</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>02013924</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6023,17 +6023,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811299416</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>811299416</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6109,17 +6109,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811299443</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>811299443</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6195,17 +6195,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>811453866</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>FIBERWORK</t>
-        </is>
-      </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>811453866</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6281,17 +6281,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811453904</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>811453904</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t xml:space="preserve">02511385 </t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">02511385 </t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6453,17 +6453,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811454440</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>811454440</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6539,17 +6539,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811454538</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>811454538</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6625,17 +6625,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>FIBERWORK</t>
-        </is>
-      </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6699,17 +6699,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812439895</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>812439895</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6785,17 +6785,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811626888</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>811626888</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6871,17 +6871,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811626986</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>811626986</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6957,17 +6957,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811626981</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>811626981</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7043,17 +7043,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811627014</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>811627014</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7129,17 +7129,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811627077</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>811627077</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7215,17 +7215,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811627062</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>811627062</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -7301,17 +7301,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>811627128</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>811627128</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7387,17 +7387,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812439968</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>812439968</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -7473,17 +7473,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812440156</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>812440156</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -7559,17 +7559,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812440173</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>812440173</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7645,17 +7645,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812440165</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>812440165</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7731,17 +7731,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812440614</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>812440614</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -7817,17 +7817,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812440354</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>812440354</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7903,17 +7903,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812440282</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>812440282</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7989,17 +7989,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812503638</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>812503638</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8075,17 +8075,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814105603</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>814105603</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8161,17 +8161,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814107131</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>814107131</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8247,17 +8247,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812879940</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>812879940</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8333,17 +8333,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812879982</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>812879982</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -8419,17 +8419,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812880406</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>812880406</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -8505,17 +8505,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814109847</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>814109847</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -8591,17 +8591,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812880625</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>812880625</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -8677,17 +8677,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812880655</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>812880655</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -8763,17 +8763,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812880662</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>812880662</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -8849,17 +8849,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812880685</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>812880685</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -8935,17 +8935,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>812880736</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>812880736</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -9021,17 +9021,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813046342</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>813046342</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -9107,17 +9107,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813046658</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>813046658</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -9193,17 +9193,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813046791</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>813046791</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9279,17 +9279,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813046795</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>813046795</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -9365,17 +9365,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813046806</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>813046806</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -9451,17 +9451,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813046819</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>813046819</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -9537,17 +9537,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813046866</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>813046866</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -9623,17 +9623,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813046970</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>813046970</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -9709,17 +9709,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813046971</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>813046971</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -9795,17 +9795,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813046994</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>813046994</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -9881,17 +9881,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813047007</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>813047007</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -9967,17 +9967,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813047012</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>813047012</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -10053,17 +10053,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813047017</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>813047017</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -10139,17 +10139,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813047019</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>813047019</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -10225,17 +10225,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813047657</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>813047657</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -10311,17 +10311,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813304903</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>813304903</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -10397,17 +10397,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813304915</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>813304915</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -10483,17 +10483,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813350607</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>813350607</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -10569,17 +10569,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813350620</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>813350620</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -10655,17 +10655,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813350953</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>813350953</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -10741,17 +10741,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813351576</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>813351576</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -10827,17 +10827,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814105853</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>814105853</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -10913,17 +10913,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813352212</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>813352212</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -10999,17 +10999,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813352473</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>813352473</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -11085,17 +11085,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813352481</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>813352481</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -11171,17 +11171,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813352482</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>813352482</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -11257,17 +11257,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813352486</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>813352486</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -11343,17 +11343,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813352494</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>813352494</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -11429,17 +11429,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814105864</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>814105864</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -11515,17 +11515,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813352497</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>813352497</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -11601,17 +11601,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813352774</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>813352774</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813352855</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>813352855</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -11773,17 +11773,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813352873</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>813352873</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -11859,17 +11859,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813353299</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>813353299</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -11945,17 +11945,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813631423</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>813631423</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -12031,17 +12031,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813631424</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>813631424</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -12117,17 +12117,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813631550</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>813631550</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -12203,17 +12203,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813632251</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>813632251</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813632257</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>813632257</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -12375,17 +12375,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813632439</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>813632439</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -12459,17 +12459,17 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr"/>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>FIBERWORK</t>
+        </is>
+      </c>
       <c r="H141" t="inlineStr">
         <is>
           <t>NORMALIZAR RIENDA A PIQUE</t>
@@ -12543,17 +12543,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>813352547</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>813352547</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -12629,17 +12629,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814109709</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>814109709</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -12715,17 +12715,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814109753</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>814109753</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -12801,17 +12801,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814108068</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>814108068</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -12885,17 +12885,17 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr"/>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>FIBERWORK</t>
+        </is>
+      </c>
       <c r="H146" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
@@ -12969,17 +12969,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814108086</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>814108086</t>
+          <t>FIBERWORK</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -13055,15 +13055,19 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>814111727</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>FIBERWORK</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr"/>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>FIBERWORK</t>
+        </is>
+      </c>
       <c r="H148" t="inlineStr">
         <is>
           <t>COLUMNA INCLINADA</t>
@@ -13071,7 +13075,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -13111,6 +13115,522 @@
       <c r="R148" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>-776</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>6/2/2026</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ALSINA, ADOLFO 2457</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>814125554</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>FIBERWORK</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="n">
+        <v>-58.401052</v>
+      </c>
+      <c r="N149" t="n">
+        <v>-34.612103</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>CEN-H</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>-801</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>6/2/2026</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>YRIGOYEN, HIPOLITO 2754</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>814125643</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>FIBERWORK</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" t="n">
+        <v>-58.405116</v>
+      </c>
+      <c r="N150" t="n">
+        <v>-34.611253</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>CEN-H</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>-810</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>6/2/2026</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>MEXICO 2183</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>814125664</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>FIBERWORK</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>1</v>
+      </c>
+      <c r="M151" t="n">
+        <v>-58.397489</v>
+      </c>
+      <c r="N151" t="n">
+        <v>-34.616089</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>CEN-C</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>-818</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>6/2/2026</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>PRINGLES 795</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>814125690</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>FIBERWORK</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>base podrida</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" t="n">
+        <v>-58.427096</v>
+      </c>
+      <c r="N152" t="n">
+        <v>-34.602833</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>CLI-M</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>-820</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>6/2/2026</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>RIOBAMBA 558</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>814125697</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>FIBERWORK</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
+        <v>1</v>
+      </c>
+      <c r="M153" t="n">
+        <v>-58.394106</v>
+      </c>
+      <c r="N153" t="n">
+        <v>-34.602514</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>RET-J</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>ARATO-25058.PO.1RET</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>-828</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>6/2/2026</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>TUCUMAN 2074</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>FIBERWORK</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>1</v>
+      </c>
+      <c r="M154" t="n">
+        <v>-58.396631</v>
+      </c>
+      <c r="N154" t="n">
+        <v>-34.60222</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>RET-J</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>

--- a/mapa_interactivo_Fiberwork.xlsx
+++ b/mapa_interactivo_Fiberwork.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R154"/>
+  <dimension ref="A1:R153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -765,17 +765,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>-105</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6/24/2024</t>
+          <t>1/9/2025</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RINCON /ALT/ 1191</t>
+          <t>PASCO 10</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>789151020</t>
+          <t>802438793</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>recambio de columna podrida en la base</t>
+          <t>PIcada</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -810,26 +810,26 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>-58.395465</v>
+        <v>-58.397512</v>
       </c>
       <c r="N5" t="n">
-        <v>-34.622784</v>
+        <v>-34.609923</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -851,22 +851,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1/9/2025</t>
+          <t>1/16/2025</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PASCO 10</t>
+          <t>BARCO CENTENERA DEL 545</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>802438793</t>
+          <t>802774521</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>PIcada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -896,26 +896,26 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L6" t="n">
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>-58.397512</v>
+        <v>-58.440625</v>
       </c>
       <c r="N6" t="n">
-        <v>-34.609923</v>
+        <v>-34.625499</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>PCH-C</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -937,32 +937,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>-275</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1/16/2025</t>
+          <t>2/3/2025</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BARCO CENTENERA DEL 545</t>
+          <t>DEAN FUNES /ALT/ 481</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>802774521</t>
+          <t>803039902</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t xml:space="preserve">Propia diámetro 114mm </t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -994,14 +994,14 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>-58.440625</v>
+        <v>-58.407076</v>
       </c>
       <c r="N7" t="n">
-        <v>-34.625499</v>
+        <v>-34.616016</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>PCH-C</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1023,17 +1023,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>-275</t>
+          <t>803666441</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2/3/2025</t>
+          <t>2/28/2025</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DEAN FUNES /ALT/ 481</t>
+          <t>Pichincha 1160</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>803039902</t>
+          <t>803666441</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Propia diámetro 114mm </t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1077,17 +1077,17 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-58.407076</v>
+        <v>-58.397946</v>
       </c>
       <c r="N8" t="n">
-        <v>-34.616016</v>
+        <v>-34.622625</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>CEN-N</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1109,22 +1109,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>803666441</t>
+          <t>8849</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2/28/2025</t>
+          <t>3/18/2025</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pichincha 1160</t>
+          <t>Av. Hipólito Yrigoyen 3451</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>803666441</t>
+          <t>804161204</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1163,17 +1163,17 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>-58.397946</v>
+        <v>-58.415566</v>
       </c>
       <c r="N9" t="n">
-        <v>-34.622625</v>
+        <v>-34.613244</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>CEN-N</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1195,7 +1195,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8849</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Av. Hipólito Yrigoyen 3451</t>
+          <t>TREINTA Y TRES ORIENTALES 965</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>804161204</t>
+          <t>804161231</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1252,14 +1252,14 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>-58.415566</v>
+        <v>-58.423042</v>
       </c>
       <c r="N10" t="n">
-        <v>-34.613244</v>
+        <v>-34.625868</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1281,17 +1281,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>804270064</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3/18/2025</t>
+          <t>3/21/2025</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TREINTA Y TRES ORIENTALES 965</t>
+          <t>Colombres 636</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>804161231</t>
+          <t>804270064</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1335,17 +1335,17 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-58.423042</v>
+        <v>-58.418089</v>
       </c>
       <c r="N11" t="n">
-        <v>-34.625868</v>
+        <v>-34.620313</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>ALM-B</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>804270064</t>
+          <t>804270068</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Colombres 636</t>
+          <t>Quito 4292</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>804270064</t>
+          <t>804270068</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1424,10 +1424,10 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-58.418089</v>
+        <v>-58.427201</v>
       </c>
       <c r="N12" t="n">
-        <v>-34.620313</v>
+        <v>-34.617131</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ALM-B</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1453,7 +1453,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>804270068</t>
+          <t>804270074</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Quito 4292</t>
+          <t>Maza 836</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>804270068</t>
+          <t>804270074</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1510,14 +1510,14 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-58.427201</v>
+        <v>-58.414984</v>
       </c>
       <c r="N13" t="n">
-        <v>-34.617131</v>
+        <v>-34.621386</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1539,17 +1539,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>804270074</t>
+          <t>S00431877</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3/21/2025</t>
+          <t>4/8/2025</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Maza 836</t>
+          <t>SARMIENTO 4290</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>804270074</t>
+          <t>804569065</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna corroída en su base entro tambien como caso 7049</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1593,17 +1593,17 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>-58.414984</v>
+        <v>-58.425764</v>
       </c>
       <c r="N14" t="n">
-        <v>-34.621386</v>
+        <v>-34.604359</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>ALM-L</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1625,32 +1625,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S00431877</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4/8/2025</t>
+          <t>4/23/2025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SARMIENTO 4290</t>
+          <t>COCHABAMBA 2207</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>804569065</t>
+          <t>804903806</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Columna corroída en su base entro tambien como caso 7049</t>
+          <t>picada</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1679,17 +1679,17 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-58.425764</v>
+        <v>-58.396135</v>
       </c>
       <c r="N15" t="n">
-        <v>-34.604359</v>
+        <v>-34.624285</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>ALM-L</t>
+          <t>CON-C</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1711,17 +1711,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4/23/2025</t>
+          <t>4/29/2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>COCHABAMBA 2207</t>
+          <t>República Bolivariana de Venezuela 2701</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>804903806</t>
+          <t>805507294</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>picada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1756,26 +1756,26 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>-58.396135</v>
+        <v>-58.404913</v>
       </c>
       <c r="N16" t="n">
-        <v>-34.624285</v>
+        <v>-34.615857</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>CON-C</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1797,17 +1797,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4/29/2025</t>
+          <t>5/1/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>República Bolivariana de Venezuela 2701</t>
+          <t>RIOBAMBA 659</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>805507294</t>
+          <t>805579188</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Pendiente de traspaso nodo entro tambien como 7100</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1847,17 +1847,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L17" t="n">
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>-58.404913</v>
+        <v>-58.394118</v>
       </c>
       <c r="N17" t="n">
-        <v>-34.615857</v>
+        <v>-34.601416</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>RET-H</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1883,17 +1883,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5/1/2025</t>
+          <t>5/19/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RIOBAMBA 659</t>
+          <t>AYACUCHO 267</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>805579188</t>
+          <t>806926385</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pendiente de traspaso nodo entro tambien como 7100</t>
+          <t>Colocar columna y dar aviso para traspaso de nodo teco</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1940,10 +1940,10 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>-58.394118</v>
+        <v>-58.395063</v>
       </c>
       <c r="N18" t="n">
-        <v>-34.601416</v>
+        <v>-34.606257</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>RET-H</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1969,22 +1969,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5/19/2025</t>
+          <t>5/26/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AYACUCHO 267</t>
+          <t>COCHABAMBA 4090</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>806926385</t>
+          <t>806926861</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Colocar columna y dar aviso para traspaso de nodo teco</t>
+          <t>Columna base podrida colocar r400 para pedir traspaso de fuente</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2026,14 +2026,14 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>-58.395063</v>
+        <v>-58.422268</v>
       </c>
       <c r="N19" t="n">
-        <v>-34.606257</v>
+        <v>-34.627754</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2055,17 +2055,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>807187860</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5/26/2025</t>
+          <t>6/4/2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>COCHABAMBA 4090</t>
+          <t>San Juan 3960</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>806926861</t>
+          <t>807187860</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Columna base podrida colocar r400 para pedir traspaso de fuente</t>
+          <t>Colocar columna contactar a Matias Tapia 1171744701 por si hay alguna duda o problema que surja en el momento ya que es para posterior tendido de ftth</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2112,10 +2112,10 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>-58.422268</v>
+        <v>-58.420909</v>
       </c>
       <c r="N20" t="n">
-        <v>-34.627754</v>
+        <v>-34.626221</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>PPT-R</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>807187860</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6/4/2025</t>
+          <t>6/5/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Juan 3960</t>
+          <t>MAZA 181</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>807187860</t>
+          <t>807215439</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Colocar columna contactar a Matias Tapia 1171744701 por si hay alguna duda o problema que surja en el momento ya que es para posterior tendido de ftth</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2198,14 +2198,14 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>-58.420909</v>
+        <v>-58.416477</v>
       </c>
       <c r="N21" t="n">
-        <v>-34.626221</v>
+        <v>-34.61303</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>PPT-R</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MAZA 181</t>
+          <t>ESTADO DE PALESTINA 771</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>807215439</t>
+          <t>807215458</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada y mal ubicada ver con Pedro</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2284,10 +2284,10 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>-58.416477</v>
+        <v>-58.425478</v>
       </c>
       <c r="N22" t="n">
-        <v>-34.61303</v>
+        <v>-34.601865</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2313,22 +2313,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6/5/2025</t>
+          <t>6/9/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 771</t>
+          <t>ALBERTI 191</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>807215458</t>
+          <t>810533286</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Picada y mal ubicada ver con Pedro</t>
+          <t>Desmontar PRFV 400</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2370,10 +2370,10 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-58.425478</v>
+        <v>-58.401624</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.601865</v>
+        <v>-34.612001</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2399,17 +2399,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6/9/2025</t>
+          <t>6/24/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ALBERTI 191</t>
+          <t>MATHEU 727</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>810533286</t>
+          <t>ICD31456940</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2432,11 +2432,7 @@
           <t>FIBERWORK</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Desmontar PRFV 400</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -2444,7 +2440,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Nodo TLC</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2456,10 +2452,10 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.401624</v>
+        <v>-58.400169</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.612001</v>
+        <v>-34.617784</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2473,7 +2469,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>CEN-N</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2485,17 +2481,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6/24/2025</t>
+          <t>6/30/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MATHEU 727</t>
+          <t>CHILE 2561</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2510,7 +2506,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ICD31456940</t>
+          <t>807851584</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2526,7 +2522,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Nodo TLC</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2538,10 +2534,10 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.400169</v>
+        <v>-58.401827</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.617784</v>
+        <v>-34.617667</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2555,7 +2551,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>CEN-N</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2567,17 +2563,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>-510</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6/30/2025</t>
+          <t>7/14/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CHILE 2561</t>
+          <t>Larrea 590</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2587,12 +2583,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>807851584</t>
+          <t>808194254</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2600,7 +2596,11 @@
           <t>FIBERWORK</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Picada</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2620,10 +2620,10 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.401827</v>
+        <v>-58.402353</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.617667</v>
+        <v>-34.602205</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>CLI-E</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2649,7 +2649,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>-510</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Larrea 590</t>
+          <t>CASTELLI 304</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>808194254</t>
+          <t>808194260</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2706,10 +2706,10 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.402353</v>
+        <v>-58.404696</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.602205</v>
+        <v>-34.606337</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>CLI-E</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2735,17 +2735,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7/14/2025</t>
+          <t>7/15/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CASTELLI 304</t>
+          <t>TUCUMAN 3253</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>808194260</t>
+          <t>808373657</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2792,10 +2792,10 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.404696</v>
+        <v>-58.411609</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.606337</v>
+        <v>-34.600329</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CLI-F</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2821,17 +2821,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7/15/2025</t>
+          <t>7/29/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TUCUMAN 3253</t>
+          <t>CALLAO AV. 316</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>808373657</t>
+          <t>808579773</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2878,14 +2878,14 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.411609</v>
+        <v>-58.39231</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.600329</v>
+        <v>-34.605507</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>CLI-F</t>
+          <t>CEN-E</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2907,17 +2907,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7/29/2025</t>
+          <t>8/4/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CALLAO AV. 316</t>
+          <t>MITRE, BARTOLOME 2482</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>808579773</t>
+          <t>808703866</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2964,14 +2964,14 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.39231</v>
+        <v>-58.40161</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.605507</v>
+        <v>-34.608641</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>CEN-E</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2993,32 +2993,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8/4/2025</t>
+          <t>8/12/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MITRE, BARTOLOME 2482</t>
+          <t>MARMOL, JOSE 228</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>808703866</t>
+          <t>808918687</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Se deriva directamente a traspaso de fuente ya que hay una columna existente</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3047,13 +3047,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.40161</v>
+        <v>-58.425858</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.608641</v>
+        <v>-34.61629</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3079,32 +3079,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8/12/2025</t>
+          <t>8/26/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MARMOL, JOSE 228</t>
+          <t>SARANDI 1011</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>808918687</t>
+          <t>809195660</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Se deriva directamente a traspaso de fuente ya que hay una columna existente</t>
+          <t>Picada entro tambien como caso 7209</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3133,17 +3133,17 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.425858</v>
+        <v>-58.394543</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.61629</v>
+        <v>-34.620732</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3165,7 +3165,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SARANDI 1011</t>
+          <t>PRINGLES 788</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>809195660</t>
+          <t>809195664</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Picada entro tambien como caso 7209</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3215,21 +3215,21 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L33" t="n">
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.394543</v>
+        <v>-58.427206</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.620732</v>
+        <v>-34.602914</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3251,17 +3251,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7050</t>
+          <t>-596</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>8/26/2025</t>
+          <t>9/14/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PRINGLES 788</t>
+          <t>Humahuaca 3866</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>809195664</t>
+          <t>809732190</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3301,17 +3301,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L34" t="n">
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.427206</v>
+        <v>-58.418823</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.602914</v>
+        <v>-34.602148</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3337,22 +3337,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>-596</t>
+          <t>-597</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>9/14/2025</t>
+          <t>9/16/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Humahuaca 3866</t>
+          <t>La Rioja 1261</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>809732190</t>
+          <t>809800215</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3394,14 +3394,14 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.418823</v>
+        <v>-58.407029</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.602148</v>
+        <v>-34.62526</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3423,17 +3423,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>-597</t>
+          <t>-603</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/22/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>La Rioja 1261</t>
+          <t>ANCHORENA, TOMAS MANUEL DE, DR. 821</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>809800215</t>
+          <t>809910086</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna chocada pendiente para instalar un corporativo</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3480,14 +3480,14 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.407029</v>
+        <v>-58.408551</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.62526</v>
+        <v>-34.599265</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>CLI-F</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3509,22 +3509,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>-603</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>9/22/2025</t>
+          <t>9/25/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ANCHORENA, TOMAS MANUEL DE, DR. 821</t>
+          <t>MARMOL, JOSE 588</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>809910086</t>
+          <t>809979740</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Columna chocada pendiente para instalar un corporativo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3566,10 +3566,10 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.408551</v>
+        <v>-58.425357</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.599265</v>
+        <v>-34.620223</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>CLI-F</t>
+          <t>ALM-B</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3595,22 +3595,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>-628</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>9/25/2025</t>
+          <t>10/1/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MARMOL, JOSE 588</t>
+          <t>Hipolito Yrigoyen 3250</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>809979740</t>
+          <t>810093628</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3652,10 +3652,10 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.425357</v>
+        <v>-58.412606</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.620223</v>
+        <v>-34.612353</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>ALM-B</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3681,17 +3681,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>-628</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10/1/2025</t>
+          <t>10/6/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hipolito Yrigoyen 3250</t>
+          <t>LARREA 320</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>810093628</t>
+          <t>810244454</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3738,10 +3738,10 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.412606</v>
+        <v>-58.402105</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.612353</v>
+        <v>-34.606071</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3767,7 +3767,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6404</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LARREA 320</t>
+          <t>RINCON 781</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>810244454</t>
+          <t>810244458</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3824,10 +3824,10 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.402105</v>
+        <v>-58.396055</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.606071</v>
+        <v>-34.618126</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3853,17 +3853,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7713</t>
+          <t>-633</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10/6/2025</t>
+          <t>10/8/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>RINCON 781</t>
+          <t>Junin 74</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>810244458</t>
+          <t>ICD31464881</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R400</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3907,13 +3907,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.396055</v>
+        <v>-58.39641</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.618126</v>
+        <v>-34.608561</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>CLI-C</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3939,22 +3939,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>-633</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10/8/2025</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Junin 74</t>
+          <t>SAN JUAN AV. 4256</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ICD31464881</t>
+          <t>810394752</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Colocar R400</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3993,17 +3993,17 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.39641</v>
+        <v>-58.424867</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.608561</v>
+        <v>-34.626806</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>CLI-C</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4025,17 +4025,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>10/20/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 4256</t>
+          <t>CORRIENTES AV. 4515</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>810394752</t>
+          <t>810398934</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4082,14 +4082,14 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.424867</v>
+        <v>-58.428907</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.626806</v>
+        <v>-34.602301</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4111,17 +4111,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10/20/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CORRIENTES AV. 4515</t>
+          <t>SANCHEZ DE LORIA 1923</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>810398934</t>
+          <t>810416656</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>cambiar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4168,14 +4168,14 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.428907</v>
+        <v>-58.411426</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.602301</v>
+        <v>-34.633266</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4197,17 +4197,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1923</t>
+          <t>CALVO, CARLOS 3762</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>810416656</t>
+          <t>810451584</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4254,14 +4254,14 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.411426</v>
+        <v>-58.418542</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.633266</v>
+        <v>-34.624609</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4283,22 +4283,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3762</t>
+          <t>ALSINA, ADOLFO 2499</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>810451584</t>
+          <t>810487023</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4340,14 +4340,14 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.418542</v>
+        <v>-58.40129</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.624609</v>
+        <v>-34.612123</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4369,7 +4369,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ALSINA, ADOLFO 2499</t>
+          <t>LINIERS VIRREY 1142</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>810487023</t>
+          <t>810487035</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4426,14 +4426,14 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.40129</v>
+        <v>-58.413563</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.612123</v>
+        <v>-34.624645</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4455,17 +4455,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1142</t>
+          <t>SAN JUAN AV. 3741</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>810487035</t>
+          <t>810712796</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4512,10 +4512,10 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.413563</v>
+        <v>-58.418108</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.624645</v>
+        <v>-34.62564</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4541,22 +4541,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/17/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 3741</t>
+          <t>Paso 280</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>810712796</t>
+          <t>810787612</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>base picada</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4598,14 +4598,14 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.418108</v>
+        <v>-58.403566</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.62564</v>
+        <v>-34.606691</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4627,22 +4627,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>11/14/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Paso 280</t>
+          <t>DIAZ VELEZ AV. 3485</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>810787612</t>
+          <t>810787513</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>base picada</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4684,10 +4684,10 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.403566</v>
+        <v>-58.415838</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.606691</v>
+        <v>-34.608469</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CLI-J</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4713,17 +4713,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>S00110420</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11/14/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV. 3485</t>
+          <t>YATAY 760</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>810787513</t>
+          <t>810804303</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4770,10 +4770,10 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.415838</v>
+        <v>-58.428752</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.608469</v>
+        <v>-34.603273</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>CLI-J</t>
+          <t>ALM-M</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4799,17 +4799,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S00110420</t>
+          <t>S00921590</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>YATAY 760</t>
+          <t>CASEROS AV. 3621</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>810804303</t>
+          <t>810804462</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4856,14 +4856,14 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.428752</v>
+        <v>-58.416134</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.603273</v>
+        <v>-34.638879</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>ALM-M</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4885,7 +4885,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S00921590</t>
+          <t>S00921597</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CASEROS AV. 3621</t>
+          <t>CASEROS AV. 3507</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>810804462</t>
+          <t>810804451</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4942,10 +4942,10 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.416134</v>
+        <v>-58.414769</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.638879</v>
+        <v>-34.638638</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S00921597</t>
+          <t>S00921602</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CASEROS AV. 3507</t>
+          <t>CASEROS AV. 3411</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>810804451</t>
+          <t>810804383</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo TLC</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5028,10 +5028,10 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.414769</v>
+        <v>-58.413499</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.638638</v>
+        <v>-34.638416</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S00921602</t>
+          <t>S00942399</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CASEROS AV. 3411</t>
+          <t>ESTADOS UNIDOS 4030</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>810804383</t>
+          <t xml:space="preserve">01503983 </t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>base corroida Colocar PRFV 400</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Nodo TLC</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5114,14 +5114,14 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.413499</v>
+        <v>-58.422536</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.638416</v>
+        <v>-34.623094</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5143,7 +5143,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S00942399</t>
+          <t>01110546</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ESTADOS UNIDOS 4030</t>
+          <t>ALSINA, ADOLFO 2490</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">01503983 </t>
+          <t>810804369</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>base corroida Colocar PRFV 400</t>
+          <t>columna inclinada  base corroida</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5200,14 +5200,14 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.422536</v>
+        <v>-58.401266</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.623094</v>
+        <v>-34.612194</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5229,17 +5229,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>01110546</t>
+          <t>7874</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ALSINA, ADOLFO 2490</t>
+          <t>SAN LUIS 2488</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>810804369</t>
+          <t>810820592</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>columna inclinada  base corroida</t>
+          <t>base muy picada</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5286,10 +5286,10 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.401266</v>
+        <v>-58.402179</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.612194</v>
+        <v>-34.600152</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>CLI-E</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5315,17 +5315,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>-687</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SAN LUIS 2488</t>
+          <t>Junin 722</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>810820592</t>
+          <t>810862729</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>base muy picada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5372,10 +5372,10 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.402179</v>
+        <v>-58.397171</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.600152</v>
+        <v>-34.600729</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -5389,34 +5389,34 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>CLI-E</t>
+          <t>RET-J</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>-687</t>
+          <t>900008882010</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Junin 722</t>
+          <t xml:space="preserve"> PAVON AV. 3707 </t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>810862729</t>
+          <t>810984598</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5458,14 +5458,14 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.397171</v>
+        <v>-58.416724</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.600729</v>
+        <v>-34.630181</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5475,29 +5475,29 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>RET-J</t>
+          <t>PPT-R</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>900008882010</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PAVON AV. 3707 </t>
+          <t>Querandíes 4220</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>810984598</t>
+          <t>810984700</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>correr, obstaculiza acceso a garage</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5537,21 +5537,21 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L60" t="n">
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.416724</v>
+        <v>-58.426168</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.630181</v>
+        <v>-34.611095</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>PPT-R</t>
+          <t>ALM-E</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5573,22 +5573,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Querandíes 4220</t>
+          <t xml:space="preserve">URQUIZA, GRAL. 779 </t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>810984700</t>
+          <t>811198737</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>correr, obstaculiza acceso a garage</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5623,17 +5623,17 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L61" t="n">
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.426168</v>
+        <v>-58.409318</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.611095</v>
+        <v>-34.619842</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>ALM-E</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5659,7 +5659,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">URQUIZA, GRAL. 779 </t>
+          <t xml:space="preserve">HUMAHUACA 4298 </t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>811198737</t>
+          <t>811198696</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5716,10 +5716,10 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.409318</v>
+        <v>-58.425302</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.619842</v>
+        <v>-34.601502</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5745,17 +5745,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>S01199412</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUMAHUACA 4298 </t>
+          <t>ACUÑA DE FIGUEROA, FRANCISCO 1028</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>811198696</t>
+          <t>811198676</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5802,10 +5802,10 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.425302</v>
+        <v>-58.422033</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.601502</v>
+        <v>-34.598976</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>CLI-L</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5831,22 +5831,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S01199412</t>
+          <t>-705</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/22/2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ACUÑA DE FIGUEROA, FRANCISCO 1028</t>
+          <t>Larrea 370</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>811198676</t>
+          <t>02013924</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -5888,10 +5888,10 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.422033</v>
+        <v>-58.402154</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.598976</v>
+        <v>-34.605295</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>CLI-L</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5917,22 +5917,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>-705</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12/22/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Larrea 370</t>
+          <t>BRAVO, MARIO 478</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>02013924</t>
+          <t>811299416</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -5974,10 +5974,10 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.402154</v>
+        <v>-58.416901</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.605295</v>
+        <v>-34.604236</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6003,17 +6003,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>-711</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BRAVO, MARIO 478</t>
+          <t>México 3306</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>811299416</t>
+          <t>811299443</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -6060,10 +6060,10 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.416901</v>
+        <v>-58.412865</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.604236</v>
+        <v>-34.619484</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6089,17 +6089,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>-711</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>México 3306</t>
+          <t>LAMBARE 864</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>811299443</t>
+          <t>811453866</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6146,10 +6146,10 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.412865</v>
+        <v>-58.430579</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.619484</v>
+        <v>-34.604908</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>ALM-M</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6175,17 +6175,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>S00941232</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LAMBARE 864</t>
+          <t>TARIJA 3323</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6195,12 +6195,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>811453866</t>
+          <t>811453904</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6232,14 +6232,14 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.430579</v>
+        <v>-58.412204</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.604908</v>
+        <v>-34.628609</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>ALM-M</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6261,22 +6261,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S00941232</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TARIJA 3323</t>
+          <t>Catamarca 236</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>811453904</t>
+          <t xml:space="preserve">02511385 </t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6318,14 +6318,14 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.412204</v>
+        <v>-58.406807</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.628609</v>
+        <v>-34.612902</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6347,7 +6347,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>8124</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6357,12 +6357,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Catamarca 236</t>
+          <t xml:space="preserve"> DIAZ VELEZ AV. 4421</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">02511385 </t>
+          <t>811454440</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6404,10 +6404,10 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.406807</v>
+        <v>-58.429481</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.612902</v>
+        <v>-34.608647</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>ALM-K</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6433,22 +6433,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>S01432754</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/16/2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DIAZ VELEZ AV. 4421</t>
+          <t>MISIONES 242</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>811454440</t>
+          <t>811454538</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6490,10 +6490,10 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.429481</v>
+        <v>-58.404243</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.608647</v>
+        <v>-34.612859</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>ALM-K</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6519,7 +6519,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S01432754</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MISIONES 242</t>
+          <t>Castelli 60</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6539,12 +6539,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>811454538</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6554,32 +6554,20 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>corroida</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+          <t>traspaso propio tlc coloco columna</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="n">
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.404243</v>
+        <v>-58.404691</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.612859</v>
+        <v>-34.609194</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -6593,7 +6581,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6605,17 +6593,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>S01408162</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1/16/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Castelli 60</t>
+          <t xml:space="preserve">GARAY, JUAN DE AV. 2871 </t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6625,12 +6613,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812439895</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6640,24 +6628,36 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>traspaso propio tlc coloco columna</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
       <c r="L73" t="n">
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.404691</v>
+        <v>-58.4048</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.609194</v>
+        <v>-34.629021</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6679,17 +6679,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S01408162</t>
+          <t>S00034481</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARAY, JUAN DE AV. 2871 </t>
+          <t xml:space="preserve">MITRE, BARTOLOME 2294 </t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>812439895</t>
+          <t>811626888</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -6736,14 +6736,14 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.4048</v>
+        <v>-58.399059</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.629021</v>
+        <v>-34.608499</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>CLI-C</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6765,17 +6765,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S00034481</t>
+          <t>S01314715</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">MITRE, BARTOLOME 2294 </t>
+          <t xml:space="preserve"> CATAMARCA 919</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>811626888</t>
+          <t>811626986</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Corroida</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6822,14 +6822,14 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.399059</v>
+        <v>-58.404766</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.608499</v>
+        <v>-34.620521</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>CLI-C</t>
+          <t>CEN-K</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6851,7 +6851,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S01314715</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6861,12 +6861,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CATAMARCA 919</t>
+          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>811626986</t>
+          <t>811626981</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6908,14 +6908,14 @@
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.404766</v>
+        <v>-58.423058</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.620521</v>
+        <v>-34.608916</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>CEN-K</t>
+          <t>ALM-E</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6937,22 +6937,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>8125</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
+          <t>COMBATE DE LOS POZOS 1103</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>811626981</t>
+          <t>811627014</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6994,14 +6994,14 @@
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.423058</v>
+        <v>-58.393145</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.608916</v>
+        <v>-34.621778</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>ALM-E</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7023,17 +7023,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>S00022862</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>COMBATE DE LOS POZOS 1103</t>
+          <t>YRIGOYEN, HIPOLITO 2395</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>811627014</t>
+          <t>811627077</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7080,14 +7080,14 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.393145</v>
+        <v>-58.400243</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.621778</v>
+        <v>-34.610864</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7109,7 +7109,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S00022862</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO 2395</t>
+          <t>PICHINCHA 89</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>811627077</t>
+          <t>811627062</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7166,10 +7166,10 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.400243</v>
+        <v>-58.399124</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.610864</v>
+        <v>-34.610705</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -7195,22 +7195,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/6/2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PICHINCHA 89</t>
+          <t>GALLO 77</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>811627062</t>
+          <t>811627128</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>tensor roto inclinada</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7245,17 +7245,17 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L80" t="n">
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.399124</v>
+        <v>-58.413979</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.610705</v>
+        <v>-34.607475</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7281,22 +7281,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>8296</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2/6/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GALLO 77</t>
+          <t>RINCON 1109</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>811627128</t>
+          <t>812439968</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>tensor roto inclinada</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7331,21 +7331,21 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L81" t="n">
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.413979</v>
+        <v>-58.395668</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.607475</v>
+        <v>-34.621926</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>CEN-N</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7367,17 +7367,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>8329</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>RINCON 1109</t>
+          <t xml:space="preserve">ALBERTI 1055 </t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>812439968</t>
+          <t>812440156</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7424,10 +7424,10 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.395668</v>
+        <v>-58.400774</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.621926</v>
+        <v>-34.621503</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -7453,17 +7453,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>S00136365</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALBERTI 1055 </t>
+          <t>PERON, JUAN DOMINGO, TTE. GENERAL 2697</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>812440156</t>
+          <t>812440173</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7510,14 +7510,14 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.400774</v>
+        <v>-58.404576</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.621503</v>
+        <v>-34.607569</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>CEN-N</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -7539,7 +7539,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S00136365</t>
+          <t>S00144805</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PERON, JUAN DOMINGO, TTE. GENERAL 2697</t>
+          <t>VIAMONTE 1990</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>812440173</t>
+          <t>812440165</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -7596,10 +7596,10 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.404576</v>
+        <v>-58.395384</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.607569</v>
+        <v>-34.600962</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -7613,29 +7613,29 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>RET-J</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S00144805</t>
+          <t>-749</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>VIAMONTE 1990</t>
+          <t>Moreno 2965</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>812440165</t>
+          <t>812440614</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7682,10 +7682,10 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.395384</v>
+        <v>-58.407758</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.600962</v>
+        <v>-34.613793</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -7699,19 +7699,19 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>RET-J</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>-749</t>
+          <t>-760</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Moreno 2965</t>
+          <t>MAZA 1615</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>812440614</t>
+          <t>812440354</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>base corroida e inclinada</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7768,14 +7768,14 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.407758</v>
+        <v>-58.414586</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.613793</v>
+        <v>-34.630095</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7797,7 +7797,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>-760</t>
+          <t>S00519068</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MAZA 1615</t>
+          <t>CALVO, CARLOS 3747</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>812440354</t>
+          <t>812440282</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>base corroida e inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7854,10 +7854,10 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.414586</v>
+        <v>-58.41859</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.630095</v>
+        <v>-34.624508</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7883,17 +7883,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S00519068</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/27/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3747</t>
+          <t xml:space="preserve">BRAVO, MARIO 836 </t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>812440282</t>
+          <t>812503638</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -7940,14 +7940,14 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.41859</v>
+        <v>-58.416187</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.624508</v>
+        <v>-34.600138</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CLI-G</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7969,17 +7969,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>S00100362</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2/27/2026</t>
+          <t>3/4/2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRAVO, MARIO 836 </t>
+          <t>RIO DE JANEIRO 901</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>812503638</t>
+          <t>814105603</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8026,10 +8026,10 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.416187</v>
+        <v>-58.431406</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.600138</v>
+        <v>-34.605009</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>CLI-G</t>
+          <t>ALM-M</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8055,17 +8055,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S00100362</t>
+          <t>-774</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>3/4/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO 901</t>
+          <t>CASEROS AV. 4131</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>814105603</t>
+          <t>814107131</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>mover a 4111</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8112,14 +8112,14 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.431406</v>
+        <v>-58.422741</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.605009</v>
+        <v>-34.639999</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>ALM-M</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8141,17 +8141,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>-774</t>
+          <t>00050599</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CASEROS AV. 4131</t>
+          <t xml:space="preserve">BELGRANO AV 3689 </t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>814107131</t>
+          <t>812879940</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>mover a 4111</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8198,14 +8198,14 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.422741</v>
+        <v>-58.418254</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.639999</v>
+        <v>-34.615692</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8227,7 +8227,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>00050599</t>
+          <t>00223191</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8237,12 +8237,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">BELGRANO AV 3689 </t>
+          <t>CATAMARCA 254</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>812879940</t>
+          <t>812879982</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -8284,10 +8284,10 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.418254</v>
+        <v>-58.406734</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.615692</v>
+        <v>-34.613107</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8313,7 +8313,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>00223191</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CATAMARCA 254</t>
+          <t>CORRIENTES AV 4073</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>812879982</t>
+          <t>812880406</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -8370,10 +8370,10 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.406734</v>
+        <v>-58.422076</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.613107</v>
+        <v>-34.60298</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8399,7 +8399,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>00223023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8409,12 +8409,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CORRIENTES AV 4073</t>
+          <t>SAN JUAN AV. 2201</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>812880406</t>
+          <t>814109847</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -8456,14 +8456,14 @@
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.422076</v>
+        <v>-58.396491</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.60298</v>
+        <v>-34.622986</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8485,22 +8485,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>00223023</t>
+          <t>00317296</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/23/2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 2201</t>
+          <t>AGRELO 3620</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>814109847</t>
+          <t>812880625</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -8542,14 +8542,14 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.396491</v>
+        <v>-58.417002</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.622986</v>
+        <v>-34.618613</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>ALM-B</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8571,7 +8571,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>00317296</t>
+          <t>00322642</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AGRELO 3620</t>
+          <t>ESTADO DE PALESTINA 727</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>812880625</t>
+          <t>812880655</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -8628,10 +8628,10 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.417002</v>
+        <v>-58.425539</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.618613</v>
+        <v>-34.602286</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>ALM-B</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8657,7 +8657,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>00322642</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 727</t>
+          <t>MEXICO 3306</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>812880655</t>
+          <t>812880662</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -8714,10 +8714,10 @@
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.425539</v>
+        <v>-58.412865</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.602286</v>
+        <v>-34.619484</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8743,7 +8743,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>8265</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MEXICO 3306</t>
+          <t>HUMBERTO 1 1999</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>812880662</t>
+          <t>812880685</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -8800,14 +8800,14 @@
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.412865</v>
+        <v>-58.394304</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.619484</v>
+        <v>-34.621645</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8829,17 +8829,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3/23/2026</t>
+          <t>3/28/2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>HUMBERTO 1 1999</t>
+          <t>RIVADAVIA AV 1985</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>812880685</t>
+          <t>812880736</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -8864,12 +8864,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>APLOMAR COLUMNA</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -8886,14 +8886,14 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.394304</v>
+        <v>-58.394609</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.621645</v>
+        <v>-34.609304</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8915,22 +8915,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>M881</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>3/28/2026</t>
+          <t>4/1/2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>RIVADAVIA AV 1985</t>
+          <t>AV LA PLATA 2288</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>812880736</t>
+          <t>813046342</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -8950,17 +8950,17 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>APLOMAR COLUMNA</t>
+          <t>DESMONTAR COLUMNA Y  DESPLAZAR PCALOGERO</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -8972,14 +8972,14 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.394609</v>
+        <v>-58.423203</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.609304</v>
+        <v>-34.640909</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9001,22 +9001,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>M881</t>
+          <t>8802</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>4/1/2026</t>
+          <t>4/11/2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AV LA PLATA 2288</t>
+          <t>RINCON 731</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>813046342</t>
+          <t>813046658</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>DESMONTAR COLUMNA Y  DESPLAZAR PCALOGERO</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9058,14 +9058,14 @@
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.423203</v>
+        <v>-58.396088</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.640909</v>
+        <v>-34.617527</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9087,7 +9087,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>8802</t>
+          <t>S00374917</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>RINCON 731</t>
+          <t>24 DE NOVIEMBRE 695</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>813046658</t>
+          <t>813046791</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -9144,10 +9144,10 @@
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.396088</v>
+        <v>-58.411053</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.617527</v>
+        <v>-34.618979</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9173,7 +9173,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S00374917</t>
+          <t>S00379764</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>24 DE NOVIEMBRE 695</t>
+          <t>JAURES JEAN 491</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>813046791</t>
+          <t>813046795</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -9230,10 +9230,10 @@
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.411053</v>
+        <v>-58.408934</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.618979</v>
+        <v>-34.604273</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>CLI-H</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9259,7 +9259,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S00379764</t>
+          <t>S00379996</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>JAURES JEAN 491</t>
+          <t>SARANDI 1439</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>813046795</t>
+          <t>813046806</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -9316,14 +9316,14 @@
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.408934</v>
+        <v>-58.393455</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.604273</v>
+        <v>-34.625779</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>CLI-H</t>
+          <t>CON-C</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9345,7 +9345,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S00379996</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SARANDI 1439</t>
+          <t>SARMIENTO 2108</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>813046806</t>
+          <t>813046819</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -9402,14 +9402,14 @@
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.393455</v>
+        <v>-58.39675</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.625779</v>
+        <v>-34.605996</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -9419,7 +9419,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>CON-C</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9431,7 +9431,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SARMIENTO 2108</t>
+          <t>SANCHEZ DE BUSTAMANTE 633</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>813046819</t>
+          <t>813046866</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -9488,10 +9488,10 @@
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.39675</v>
+        <v>-58.414203</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.605996</v>
+        <v>-34.602602</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>CLI-G</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9517,7 +9517,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SANCHEZ DE BUSTAMANTE 633</t>
+          <t>RIVADAVIA AV 4245</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>813046866</t>
+          <t>813046970</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -9574,10 +9574,10 @@
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.414203</v>
+        <v>-58.425567</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.602602</v>
+        <v>-34.613382</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>CLI-G</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9603,7 +9603,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>RIVADAVIA AV 4245</t>
+          <t>DIAZ VELEZ AV 4449</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>813046970</t>
+          <t>813046971</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -9660,10 +9660,10 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.425567</v>
+        <v>-58.429714</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.613382</v>
+        <v>-34.608645</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>ALM-K</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9689,7 +9689,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV 4449</t>
+          <t>LAS CASAS 3989</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>813046971</t>
+          <t>813046994</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -9746,14 +9746,14 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.429714</v>
+        <v>-58.421676</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.608645</v>
+        <v>-34.635878</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>ALM-K</t>
+          <t>PPT-R</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9775,7 +9775,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>8851</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>LAS CASAS 3989</t>
+          <t>SALCEDO 3541</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>813046994</t>
+          <t>813047007</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -9832,10 +9832,10 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.421676</v>
+        <v>-58.415121</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.635878</v>
+        <v>-34.633772</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>PPT-R</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9861,7 +9861,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>8852</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SALCEDO 3541</t>
+          <t>TARIJA 4079</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>813047007</t>
+          <t>813047012</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -9918,10 +9918,10 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.415121</v>
+        <v>-58.421804</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.633772</v>
+        <v>-34.629558</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>PPT-R</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9947,7 +9947,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>8853</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TARIJA 4079</t>
+          <t>TIMBUES 2086</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>813047012</t>
+          <t>813047017</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -10004,10 +10004,10 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.421804</v>
+        <v>-58.421835</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.629558</v>
+        <v>-34.63863</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>PPT-R</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10033,7 +10033,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>8855</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TIMBUES 2086</t>
+          <t>GOMEZ VALENTIN 3684</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>813047017</t>
+          <t>813047019</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -10090,14 +10090,14 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.421835</v>
+        <v>-58.416726</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.63863</v>
+        <v>-34.604773</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10119,7 +10119,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>S00390896</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>GOMEZ VALENTIN 3684</t>
+          <t>AV INDEPENDENCIA 2018</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10144,7 +10144,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>813047019</t>
+          <t>813047657</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -10176,10 +10176,10 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.416726</v>
+        <v>-58.39469</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.604773</v>
+        <v>-34.618394</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10205,22 +10205,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S00390896</t>
+          <t>RB00001</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>AV INDEPENDENCIA 2018</t>
+          <t>BELGRANO AV. 3715</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>813047657</t>
+          <t>813304903</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -10262,10 +10262,10 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.39469</v>
+        <v>-58.418851</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.618394</v>
+        <v>-34.615716</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10291,7 +10291,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>RB00001</t>
+          <t>AM00039</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BELGRANO AV. 3715</t>
+          <t>CASTRO BARROS 852</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>813304903</t>
+          <t>813304915</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -10348,14 +10348,14 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.418851</v>
+        <v>-58.419281</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.615716</v>
+        <v>-34.62215</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10377,7 +10377,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AM00039</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10387,12 +10387,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CASTRO BARROS 852</t>
+          <t>ALSINA, ADOLFO 3293</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>813304915</t>
+          <t>813350607</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -10434,14 +10434,14 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.419281</v>
+        <v>-58.412936</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.62215</v>
+        <v>-34.613332</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10463,7 +10463,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>S00423738</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ALSINA, ADOLFO 3293</t>
+          <t>CATAMARCA 568</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>813350607</t>
+          <t>813350620</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -10520,10 +10520,10 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.412936</v>
+        <v>-58.405541</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.613332</v>
+        <v>-34.616959</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10549,22 +10549,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S00423738</t>
+          <t>S00299569</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/21/2026</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CATAMARCA 568</t>
+          <t>YRIGOYEN, HIPOLITO AV. 4156</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>813350620</t>
+          <t>813350953</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -10606,10 +10606,10 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.405541</v>
+        <v>-58.425213</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.616959</v>
+        <v>-34.614924</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10635,7 +10635,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S00299569</t>
+          <t>S004318770</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO AV. 4156</t>
+          <t>SARMIENTO 4290</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>813350953</t>
+          <t>813351576</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -10692,10 +10692,10 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.425213</v>
+        <v>-58.425764</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.614924</v>
+        <v>-34.604359</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>ALM-L</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10721,7 +10721,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S004318770</t>
+          <t>S00431893</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SARMIENTO 4290</t>
+          <t>MUÑIZ 1151</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>813351576</t>
+          <t>814105853</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -10778,14 +10778,14 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.425764</v>
+        <v>-58.425442</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.604359</v>
+        <v>-34.627634</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -10795,7 +10795,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>ALM-L</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10807,7 +10807,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S00431893</t>
+          <t>S00434849</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MUÑIZ 1151</t>
+          <t>YRIGOYEN, HIPOLITO AV. 3484</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>814105853</t>
+          <t>813352212</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -10864,14 +10864,14 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.425442</v>
+        <v>-58.416028</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.627634</v>
+        <v>-34.613538</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10893,7 +10893,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S00434849</t>
+          <t xml:space="preserve">9009 </t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO AV. 3484</t>
+          <t>SANCHEZ DE LORIA 1913</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>813352212</t>
+          <t>813352473</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -10950,14 +10950,14 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.416028</v>
+        <v>-58.411474</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.613538</v>
+        <v>-34.633143</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10979,7 +10979,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9009 </t>
+          <t xml:space="preserve">9011 </t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1913</t>
+          <t>SANCHEZ DE LORIA 1583</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>813352473</t>
+          <t>813352481</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -11036,14 +11036,14 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.411474</v>
+        <v>-58.411926</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.633143</v>
+        <v>-34.628861</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11065,7 +11065,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9011 </t>
+          <t xml:space="preserve">9012 </t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1583</t>
+          <t xml:space="preserve">LINIERS VIRREY 2315 </t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>813352481</t>
+          <t>813352482</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -11122,14 +11122,14 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.411926</v>
+        <v>-58.41191</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.628861</v>
+        <v>-34.637333</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11151,7 +11151,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9012 </t>
+          <t xml:space="preserve">9014 </t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINIERS VIRREY 2315 </t>
+          <t>LINIERS VIRREY 896</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>813352482</t>
+          <t>813352486</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -11208,14 +11208,14 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.41191</v>
+        <v>-58.413645</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.637333</v>
+        <v>-34.621935</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -11225,7 +11225,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11237,7 +11237,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9014 </t>
+          <t xml:space="preserve">9016 </t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 896</t>
+          <t>HUMBERTO 1° 3368</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>813352486</t>
+          <t>813352494</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -11294,10 +11294,10 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.413645</v>
+        <v>-58.413189</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.621935</v>
+        <v>-34.624187</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9016 </t>
+          <t xml:space="preserve">9017 </t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>HUMBERTO 1° 3368</t>
+          <t>MUÑIZ 1237</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>813352494</t>
+          <t>814105864</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -11380,10 +11380,10 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.413189</v>
+        <v>-58.425206</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.624187</v>
+        <v>-34.628705</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11409,7 +11409,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9017 </t>
+          <t xml:space="preserve">9020 </t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MUÑIZ 1237</t>
+          <t>TARIJA 3497</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>814105864</t>
+          <t>813352497</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -11466,10 +11466,10 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.425206</v>
+        <v>-58.414424</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.628705</v>
+        <v>-34.628778</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11495,17 +11495,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">9020 </t>
+          <t>9028</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>4/21/2026</t>
+          <t>4/24/2026</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>TARIJA 3497</t>
+          <t>BRAVO, MARIO 740</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>813352497</t>
+          <t>813352774</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -11552,14 +11552,14 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.414424</v>
+        <v>-58.416308</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.628778</v>
+        <v>-34.601047</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>CLI-G</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11581,7 +11581,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t>S00413025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11591,12 +11591,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>BRAVO, MARIO 740</t>
+          <t>CHILE 2550</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>813352774</t>
+          <t>813352855</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -11638,10 +11638,10 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.416308</v>
+        <v>-58.40174</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.601047</v>
+        <v>-34.617754</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>CLI-G</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11667,7 +11667,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S00413025</t>
+          <t>S00429731</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CHILE 2550</t>
+          <t xml:space="preserve">ALSINA, ADOLFO 2291 </t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>813352855</t>
+          <t>813352873</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -11724,10 +11724,10 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.40174</v>
+        <v>-58.398771</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.617754</v>
+        <v>-34.611932</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11753,22 +11753,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S00429731</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/29/2026</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALSINA, ADOLFO 2291 </t>
+          <t xml:space="preserve">GALLEGOS 3443 </t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>813352873</t>
+          <t>813353299</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -11810,14 +11810,14 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.398771</v>
+        <v>-58.413647</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.611932</v>
+        <v>-34.631434</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11839,17 +11839,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t xml:space="preserve">9045 </t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>4/29/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALLEGOS 3443 </t>
+          <t>LINIERS VIRREY 1793</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>813353299</t>
+          <t>813631423</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -11896,14 +11896,14 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.413647</v>
+        <v>-58.413025</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.631434</v>
+        <v>-34.631929</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11925,7 +11925,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">9045 </t>
+          <t>9049</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1793</t>
+          <t>BATHURST 3377</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11950,7 +11950,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>813631423</t>
+          <t>813631424</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -11982,10 +11982,10 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.413025</v>
+        <v>-58.411896</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.631929</v>
+        <v>-34.636028</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -12011,22 +12011,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>S00215089</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>BATHURST 3377</t>
+          <t>LARREA 122</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>813631424</t>
+          <t>813631550</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -12068,14 +12068,14 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.411896</v>
+        <v>-58.401972</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.636028</v>
+        <v>-34.608317</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -12085,7 +12085,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12097,7 +12097,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S00215089</t>
+          <t>S00401648</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>LARREA 122</t>
+          <t>JUNIN 312</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -12122,7 +12122,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>813631550</t>
+          <t>813632251</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -12154,10 +12154,10 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.401972</v>
+        <v>-58.396676</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.608317</v>
+        <v>-34.605753</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12183,7 +12183,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S00401648</t>
+          <t>S00465940</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>JUNIN 312</t>
+          <t>BELGRANO AV. 3669</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12208,7 +12208,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>813632251</t>
+          <t>813632257</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -12240,10 +12240,10 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.396676</v>
+        <v>-58.417949</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.605753</v>
+        <v>-34.615674</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12269,7 +12269,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S00465940</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12279,12 +12279,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>BELGRANO AV. 3669</t>
+          <t>JAURES, JEAN 309</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>813632257</t>
+          <t>813632439</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -12326,10 +12326,10 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.417949</v>
+        <v>-58.409868</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.615674</v>
+        <v>-34.606562</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>CLI-H</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12355,22 +12355,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>S00364775</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>JAURES, JEAN 309</t>
+          <t>CASTRO 511</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12378,11 +12378,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>813632439</t>
-        </is>
-      </c>
+      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
           <t>FIBERWORK</t>
@@ -12390,12 +12386,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>NORMALIZAR RIENDA A PIQUE</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Tensor</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -12405,17 +12401,17 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.409868</v>
+        <v>-58.420597</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.606562</v>
+        <v>-34.617818</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -12429,7 +12425,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>CLI-H</t>
+          <t>ALM-B</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12441,7 +12437,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S00364775</t>
+          <t>S00493114</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12451,12 +12447,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CASTRO 511</t>
+          <t>ARENALES 3648</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12464,7 +12460,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>813352547</t>
+        </is>
+      </c>
       <c r="G141" t="inlineStr">
         <is>
           <t>FIBERWORK</t>
@@ -12472,36 +12472,36 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>NORMALIZAR RIENDA A PIQUE</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Tensor</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L141" t="n">
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.420597</v>
+        <v>-58.413656</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.617818</v>
+        <v>-34.585464</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>ALM-B</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12523,7 +12523,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S00493114</t>
+          <t xml:space="preserve">7880 </t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ARENALES 3648</t>
+          <t>MUÑIZ 16</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>813352547</t>
+          <t>814109709</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -12568,7 +12568,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -12580,14 +12580,14 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.413656</v>
+        <v>-58.427498</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.585464</v>
+        <v>-34.614599</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12609,7 +12609,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">7880 </t>
+          <t xml:space="preserve">9923 </t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>MUÑIZ 16</t>
+          <t>PRINGLES 1094</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -12634,7 +12634,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>814109709</t>
+          <t>814109753</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -12666,10 +12666,10 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.427498</v>
+        <v>-58.426722</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.614599</v>
+        <v>-34.599427</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12695,17 +12695,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9923 </t>
+          <t xml:space="preserve">9019 </t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>PRINGLES 1094</t>
+          <t>CASTRO BARROS AV. 338</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -12720,7 +12720,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>814109753</t>
+          <t>814108068</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -12752,10 +12752,10 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.426722</v>
+        <v>-58.419864</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.599427</v>
+        <v>-34.616375</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12781,7 +12781,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9019 </t>
+          <t xml:space="preserve">9031 </t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12791,12 +12791,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CASTRO BARROS AV. 338</t>
+          <t>YRIGOYEN, HIPOLITO 1938</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12804,11 +12804,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>814108068</t>
-        </is>
-      </c>
+      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
           <t>FIBERWORK</t>
@@ -12826,7 +12822,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -12838,10 +12834,10 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.419864</v>
+        <v>-58.394079</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.616375</v>
+        <v>-34.61051</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -12855,7 +12851,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12867,7 +12863,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">9031 </t>
+          <t xml:space="preserve">9088 </t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12877,12 +12873,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO 1938</t>
+          <t>HUMAHUACA 4296</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -12890,7 +12886,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>814108086</t>
+        </is>
+      </c>
       <c r="G146" t="inlineStr">
         <is>
           <t>FIBERWORK</t>
@@ -12908,7 +12908,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -12920,10 +12920,10 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.394079</v>
+        <v>-58.425282</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.61051</v>
+        <v>-34.601504</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12949,7 +12949,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">9088 </t>
+          <t xml:space="preserve">10059 </t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12959,12 +12959,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>HUMAHUACA 4296</t>
+          <t xml:space="preserve">SALGUERO, JERONIMO 2296 </t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>814108086</t>
+          <t>814111727</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -13006,14 +13006,14 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.425282</v>
+        <v>-58.411132</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.601504</v>
+        <v>-34.585267</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>AGU-K</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -13035,17 +13035,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">10059 </t>
+          <t>-776</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>6/2/2026</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALGUERO, JERONIMO 2296 </t>
+          <t>ALSINA, ADOLFO 2457</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>814111727</t>
+          <t>814125554</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -13092,14 +13092,14 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.411132</v>
+        <v>-58.401052</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.585267</v>
+        <v>-34.612103</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>AGU-K</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13121,7 +13121,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>-776</t>
+          <t>-801</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ALSINA, ADOLFO 2457</t>
+          <t>YRIGOYEN, HIPOLITO 2754</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>814125554</t>
+          <t>814125643</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -13178,10 +13178,10 @@
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.401052</v>
+        <v>-58.405116</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.612103</v>
+        <v>-34.611253</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>-801</t>
+          <t>-810</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13217,7 +13217,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO 2754</t>
+          <t>MEXICO 2183</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>814125643</t>
+          <t>814125664</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -13264,10 +13264,10 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.405116</v>
+        <v>-58.397489</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.611253</v>
+        <v>-34.616089</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -13293,7 +13293,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>-810</t>
+          <t>-818</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13303,12 +13303,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>MEXICO 2183</t>
+          <t>PRINGLES 795</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13318,7 +13318,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>814125664</t>
+          <t>814125690</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -13328,7 +13328,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base podrida</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -13350,10 +13350,10 @@
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.397489</v>
+        <v>-58.427096</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.616089</v>
+        <v>-34.602833</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -13379,7 +13379,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>-818</t>
+          <t>-820</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13389,12 +13389,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>PRINGLES 795</t>
+          <t>RIOBAMBA 558</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>814125690</t>
+          <t>814125697</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>base podrida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -13436,10 +13436,10 @@
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.427096</v>
+        <v>-58.394106</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.602833</v>
+        <v>-34.602514</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
@@ -13453,19 +13453,19 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>RET-J</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>-820</t>
+          <t>-828</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>RIOBAMBA 558</t>
+          <t>TUCUMAN 2074</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>814125697</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -13510,7 +13510,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -13522,10 +13522,10 @@
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>-58.394106</v>
+        <v>-58.396631</v>
       </c>
       <c r="N153" t="n">
-        <v>-34.602514</v>
+        <v>-34.60222</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -13543,92 +13543,6 @@
         </is>
       </c>
       <c r="R153" t="inlineStr">
-        <is>
-          <t>ARATO-25058.PO.1RET</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>-828</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>6/2/2026</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>TUCUMAN 2074</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>FIBERWORK</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L154" t="n">
-        <v>1</v>
-      </c>
-      <c r="M154" t="n">
-        <v>-58.396631</v>
-      </c>
-      <c r="N154" t="n">
-        <v>-34.60222</v>
-      </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>Almagro</t>
-        </is>
-      </c>
-      <c r="P154" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>RET-J</t>
-        </is>
-      </c>
-      <c r="R154" t="inlineStr">
         <is>
           <t>ARATO-25058.PO.1RET</t>
         </is>

--- a/mapa_interactivo_Fiberwork.xlsx
+++ b/mapa_interactivo_Fiberwork.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R153"/>
+  <dimension ref="A1:R152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5659,17 +5659,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>S01199412</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUMAHUACA 4298 </t>
+          <t>ACUÑA DE FIGUEROA, FRANCISCO 1028</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>811198696</t>
+          <t>811198676</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5716,10 +5716,10 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.425302</v>
+        <v>-58.422033</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.601502</v>
+        <v>-34.598976</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>CLI-L</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5745,22 +5745,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S01199412</t>
+          <t>-705</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/22/2025</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ACUÑA DE FIGUEROA, FRANCISCO 1028</t>
+          <t>Larrea 370</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>811198676</t>
+          <t>02013924</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -5802,10 +5802,10 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.422033</v>
+        <v>-58.402154</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.598976</v>
+        <v>-34.605295</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>CLI-L</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5831,22 +5831,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>-705</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12/22/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Larrea 370</t>
+          <t>BRAVO, MARIO 478</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>02013924</t>
+          <t>811299416</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -5888,10 +5888,10 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.402154</v>
+        <v>-58.416901</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.605295</v>
+        <v>-34.604236</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5917,17 +5917,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>-711</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BRAVO, MARIO 478</t>
+          <t>México 3306</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>811299416</t>
+          <t>811299443</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5974,10 +5974,10 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.416901</v>
+        <v>-58.412865</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.604236</v>
+        <v>-34.619484</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6003,17 +6003,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>-711</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>México 3306</t>
+          <t>LAMBARE 864</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>811299443</t>
+          <t>811453866</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -6060,10 +6060,10 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.412865</v>
+        <v>-58.430579</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.619484</v>
+        <v>-34.604908</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>ALM-M</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6089,17 +6089,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>S00941232</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>LAMBARE 864</t>
+          <t>TARIJA 3323</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>811453866</t>
+          <t>811453904</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6146,14 +6146,14 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.430579</v>
+        <v>-58.412204</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.604908</v>
+        <v>-34.628609</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>ALM-M</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6175,22 +6175,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S00941232</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>TARIJA 3323</t>
+          <t>Catamarca 236</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>811453904</t>
+          <t xml:space="preserve">02511385 </t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6232,14 +6232,14 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.412204</v>
+        <v>-58.406807</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.628609</v>
+        <v>-34.612902</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6261,7 +6261,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>8124</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Catamarca 236</t>
+          <t xml:space="preserve"> DIAZ VELEZ AV. 4421</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">02511385 </t>
+          <t>811454440</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6318,10 +6318,10 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.406807</v>
+        <v>-58.429481</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.612902</v>
+        <v>-34.608647</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>ALM-K</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6347,22 +6347,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>S01432754</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/16/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DIAZ VELEZ AV. 4421</t>
+          <t>MISIONES 242</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>811454440</t>
+          <t>811454538</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6404,10 +6404,10 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.429481</v>
+        <v>-58.404243</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.608647</v>
+        <v>-34.612859</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>ALM-K</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6433,7 +6433,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S01432754</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MISIONES 242</t>
+          <t>Castelli 60</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>811454538</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6468,32 +6468,20 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>corroida</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+          <t>traspaso propio tlc coloco columna</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="n">
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.404243</v>
+        <v>-58.404691</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.612859</v>
+        <v>-34.609194</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6507,7 +6495,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6519,17 +6507,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>S01408162</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1/16/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Castelli 60</t>
+          <t xml:space="preserve">GARAY, JUAN DE AV. 2871 </t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6539,12 +6527,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812439895</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6554,24 +6542,36 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>traspaso propio tlc coloco columna</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
       <c r="L72" t="n">
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.404691</v>
+        <v>-58.4048</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.609194</v>
+        <v>-34.629021</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6593,17 +6593,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S01408162</t>
+          <t>S00034481</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARAY, JUAN DE AV. 2871 </t>
+          <t xml:space="preserve">MITRE, BARTOLOME 2294 </t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>812439895</t>
+          <t>811626888</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6650,14 +6650,14 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.4048</v>
+        <v>-58.399059</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.629021</v>
+        <v>-34.608499</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>CLI-C</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6679,17 +6679,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S00034481</t>
+          <t>S01314715</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">MITRE, BARTOLOME 2294 </t>
+          <t xml:space="preserve"> CATAMARCA 919</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>811626888</t>
+          <t>811626986</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Corroida</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6736,14 +6736,14 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.399059</v>
+        <v>-58.404766</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.608499</v>
+        <v>-34.620521</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>CLI-C</t>
+          <t>CEN-K</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6765,7 +6765,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S01314715</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CATAMARCA 919</t>
+          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>811626986</t>
+          <t>811626981</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6822,14 +6822,14 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.404766</v>
+        <v>-58.423058</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.620521</v>
+        <v>-34.608916</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>CEN-K</t>
+          <t>ALM-E</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6851,22 +6851,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8125</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
+          <t>COMBATE DE LOS POZOS 1103</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>811626981</t>
+          <t>811627014</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6908,14 +6908,14 @@
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.423058</v>
+        <v>-58.393145</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.608916</v>
+        <v>-34.621778</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>ALM-E</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6937,17 +6937,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>S00022862</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>COMBATE DE LOS POZOS 1103</t>
+          <t>YRIGOYEN, HIPOLITO 2395</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>811627014</t>
+          <t>811627077</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6994,14 +6994,14 @@
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.393145</v>
+        <v>-58.400243</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.621778</v>
+        <v>-34.610864</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7023,7 +7023,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S00022862</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO 2395</t>
+          <t>PICHINCHA 89</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>811627077</t>
+          <t>811627062</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7080,10 +7080,10 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.400243</v>
+        <v>-58.399124</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.610864</v>
+        <v>-34.610705</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -7109,22 +7109,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/6/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PICHINCHA 89</t>
+          <t>GALLO 77</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>811627062</t>
+          <t>811627128</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>tensor roto inclinada</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7159,17 +7159,17 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L79" t="n">
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.399124</v>
+        <v>-58.413979</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.610705</v>
+        <v>-34.607475</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7195,22 +7195,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8296</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2/6/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GALLO 77</t>
+          <t>RINCON 1109</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>811627128</t>
+          <t>812439968</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>tensor roto inclinada</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7245,21 +7245,21 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L80" t="n">
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.413979</v>
+        <v>-58.395668</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.607475</v>
+        <v>-34.621926</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>CEN-N</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7281,17 +7281,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>8329</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>RINCON 1109</t>
+          <t xml:space="preserve">ALBERTI 1055 </t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>812439968</t>
+          <t>812440156</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7338,10 +7338,10 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.395668</v>
+        <v>-58.400774</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.621926</v>
+        <v>-34.621503</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -7367,17 +7367,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>S00136365</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALBERTI 1055 </t>
+          <t>PERON, JUAN DOMINGO, TTE. GENERAL 2697</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>812440156</t>
+          <t>812440173</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -7424,14 +7424,14 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.400774</v>
+        <v>-58.404576</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.621503</v>
+        <v>-34.607569</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>CEN-N</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7453,7 +7453,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S00136365</t>
+          <t>S00144805</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PERON, JUAN DOMINGO, TTE. GENERAL 2697</t>
+          <t>VIAMONTE 1990</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>812440173</t>
+          <t>812440165</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7510,10 +7510,10 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.404576</v>
+        <v>-58.395384</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.607569</v>
+        <v>-34.600962</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -7527,29 +7527,29 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>RET-J</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S00144805</t>
+          <t>-749</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>VIAMONTE 1990</t>
+          <t>Moreno 2965</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>812440165</t>
+          <t>812440614</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -7596,10 +7596,10 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.395384</v>
+        <v>-58.407758</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.600962</v>
+        <v>-34.613793</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -7613,19 +7613,19 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>RET-J</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>-749</t>
+          <t>-760</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Moreno 2965</t>
+          <t>MAZA 1615</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>812440614</t>
+          <t>812440354</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>base corroida e inclinada</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7682,14 +7682,14 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.407758</v>
+        <v>-58.414586</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.613793</v>
+        <v>-34.630095</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -7711,7 +7711,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>-760</t>
+          <t>S00519068</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MAZA 1615</t>
+          <t>CALVO, CARLOS 3747</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>812440354</t>
+          <t>812440282</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>base corroida e inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7768,10 +7768,10 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.414586</v>
+        <v>-58.41859</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.630095</v>
+        <v>-34.624508</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7797,17 +7797,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S00519068</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/27/2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3747</t>
+          <t xml:space="preserve">BRAVO, MARIO 836 </t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>812440282</t>
+          <t>812503638</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -7854,14 +7854,14 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.41859</v>
+        <v>-58.416187</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.624508</v>
+        <v>-34.600138</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CLI-G</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7883,17 +7883,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>S00100362</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2/27/2026</t>
+          <t>3/4/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRAVO, MARIO 836 </t>
+          <t>RIO DE JANEIRO 901</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>812503638</t>
+          <t>814105603</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7940,10 +7940,10 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.416187</v>
+        <v>-58.431406</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.600138</v>
+        <v>-34.605009</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>CLI-G</t>
+          <t>ALM-M</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7969,17 +7969,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S00100362</t>
+          <t>-774</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>3/4/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO 901</t>
+          <t>CASEROS AV. 4131</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>814105603</t>
+          <t>814107131</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>mover a 4111</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8026,14 +8026,14 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.431406</v>
+        <v>-58.422741</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.605009</v>
+        <v>-34.639999</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>ALM-M</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8055,17 +8055,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>-774</t>
+          <t>00050599</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CASEROS AV. 4131</t>
+          <t xml:space="preserve">BELGRANO AV 3689 </t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>814107131</t>
+          <t>812879940</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>mover a 4111</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8112,14 +8112,14 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.422741</v>
+        <v>-58.418254</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.639999</v>
+        <v>-34.615692</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8141,7 +8141,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>00050599</t>
+          <t>00223191</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">BELGRANO AV 3689 </t>
+          <t>CATAMARCA 254</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>812879940</t>
+          <t>812879982</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8198,10 +8198,10 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.418254</v>
+        <v>-58.406734</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.615692</v>
+        <v>-34.613107</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8227,7 +8227,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>00223191</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8237,12 +8237,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CATAMARCA 254</t>
+          <t>CORRIENTES AV 4073</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>812879982</t>
+          <t>812880406</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -8284,10 +8284,10 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.406734</v>
+        <v>-58.422076</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.613107</v>
+        <v>-34.60298</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8313,7 +8313,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>00223023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CORRIENTES AV 4073</t>
+          <t>SAN JUAN AV. 2201</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>812880406</t>
+          <t>814109847</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -8370,14 +8370,14 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.422076</v>
+        <v>-58.396491</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.60298</v>
+        <v>-34.622986</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8399,22 +8399,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>00223023</t>
+          <t>00317296</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/23/2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 2201</t>
+          <t>AGRELO 3620</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>814109847</t>
+          <t>812880625</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -8456,14 +8456,14 @@
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.396491</v>
+        <v>-58.417002</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.622986</v>
+        <v>-34.618613</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>ALM-B</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8485,7 +8485,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>00317296</t>
+          <t>00322642</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AGRELO 3620</t>
+          <t>ESTADO DE PALESTINA 727</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>812880625</t>
+          <t>812880655</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -8542,10 +8542,10 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.417002</v>
+        <v>-58.425539</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.618613</v>
+        <v>-34.602286</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>ALM-B</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8571,7 +8571,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>00322642</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 727</t>
+          <t>MEXICO 3306</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>812880655</t>
+          <t>812880662</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -8628,10 +8628,10 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.425539</v>
+        <v>-58.412865</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.602286</v>
+        <v>-34.619484</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8657,7 +8657,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>8265</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MEXICO 3306</t>
+          <t>HUMBERTO 1 1999</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>812880662</t>
+          <t>812880685</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -8714,14 +8714,14 @@
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.412865</v>
+        <v>-58.394304</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.619484</v>
+        <v>-34.621645</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8743,17 +8743,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>3/23/2026</t>
+          <t>3/28/2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>HUMBERTO 1 1999</t>
+          <t>RIVADAVIA AV 1985</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>812880685</t>
+          <t>812880736</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>APLOMAR COLUMNA</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -8800,14 +8800,14 @@
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.394304</v>
+        <v>-58.394609</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.621645</v>
+        <v>-34.609304</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8829,22 +8829,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>M881</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3/28/2026</t>
+          <t>4/1/2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>RIVADAVIA AV 1985</t>
+          <t>AV LA PLATA 2288</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>812880736</t>
+          <t>813046342</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -8864,17 +8864,17 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>APLOMAR COLUMNA</t>
+          <t>DESMONTAR COLUMNA Y  DESPLAZAR PCALOGERO</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -8886,14 +8886,14 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.394609</v>
+        <v>-58.423203</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.609304</v>
+        <v>-34.640909</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8915,22 +8915,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>M881</t>
+          <t>8802</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>4/1/2026</t>
+          <t>4/11/2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AV LA PLATA 2288</t>
+          <t>RINCON 731</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>813046342</t>
+          <t>813046658</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>DESMONTAR COLUMNA Y  DESPLAZAR PCALOGERO</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -8972,14 +8972,14 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.423203</v>
+        <v>-58.396088</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.640909</v>
+        <v>-34.617527</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9001,7 +9001,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8802</t>
+          <t>S00374917</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>RINCON 731</t>
+          <t>24 DE NOVIEMBRE 695</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>813046658</t>
+          <t>813046791</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -9058,10 +9058,10 @@
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.396088</v>
+        <v>-58.411053</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.617527</v>
+        <v>-34.618979</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9087,7 +9087,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S00374917</t>
+          <t>S00379764</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>24 DE NOVIEMBRE 695</t>
+          <t>JAURES JEAN 491</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>813046791</t>
+          <t>813046795</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -9144,10 +9144,10 @@
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.411053</v>
+        <v>-58.408934</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.618979</v>
+        <v>-34.604273</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>CLI-H</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9173,7 +9173,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S00379764</t>
+          <t>S00379996</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>JAURES JEAN 491</t>
+          <t>SARANDI 1439</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>813046795</t>
+          <t>813046806</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -9230,14 +9230,14 @@
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.408934</v>
+        <v>-58.393455</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.604273</v>
+        <v>-34.625779</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>CLI-H</t>
+          <t>CON-C</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9259,7 +9259,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S00379996</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SARANDI 1439</t>
+          <t>SARMIENTO 2108</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>813046806</t>
+          <t>813046819</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -9316,14 +9316,14 @@
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.393455</v>
+        <v>-58.39675</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.625779</v>
+        <v>-34.605996</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>CON-C</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9345,7 +9345,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9355,12 +9355,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SARMIENTO 2108</t>
+          <t>SANCHEZ DE BUSTAMANTE 633</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>813046819</t>
+          <t>813046866</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -9402,10 +9402,10 @@
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.39675</v>
+        <v>-58.414203</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.605996</v>
+        <v>-34.602602</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>CLI-G</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9431,7 +9431,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SANCHEZ DE BUSTAMANTE 633</t>
+          <t>RIVADAVIA AV 4245</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>813046866</t>
+          <t>813046970</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -9488,10 +9488,10 @@
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.414203</v>
+        <v>-58.425567</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.602602</v>
+        <v>-34.613382</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>CLI-G</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9517,7 +9517,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>RIVADAVIA AV 4245</t>
+          <t>DIAZ VELEZ AV 4449</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>813046970</t>
+          <t>813046971</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -9574,10 +9574,10 @@
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.425567</v>
+        <v>-58.429714</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.613382</v>
+        <v>-34.608645</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>ALM-K</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9603,7 +9603,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV 4449</t>
+          <t>LAS CASAS 3989</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>813046971</t>
+          <t>813046994</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -9660,14 +9660,14 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.429714</v>
+        <v>-58.421676</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.608645</v>
+        <v>-34.635878</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>ALM-K</t>
+          <t>PPT-R</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9689,7 +9689,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>8851</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>LAS CASAS 3989</t>
+          <t>SALCEDO 3541</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>813046994</t>
+          <t>813047007</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -9746,10 +9746,10 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.421676</v>
+        <v>-58.415121</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.635878</v>
+        <v>-34.633772</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>PPT-R</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9775,7 +9775,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>8852</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SALCEDO 3541</t>
+          <t>TARIJA 4079</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>813047007</t>
+          <t>813047012</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -9832,10 +9832,10 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.415121</v>
+        <v>-58.421804</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.633772</v>
+        <v>-34.629558</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>PPT-R</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9861,7 +9861,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>8853</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TARIJA 4079</t>
+          <t>TIMBUES 2086</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>813047012</t>
+          <t>813047017</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -9918,10 +9918,10 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.421804</v>
+        <v>-58.421835</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.629558</v>
+        <v>-34.63863</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>PPT-R</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9947,7 +9947,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>8855</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TIMBUES 2086</t>
+          <t>GOMEZ VALENTIN 3684</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>813047017</t>
+          <t>813047019</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -10004,14 +10004,14 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.421835</v>
+        <v>-58.416726</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.63863</v>
+        <v>-34.604773</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10033,7 +10033,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>S00390896</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10043,12 +10043,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GOMEZ VALENTIN 3684</t>
+          <t>AV INDEPENDENCIA 2018</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>813047019</t>
+          <t>813047657</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -10090,10 +10090,10 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.416726</v>
+        <v>-58.39469</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.604773</v>
+        <v>-34.618394</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10119,22 +10119,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S00390896</t>
+          <t>RB00001</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AV INDEPENDENCIA 2018</t>
+          <t>BELGRANO AV. 3715</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10144,7 +10144,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>813047657</t>
+          <t>813304903</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -10176,10 +10176,10 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.39469</v>
+        <v>-58.418851</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.618394</v>
+        <v>-34.615716</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10205,7 +10205,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>RB00001</t>
+          <t>AM00039</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>BELGRANO AV. 3715</t>
+          <t>CASTRO BARROS 852</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>813304903</t>
+          <t>813304915</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -10262,14 +10262,14 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.418851</v>
+        <v>-58.419281</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.615716</v>
+        <v>-34.62215</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10291,7 +10291,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AM00039</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10301,12 +10301,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CASTRO BARROS 852</t>
+          <t>ALSINA, ADOLFO 3293</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>813304915</t>
+          <t>813350607</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -10348,14 +10348,14 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.419281</v>
+        <v>-58.412936</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.62215</v>
+        <v>-34.613332</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10377,7 +10377,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>S00423738</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ALSINA, ADOLFO 3293</t>
+          <t>CATAMARCA 568</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>813350607</t>
+          <t>813350620</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -10434,10 +10434,10 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.412936</v>
+        <v>-58.405541</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.613332</v>
+        <v>-34.616959</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10463,22 +10463,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S00423738</t>
+          <t>S00299569</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/21/2026</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CATAMARCA 568</t>
+          <t>YRIGOYEN, HIPOLITO AV. 4156</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>813350620</t>
+          <t>813350953</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -10520,10 +10520,10 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.405541</v>
+        <v>-58.425213</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.616959</v>
+        <v>-34.614924</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10549,7 +10549,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S00299569</t>
+          <t>S004318770</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO AV. 4156</t>
+          <t>SARMIENTO 4290</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>813350953</t>
+          <t>813351576</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -10606,10 +10606,10 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.425213</v>
+        <v>-58.425764</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.614924</v>
+        <v>-34.604359</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>ALM-L</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10635,7 +10635,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S004318770</t>
+          <t>S00431893</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>SARMIENTO 4290</t>
+          <t>MUÑIZ 1151</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>813351576</t>
+          <t>814105853</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -10692,14 +10692,14 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.425764</v>
+        <v>-58.425442</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.604359</v>
+        <v>-34.627634</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>ALM-L</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10721,7 +10721,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S00431893</t>
+          <t>S00434849</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MUÑIZ 1151</t>
+          <t>YRIGOYEN, HIPOLITO AV. 3484</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>814105853</t>
+          <t>813352212</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -10778,14 +10778,14 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.425442</v>
+        <v>-58.416028</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.627634</v>
+        <v>-34.613538</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -10795,7 +10795,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10807,7 +10807,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S00434849</t>
+          <t xml:space="preserve">9009 </t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO AV. 3484</t>
+          <t>SANCHEZ DE LORIA 1913</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>813352212</t>
+          <t>813352473</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -10864,14 +10864,14 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.416028</v>
+        <v>-58.411474</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.613538</v>
+        <v>-34.633143</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10893,7 +10893,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9009 </t>
+          <t xml:space="preserve">9011 </t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1913</t>
+          <t>SANCHEZ DE LORIA 1583</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>813352473</t>
+          <t>813352481</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -10950,14 +10950,14 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.411474</v>
+        <v>-58.411926</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.633143</v>
+        <v>-34.628861</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10979,7 +10979,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9011 </t>
+          <t xml:space="preserve">9012 </t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1583</t>
+          <t xml:space="preserve">LINIERS VIRREY 2315 </t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>813352481</t>
+          <t>813352482</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -11036,14 +11036,14 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.411926</v>
+        <v>-58.41191</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.628861</v>
+        <v>-34.637333</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11065,7 +11065,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9012 </t>
+          <t xml:space="preserve">9014 </t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINIERS VIRREY 2315 </t>
+          <t>LINIERS VIRREY 896</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>813352482</t>
+          <t>813352486</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -11122,14 +11122,14 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.41191</v>
+        <v>-58.413645</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.637333</v>
+        <v>-34.621935</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11151,7 +11151,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9014 </t>
+          <t xml:space="preserve">9016 </t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 896</t>
+          <t>HUMBERTO 1° 3368</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>813352486</t>
+          <t>813352494</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -11208,10 +11208,10 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.413645</v>
+        <v>-58.413189</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.621935</v>
+        <v>-34.624187</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9016 </t>
+          <t xml:space="preserve">9017 </t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>HUMBERTO 1° 3368</t>
+          <t>MUÑIZ 1237</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>813352494</t>
+          <t>814105864</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -11294,10 +11294,10 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.413189</v>
+        <v>-58.425206</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.624187</v>
+        <v>-34.628705</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11323,7 +11323,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9017 </t>
+          <t xml:space="preserve">9020 </t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MUÑIZ 1237</t>
+          <t>TARIJA 3497</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>814105864</t>
+          <t>813352497</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -11380,10 +11380,10 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.425206</v>
+        <v>-58.414424</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.628705</v>
+        <v>-34.628778</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11409,17 +11409,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9020 </t>
+          <t>9028</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>4/21/2026</t>
+          <t>4/24/2026</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>TARIJA 3497</t>
+          <t>BRAVO, MARIO 740</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>813352497</t>
+          <t>813352774</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -11466,14 +11466,14 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.414424</v>
+        <v>-58.416308</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.628778</v>
+        <v>-34.601047</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>CLI-G</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11495,7 +11495,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t>S00413025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>BRAVO, MARIO 740</t>
+          <t>CHILE 2550</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>813352774</t>
+          <t>813352855</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -11552,10 +11552,10 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.416308</v>
+        <v>-58.40174</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.601047</v>
+        <v>-34.617754</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>CLI-G</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11581,7 +11581,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S00413025</t>
+          <t>S00429731</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CHILE 2550</t>
+          <t xml:space="preserve">ALSINA, ADOLFO 2291 </t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>813352855</t>
+          <t>813352873</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -11638,10 +11638,10 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.40174</v>
+        <v>-58.398771</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.617754</v>
+        <v>-34.611932</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11667,22 +11667,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S00429731</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/29/2026</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALSINA, ADOLFO 2291 </t>
+          <t xml:space="preserve">GALLEGOS 3443 </t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>813352873</t>
+          <t>813353299</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -11724,14 +11724,14 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.398771</v>
+        <v>-58.413647</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.611932</v>
+        <v>-34.631434</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11753,17 +11753,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t xml:space="preserve">9045 </t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>4/29/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALLEGOS 3443 </t>
+          <t>LINIERS VIRREY 1793</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>813353299</t>
+          <t>813631423</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -11810,14 +11810,14 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.413647</v>
+        <v>-58.413025</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.631434</v>
+        <v>-34.631929</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11839,7 +11839,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">9045 </t>
+          <t>9049</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1793</t>
+          <t>BATHURST 3377</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>813631423</t>
+          <t>813631424</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -11896,10 +11896,10 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.413025</v>
+        <v>-58.411896</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.631929</v>
+        <v>-34.636028</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -11925,22 +11925,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>S00215089</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BATHURST 3377</t>
+          <t>LARREA 122</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -11950,7 +11950,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>813631424</t>
+          <t>813631550</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -11982,14 +11982,14 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.411896</v>
+        <v>-58.401972</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.636028</v>
+        <v>-34.608317</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -12011,7 +12011,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S00215089</t>
+          <t>S00401648</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>LARREA 122</t>
+          <t>JUNIN 312</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>813631550</t>
+          <t>813632251</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -12068,10 +12068,10 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.401972</v>
+        <v>-58.396676</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.608317</v>
+        <v>-34.605753</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12097,7 +12097,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S00401648</t>
+          <t>S00465940</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12107,12 +12107,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>JUNIN 312</t>
+          <t>BELGRANO AV. 3669</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12122,7 +12122,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>813632251</t>
+          <t>813632257</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -12154,10 +12154,10 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.396676</v>
+        <v>-58.417949</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.605753</v>
+        <v>-34.615674</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12183,7 +12183,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S00465940</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BELGRANO AV. 3669</t>
+          <t>JAURES, JEAN 309</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12208,7 +12208,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>813632257</t>
+          <t>813632439</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -12240,10 +12240,10 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.417949</v>
+        <v>-58.409868</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.615674</v>
+        <v>-34.606562</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>CLI-H</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12269,22 +12269,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>S00364775</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>JAURES, JEAN 309</t>
+          <t>CASTRO 511</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12292,11 +12292,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>813632439</t>
-        </is>
-      </c>
+      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
           <t>FIBERWORK</t>
@@ -12304,12 +12300,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>NORMALIZAR RIENDA A PIQUE</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Tensor</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -12319,17 +12315,17 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L139" t="n">
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.409868</v>
+        <v>-58.420597</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.606562</v>
+        <v>-34.617818</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -12343,7 +12339,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>CLI-H</t>
+          <t>ALM-B</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12355,7 +12351,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S00364775</t>
+          <t>S00493114</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12365,12 +12361,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>CASTRO 511</t>
+          <t>ARENALES 3648</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12378,7 +12374,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>813352547</t>
+        </is>
+      </c>
       <c r="G140" t="inlineStr">
         <is>
           <t>FIBERWORK</t>
@@ -12386,36 +12386,36 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>NORMALIZAR RIENDA A PIQUE</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Tensor</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.420597</v>
+        <v>-58.413656</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.617818</v>
+        <v>-34.585464</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>ALM-B</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12437,7 +12437,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S00493114</t>
+          <t xml:space="preserve">7880 </t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12447,12 +12447,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ARENALES 3648</t>
+          <t>MUÑIZ 16</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>813352547</t>
+          <t>814109709</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -12482,7 +12482,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -12494,14 +12494,14 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.413656</v>
+        <v>-58.427498</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.585464</v>
+        <v>-34.614599</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12523,7 +12523,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">7880 </t>
+          <t xml:space="preserve">9923 </t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12533,7 +12533,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>MUÑIZ 16</t>
+          <t>PRINGLES 1094</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>814109709</t>
+          <t>814109753</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -12580,10 +12580,10 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.427498</v>
+        <v>-58.426722</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.614599</v>
+        <v>-34.599427</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12609,17 +12609,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">9923 </t>
+          <t xml:space="preserve">9019 </t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>PRINGLES 1094</t>
+          <t>CASTRO BARROS AV. 338</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -12634,7 +12634,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>814109753</t>
+          <t>814108068</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -12666,10 +12666,10 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.426722</v>
+        <v>-58.419864</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.599427</v>
+        <v>-34.616375</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12695,7 +12695,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9019 </t>
+          <t xml:space="preserve">9031 </t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12705,12 +12705,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CASTRO BARROS AV. 338</t>
+          <t>YRIGOYEN, HIPOLITO 1938</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -12718,11 +12718,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>814108068</t>
-        </is>
-      </c>
+      <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
           <t>FIBERWORK</t>
@@ -12740,7 +12736,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -12752,10 +12748,10 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.419864</v>
+        <v>-58.394079</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.616375</v>
+        <v>-34.61051</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -12769,7 +12765,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12781,7 +12777,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9031 </t>
+          <t xml:space="preserve">9088 </t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12791,12 +12787,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO 1938</t>
+          <t>HUMAHUACA 4296</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12804,7 +12800,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>814108086</t>
+        </is>
+      </c>
       <c r="G145" t="inlineStr">
         <is>
           <t>FIBERWORK</t>
@@ -12822,7 +12822,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -12834,10 +12834,10 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.394079</v>
+        <v>-58.425282</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.61051</v>
+        <v>-34.601504</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -12851,7 +12851,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12863,7 +12863,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">9088 </t>
+          <t xml:space="preserve">10059 </t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>HUMAHUACA 4296</t>
+          <t xml:space="preserve">SALGUERO, JERONIMO 2296 </t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>814108086</t>
+          <t>814111727</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -12920,14 +12920,14 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.425282</v>
+        <v>-58.411132</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.601504</v>
+        <v>-34.585267</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>AGU-K</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12949,17 +12949,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">10059 </t>
+          <t>-776</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>6/2/2026</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALGUERO, JERONIMO 2296 </t>
+          <t>ALSINA, ADOLFO 2457</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>814111727</t>
+          <t>814125554</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -13006,14 +13006,14 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.411132</v>
+        <v>-58.401052</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.585267</v>
+        <v>-34.612103</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>AGU-K</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -13035,7 +13035,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>-776</t>
+          <t>-801</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13045,7 +13045,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ALSINA, ADOLFO 2457</t>
+          <t>YRIGOYEN, HIPOLITO 2754</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>814125554</t>
+          <t>814125643</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -13092,10 +13092,10 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.401052</v>
+        <v>-58.405116</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.612103</v>
+        <v>-34.611253</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>-801</t>
+          <t>-810</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO 2754</t>
+          <t>MEXICO 2183</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>814125643</t>
+          <t>814125664</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -13178,10 +13178,10 @@
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.405116</v>
+        <v>-58.397489</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.611253</v>
+        <v>-34.616089</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13207,7 +13207,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>-810</t>
+          <t>-818</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13217,12 +13217,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>MEXICO 2183</t>
+          <t>PRINGLES 795</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>814125664</t>
+          <t>814125690</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -13242,7 +13242,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base podrida</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -13264,10 +13264,10 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.397489</v>
+        <v>-58.427096</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.616089</v>
+        <v>-34.602833</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -13293,7 +13293,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>-818</t>
+          <t>-820</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13303,12 +13303,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>PRINGLES 795</t>
+          <t>RIOBAMBA 558</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13318,7 +13318,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>814125690</t>
+          <t>814125697</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -13328,7 +13328,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>base podrida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -13350,10 +13350,10 @@
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.427096</v>
+        <v>-58.394106</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.602833</v>
+        <v>-34.602514</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -13367,19 +13367,19 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>RET-J</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>-820</t>
+          <t>-828</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>RIOBAMBA 558</t>
+          <t>TUCUMAN 2074</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>814125697</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -13436,10 +13436,10 @@
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.394106</v>
+        <v>-58.396631</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.602514</v>
+        <v>-34.60222</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
@@ -13457,92 +13457,6 @@
         </is>
       </c>
       <c r="R152" t="inlineStr">
-        <is>
-          <t>ARATO-25058.PO.1RET</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>-828</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>6/2/2026</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>TUCUMAN 2074</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>FIBERWORK</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L153" t="n">
-        <v>1</v>
-      </c>
-      <c r="M153" t="n">
-        <v>-58.396631</v>
-      </c>
-      <c r="N153" t="n">
-        <v>-34.60222</v>
-      </c>
-      <c r="O153" t="inlineStr">
-        <is>
-          <t>Almagro</t>
-        </is>
-      </c>
-      <c r="P153" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>RET-J</t>
-        </is>
-      </c>
-      <c r="R153" t="inlineStr">
         <is>
           <t>ARATO-25058.PO.1RET</t>
         </is>

--- a/mapa_interactivo_Fiberwork.xlsx
+++ b/mapa_interactivo_Fiberwork.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R152"/>
+  <dimension ref="A1:R151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8657,17 +8657,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>3/23/2026</t>
+          <t>3/28/2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>HUMBERTO 1 1999</t>
+          <t>RIVADAVIA AV 1985</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>812880685</t>
+          <t>812880736</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -8692,12 +8692,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>APLOMAR COLUMNA</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -8714,14 +8714,14 @@
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.394304</v>
+        <v>-58.394609</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.621645</v>
+        <v>-34.609304</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8743,22 +8743,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>M881</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>3/28/2026</t>
+          <t>4/1/2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>RIVADAVIA AV 1985</t>
+          <t>AV LA PLATA 2288</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>812880736</t>
+          <t>813046342</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -8778,17 +8778,17 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>APLOMAR COLUMNA</t>
+          <t>DESMONTAR COLUMNA Y  DESPLAZAR PCALOGERO</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -8800,14 +8800,14 @@
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.394609</v>
+        <v>-58.423203</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.609304</v>
+        <v>-34.640909</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8829,22 +8829,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>M881</t>
+          <t>8802</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>4/1/2026</t>
+          <t>4/11/2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AV LA PLATA 2288</t>
+          <t>RINCON 731</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>813046342</t>
+          <t>813046658</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>DESMONTAR COLUMNA Y  DESPLAZAR PCALOGERO</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -8886,14 +8886,14 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.423203</v>
+        <v>-58.396088</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.640909</v>
+        <v>-34.617527</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8915,7 +8915,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8802</t>
+          <t>S00374917</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>RINCON 731</t>
+          <t>24 DE NOVIEMBRE 695</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>813046658</t>
+          <t>813046791</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -8972,10 +8972,10 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.396088</v>
+        <v>-58.411053</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.617527</v>
+        <v>-34.618979</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9001,7 +9001,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S00374917</t>
+          <t>S00379764</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>24 DE NOVIEMBRE 695</t>
+          <t>JAURES JEAN 491</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>813046791</t>
+          <t>813046795</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -9058,10 +9058,10 @@
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.411053</v>
+        <v>-58.408934</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.618979</v>
+        <v>-34.604273</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>CLI-H</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9087,7 +9087,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S00379764</t>
+          <t>S00379996</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>JAURES JEAN 491</t>
+          <t>SARANDI 1439</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>813046795</t>
+          <t>813046806</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -9144,14 +9144,14 @@
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.408934</v>
+        <v>-58.393455</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.604273</v>
+        <v>-34.625779</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>CLI-H</t>
+          <t>CON-C</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9173,7 +9173,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S00379996</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SARANDI 1439</t>
+          <t>SARMIENTO 2108</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>813046806</t>
+          <t>813046819</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -9230,14 +9230,14 @@
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.393455</v>
+        <v>-58.39675</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.625779</v>
+        <v>-34.605996</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>CON-C</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9259,7 +9259,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9269,12 +9269,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SARMIENTO 2108</t>
+          <t>SANCHEZ DE BUSTAMANTE 633</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>813046819</t>
+          <t>813046866</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -9316,10 +9316,10 @@
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.39675</v>
+        <v>-58.414203</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.605996</v>
+        <v>-34.602602</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>CLI-G</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9345,7 +9345,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SANCHEZ DE BUSTAMANTE 633</t>
+          <t>RIVADAVIA AV 4245</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>813046866</t>
+          <t>813046970</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -9402,10 +9402,10 @@
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.414203</v>
+        <v>-58.425567</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.602602</v>
+        <v>-34.613382</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>CLI-G</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9431,7 +9431,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>RIVADAVIA AV 4245</t>
+          <t>DIAZ VELEZ AV 4449</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>813046970</t>
+          <t>813046971</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -9488,10 +9488,10 @@
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.425567</v>
+        <v>-58.429714</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.613382</v>
+        <v>-34.608645</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>ALM-K</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9517,7 +9517,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV 4449</t>
+          <t>LAS CASAS 3989</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>813046971</t>
+          <t>813046994</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -9574,14 +9574,14 @@
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.429714</v>
+        <v>-58.421676</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.608645</v>
+        <v>-34.635878</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>ALM-K</t>
+          <t>PPT-R</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9603,7 +9603,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>8851</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>LAS CASAS 3989</t>
+          <t>SALCEDO 3541</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>813046994</t>
+          <t>813047007</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -9660,10 +9660,10 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.421676</v>
+        <v>-58.415121</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.635878</v>
+        <v>-34.633772</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>PPT-R</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9689,7 +9689,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>8852</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SALCEDO 3541</t>
+          <t>TARIJA 4079</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>813047007</t>
+          <t>813047012</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -9746,10 +9746,10 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.415121</v>
+        <v>-58.421804</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.633772</v>
+        <v>-34.629558</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>PPT-R</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9775,7 +9775,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>8853</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TARIJA 4079</t>
+          <t>TIMBUES 2086</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>813047012</t>
+          <t>813047017</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -9832,10 +9832,10 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.421804</v>
+        <v>-58.421835</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.629558</v>
+        <v>-34.63863</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>PPT-R</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9861,7 +9861,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>8855</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TIMBUES 2086</t>
+          <t>GOMEZ VALENTIN 3684</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>813047017</t>
+          <t>813047019</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -9918,14 +9918,14 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.421835</v>
+        <v>-58.416726</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.63863</v>
+        <v>-34.604773</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9947,7 +9947,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>S00390896</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9957,12 +9957,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>GOMEZ VALENTIN 3684</t>
+          <t>AV INDEPENDENCIA 2018</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>813047019</t>
+          <t>813047657</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -10004,10 +10004,10 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.416726</v>
+        <v>-58.39469</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.604773</v>
+        <v>-34.618394</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10033,22 +10033,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S00390896</t>
+          <t>RB00001</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>AV INDEPENDENCIA 2018</t>
+          <t>BELGRANO AV. 3715</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>813047657</t>
+          <t>813304903</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -10090,10 +10090,10 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.39469</v>
+        <v>-58.418851</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.618394</v>
+        <v>-34.615716</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10119,7 +10119,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>RB00001</t>
+          <t>AM00039</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>BELGRANO AV. 3715</t>
+          <t>CASTRO BARROS 852</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -10144,7 +10144,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>813304903</t>
+          <t>813304915</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -10176,14 +10176,14 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.418851</v>
+        <v>-58.419281</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.615716</v>
+        <v>-34.62215</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10205,7 +10205,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AM00039</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10215,12 +10215,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CASTRO BARROS 852</t>
+          <t>ALSINA, ADOLFO 3293</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>813304915</t>
+          <t>813350607</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -10262,14 +10262,14 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.419281</v>
+        <v>-58.412936</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.62215</v>
+        <v>-34.613332</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10291,7 +10291,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>S00423738</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ALSINA, ADOLFO 3293</t>
+          <t>CATAMARCA 568</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>813350607</t>
+          <t>813350620</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -10348,10 +10348,10 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.412936</v>
+        <v>-58.405541</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.613332</v>
+        <v>-34.616959</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10377,22 +10377,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S00423738</t>
+          <t>S00299569</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/21/2026</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CATAMARCA 568</t>
+          <t>YRIGOYEN, HIPOLITO AV. 4156</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>813350620</t>
+          <t>813350953</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -10434,10 +10434,10 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.405541</v>
+        <v>-58.425213</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.616959</v>
+        <v>-34.614924</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10463,7 +10463,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S00299569</t>
+          <t>S004318770</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO AV. 4156</t>
+          <t>SARMIENTO 4290</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>813350953</t>
+          <t>813351576</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -10520,10 +10520,10 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.425213</v>
+        <v>-58.425764</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.614924</v>
+        <v>-34.604359</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>ALM-L</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10549,7 +10549,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S004318770</t>
+          <t>S00431893</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SARMIENTO 4290</t>
+          <t>MUÑIZ 1151</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>813351576</t>
+          <t>814105853</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -10606,14 +10606,14 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.425764</v>
+        <v>-58.425442</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.604359</v>
+        <v>-34.627634</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>ALM-L</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10635,7 +10635,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S00431893</t>
+          <t>S00434849</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MUÑIZ 1151</t>
+          <t>YRIGOYEN, HIPOLITO AV. 3484</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>814105853</t>
+          <t>813352212</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -10692,14 +10692,14 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.425442</v>
+        <v>-58.416028</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.627634</v>
+        <v>-34.613538</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10721,7 +10721,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S00434849</t>
+          <t xml:space="preserve">9009 </t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO AV. 3484</t>
+          <t>SANCHEZ DE LORIA 1913</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>813352212</t>
+          <t>813352473</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -10778,14 +10778,14 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.416028</v>
+        <v>-58.411474</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.613538</v>
+        <v>-34.633143</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -10795,7 +10795,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10807,7 +10807,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">9009 </t>
+          <t xml:space="preserve">9011 </t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1913</t>
+          <t>SANCHEZ DE LORIA 1583</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>813352473</t>
+          <t>813352481</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -10864,14 +10864,14 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.411474</v>
+        <v>-58.411926</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.633143</v>
+        <v>-34.628861</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10893,7 +10893,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9011 </t>
+          <t xml:space="preserve">9012 </t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1583</t>
+          <t xml:space="preserve">LINIERS VIRREY 2315 </t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>813352481</t>
+          <t>813352482</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -10950,14 +10950,14 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.411926</v>
+        <v>-58.41191</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.628861</v>
+        <v>-34.637333</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10979,7 +10979,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9012 </t>
+          <t xml:space="preserve">9014 </t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINIERS VIRREY 2315 </t>
+          <t>LINIERS VIRREY 896</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>813352482</t>
+          <t>813352486</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -11036,14 +11036,14 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.41191</v>
+        <v>-58.413645</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.637333</v>
+        <v>-34.621935</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11065,7 +11065,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9014 </t>
+          <t xml:space="preserve">9016 </t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 896</t>
+          <t>HUMBERTO 1° 3368</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>813352486</t>
+          <t>813352494</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -11122,10 +11122,10 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.413645</v>
+        <v>-58.413189</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.621935</v>
+        <v>-34.624187</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9016 </t>
+          <t xml:space="preserve">9017 </t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>HUMBERTO 1° 3368</t>
+          <t>MUÑIZ 1237</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>813352494</t>
+          <t>814105864</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -11208,10 +11208,10 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.413189</v>
+        <v>-58.425206</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.624187</v>
+        <v>-34.628705</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11237,7 +11237,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9017 </t>
+          <t xml:space="preserve">9020 </t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MUÑIZ 1237</t>
+          <t>TARIJA 3497</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>814105864</t>
+          <t>813352497</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -11294,10 +11294,10 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.425206</v>
+        <v>-58.414424</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.628705</v>
+        <v>-34.628778</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11323,17 +11323,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9020 </t>
+          <t>9028</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>4/21/2026</t>
+          <t>4/24/2026</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>TARIJA 3497</t>
+          <t>BRAVO, MARIO 740</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>813352497</t>
+          <t>813352774</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -11380,14 +11380,14 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.414424</v>
+        <v>-58.416308</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.628778</v>
+        <v>-34.601047</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -11397,7 +11397,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>CLI-G</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11409,7 +11409,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t>S00413025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BRAVO, MARIO 740</t>
+          <t>CHILE 2550</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>813352774</t>
+          <t>813352855</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -11466,10 +11466,10 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.416308</v>
+        <v>-58.40174</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.601047</v>
+        <v>-34.617754</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>CLI-G</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11495,7 +11495,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S00413025</t>
+          <t>S00429731</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CHILE 2550</t>
+          <t xml:space="preserve">ALSINA, ADOLFO 2291 </t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>813352855</t>
+          <t>813352873</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -11552,10 +11552,10 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.40174</v>
+        <v>-58.398771</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.617754</v>
+        <v>-34.611932</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11581,22 +11581,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S00429731</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/29/2026</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALSINA, ADOLFO 2291 </t>
+          <t xml:space="preserve">GALLEGOS 3443 </t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>813352873</t>
+          <t>813353299</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -11638,14 +11638,14 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.398771</v>
+        <v>-58.413647</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.611932</v>
+        <v>-34.631434</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11667,17 +11667,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t xml:space="preserve">9045 </t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>4/29/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALLEGOS 3443 </t>
+          <t>LINIERS VIRREY 1793</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>813353299</t>
+          <t>813631423</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -11724,14 +11724,14 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.413647</v>
+        <v>-58.413025</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.631434</v>
+        <v>-34.631929</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11753,7 +11753,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">9045 </t>
+          <t>9049</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1793</t>
+          <t>BATHURST 3377</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>813631423</t>
+          <t>813631424</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -11810,10 +11810,10 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.413025</v>
+        <v>-58.411896</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.631929</v>
+        <v>-34.636028</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -11839,22 +11839,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>S00215089</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>BATHURST 3377</t>
+          <t>LARREA 122</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>813631424</t>
+          <t>813631550</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -11896,14 +11896,14 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.411896</v>
+        <v>-58.401972</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.636028</v>
+        <v>-34.608317</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11925,7 +11925,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S00215089</t>
+          <t>S00401648</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>LARREA 122</t>
+          <t>JUNIN 312</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11950,7 +11950,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>813631550</t>
+          <t>813632251</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -11970,7 +11970,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -11982,10 +11982,10 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.401972</v>
+        <v>-58.396676</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.608317</v>
+        <v>-34.605753</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -12011,7 +12011,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S00401648</t>
+          <t>S00465940</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12021,12 +12021,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>JUNIN 312</t>
+          <t>BELGRANO AV. 3669</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>813632251</t>
+          <t>813632257</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -12068,10 +12068,10 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.396676</v>
+        <v>-58.417949</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.605753</v>
+        <v>-34.615674</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12097,7 +12097,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S00465940</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12107,12 +12107,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>BELGRANO AV. 3669</t>
+          <t>JAURES, JEAN 309</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12122,7 +12122,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>813632257</t>
+          <t>813632439</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -12154,10 +12154,10 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.417949</v>
+        <v>-58.409868</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.615674</v>
+        <v>-34.606562</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>CLI-H</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12183,22 +12183,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>S00364775</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>JAURES, JEAN 309</t>
+          <t>CASTRO 511</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12206,11 +12206,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>813632439</t>
-        </is>
-      </c>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
           <t>FIBERWORK</t>
@@ -12218,12 +12214,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>NORMALIZAR RIENDA A PIQUE</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Tensor</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -12233,17 +12229,17 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L138" t="n">
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.409868</v>
+        <v>-58.420597</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.606562</v>
+        <v>-34.617818</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -12257,7 +12253,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>CLI-H</t>
+          <t>ALM-B</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12269,7 +12265,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S00364775</t>
+          <t>S00493114</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12279,12 +12275,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CASTRO 511</t>
+          <t>ARENALES 3648</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12292,7 +12288,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>813352547</t>
+        </is>
+      </c>
       <c r="G139" t="inlineStr">
         <is>
           <t>FIBERWORK</t>
@@ -12300,36 +12300,36 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>NORMALIZAR RIENDA A PIQUE</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Tensor</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L139" t="n">
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.420597</v>
+        <v>-58.413656</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.617818</v>
+        <v>-34.585464</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>ALM-B</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12351,7 +12351,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S00493114</t>
+          <t xml:space="preserve">7880 </t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12361,12 +12361,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ARENALES 3648</t>
+          <t>MUÑIZ 16</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>813352547</t>
+          <t>814109709</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -12408,14 +12408,14 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.413656</v>
+        <v>-58.427498</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.585464</v>
+        <v>-34.614599</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12437,7 +12437,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">7880 </t>
+          <t xml:space="preserve">9923 </t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MUÑIZ 16</t>
+          <t>PRINGLES 1094</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>814109709</t>
+          <t>814109753</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -12494,10 +12494,10 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.427498</v>
+        <v>-58.426722</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.614599</v>
+        <v>-34.599427</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12523,17 +12523,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9923 </t>
+          <t xml:space="preserve">9019 </t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PRINGLES 1094</t>
+          <t>CASTRO BARROS AV. 338</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>814109753</t>
+          <t>814108068</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -12580,10 +12580,10 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.426722</v>
+        <v>-58.419864</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.599427</v>
+        <v>-34.616375</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12609,7 +12609,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">9019 </t>
+          <t xml:space="preserve">9031 </t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>CASTRO BARROS AV. 338</t>
+          <t>YRIGOYEN, HIPOLITO 1938</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12632,11 +12632,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>814108068</t>
-        </is>
-      </c>
+      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
           <t>FIBERWORK</t>
@@ -12654,7 +12650,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -12666,10 +12662,10 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.419864</v>
+        <v>-58.394079</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.616375</v>
+        <v>-34.61051</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -12683,7 +12679,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12695,7 +12691,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9031 </t>
+          <t xml:space="preserve">9088 </t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12705,12 +12701,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO 1938</t>
+          <t>HUMAHUACA 4296</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -12718,7 +12714,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>814108086</t>
+        </is>
+      </c>
       <c r="G144" t="inlineStr">
         <is>
           <t>FIBERWORK</t>
@@ -12736,7 +12736,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -12748,10 +12748,10 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.394079</v>
+        <v>-58.425282</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.61051</v>
+        <v>-34.601504</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12777,7 +12777,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9088 </t>
+          <t xml:space="preserve">10059 </t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>HUMAHUACA 4296</t>
+          <t xml:space="preserve">SALGUERO, JERONIMO 2296 </t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12802,7 +12802,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>814108086</t>
+          <t>814111727</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -12834,14 +12834,14 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.425282</v>
+        <v>-58.411132</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.601504</v>
+        <v>-34.585267</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>AGU-K</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12863,17 +12863,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">10059 </t>
+          <t>-776</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>6/2/2026</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALGUERO, JERONIMO 2296 </t>
+          <t>ALSINA, ADOLFO 2457</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>814111727</t>
+          <t>814125554</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -12920,14 +12920,14 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.411132</v>
+        <v>-58.401052</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.585267</v>
+        <v>-34.612103</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>AGU-K</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12949,7 +12949,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>-776</t>
+          <t>-801</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12959,7 +12959,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ALSINA, ADOLFO 2457</t>
+          <t>YRIGOYEN, HIPOLITO 2754</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>814125554</t>
+          <t>814125643</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -13006,10 +13006,10 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.401052</v>
+        <v>-58.405116</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.612103</v>
+        <v>-34.611253</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>-801</t>
+          <t>-810</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13045,7 +13045,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO 2754</t>
+          <t>MEXICO 2183</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>814125643</t>
+          <t>814125664</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -13092,10 +13092,10 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.405116</v>
+        <v>-58.397489</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.611253</v>
+        <v>-34.616089</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13121,7 +13121,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>-810</t>
+          <t>-818</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>MEXICO 2183</t>
+          <t>PRINGLES 795</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>814125664</t>
+          <t>814125690</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base podrida</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -13178,10 +13178,10 @@
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.397489</v>
+        <v>-58.427096</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.616089</v>
+        <v>-34.602833</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13207,7 +13207,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>-818</t>
+          <t>-820</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13217,12 +13217,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>PRINGLES 795</t>
+          <t>RIOBAMBA 558</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>814125690</t>
+          <t>814125697</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -13242,7 +13242,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>base podrida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -13264,10 +13264,10 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.427096</v>
+        <v>-58.394106</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.602833</v>
+        <v>-34.602514</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -13281,19 +13281,19 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>RET-J</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>-820</t>
+          <t>-828</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>RIOBAMBA 558</t>
+          <t>TUCUMAN 2074</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -13318,7 +13318,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>814125697</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -13350,10 +13350,10 @@
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.394106</v>
+        <v>-58.396631</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.602514</v>
+        <v>-34.60222</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -13371,92 +13371,6 @@
         </is>
       </c>
       <c r="R151" t="inlineStr">
-        <is>
-          <t>ARATO-25058.PO.1RET</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>-828</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>6/2/2026</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>TUCUMAN 2074</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>FIBERWORK</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L152" t="n">
-        <v>1</v>
-      </c>
-      <c r="M152" t="n">
-        <v>-58.396631</v>
-      </c>
-      <c r="N152" t="n">
-        <v>-34.60222</v>
-      </c>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>Almagro</t>
-        </is>
-      </c>
-      <c r="P152" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>RET-J</t>
-        </is>
-      </c>
-      <c r="R152" t="inlineStr">
         <is>
           <t>ARATO-25058.PO.1RET</t>
         </is>

--- a/mapa_interactivo_Fiberwork.xlsx
+++ b/mapa_interactivo_Fiberwork.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R151"/>
+  <dimension ref="A1:R150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1195,17 +1195,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>804270064</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3/18/2025</t>
+          <t>3/21/2025</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TREINTA Y TRES ORIENTALES 965</t>
+          <t>Colombres 636</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>804161231</t>
+          <t>804270064</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1249,17 +1249,17 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-58.423042</v>
+        <v>-58.418089</v>
       </c>
       <c r="N10" t="n">
-        <v>-34.625868</v>
+        <v>-34.620313</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>ALM-B</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>804270064</t>
+          <t>804270068</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Colombres 636</t>
+          <t>Quito 4292</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>804270064</t>
+          <t>804270068</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1338,10 +1338,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-58.418089</v>
+        <v>-58.427201</v>
       </c>
       <c r="N11" t="n">
-        <v>-34.620313</v>
+        <v>-34.617131</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ALM-B</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>804270068</t>
+          <t>804270074</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Quito 4292</t>
+          <t>Maza 836</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>804270068</t>
+          <t>804270074</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1424,14 +1424,14 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-58.427201</v>
+        <v>-58.414984</v>
       </c>
       <c r="N12" t="n">
-        <v>-34.617131</v>
+        <v>-34.621386</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1453,17 +1453,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>804270074</t>
+          <t>S00431877</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3/21/2025</t>
+          <t>4/8/2025</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Maza 836</t>
+          <t>SARMIENTO 4290</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>804270074</t>
+          <t>804569065</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna corroída en su base entro tambien como caso 7049</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1507,17 +1507,17 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>-58.414984</v>
+        <v>-58.425764</v>
       </c>
       <c r="N13" t="n">
-        <v>-34.621386</v>
+        <v>-34.604359</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>ALM-L</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1539,32 +1539,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S00431877</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4/8/2025</t>
+          <t>4/23/2025</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SARMIENTO 4290</t>
+          <t>COCHABAMBA 2207</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>804569065</t>
+          <t>804903806</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Columna corroída en su base entro tambien como caso 7049</t>
+          <t>picada</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1593,17 +1593,17 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-58.425764</v>
+        <v>-58.396135</v>
       </c>
       <c r="N14" t="n">
-        <v>-34.604359</v>
+        <v>-34.624285</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>ALM-L</t>
+          <t>CON-C</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1625,17 +1625,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4/23/2025</t>
+          <t>4/29/2025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>COCHABAMBA 2207</t>
+          <t>República Bolivariana de Venezuela 2701</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>804903806</t>
+          <t>805507294</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>picada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1670,26 +1670,26 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>-58.396135</v>
+        <v>-58.404913</v>
       </c>
       <c r="N15" t="n">
-        <v>-34.624285</v>
+        <v>-34.615857</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>CON-C</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1711,17 +1711,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4/29/2025</t>
+          <t>5/1/2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>República Bolivariana de Venezuela 2701</t>
+          <t>RIOBAMBA 659</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>805507294</t>
+          <t>805579188</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Pendiente de traspaso nodo entro tambien como 7100</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1761,17 +1761,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L16" t="n">
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>-58.404913</v>
+        <v>-58.394118</v>
       </c>
       <c r="N16" t="n">
-        <v>-34.615857</v>
+        <v>-34.601416</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>RET-H</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1797,17 +1797,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5/1/2025</t>
+          <t>5/19/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RIOBAMBA 659</t>
+          <t>AYACUCHO 267</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>805579188</t>
+          <t>806926385</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pendiente de traspaso nodo entro tambien como 7100</t>
+          <t>Colocar columna y dar aviso para traspaso de nodo teco</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1854,10 +1854,10 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>-58.394118</v>
+        <v>-58.395063</v>
       </c>
       <c r="N17" t="n">
-        <v>-34.601416</v>
+        <v>-34.606257</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>RET-H</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1883,22 +1883,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5/19/2025</t>
+          <t>5/26/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AYACUCHO 267</t>
+          <t>COCHABAMBA 4090</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>806926385</t>
+          <t>806926861</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Colocar columna y dar aviso para traspaso de nodo teco</t>
+          <t>Columna base podrida colocar r400 para pedir traspaso de fuente</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1940,14 +1940,14 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>-58.395063</v>
+        <v>-58.422268</v>
       </c>
       <c r="N18" t="n">
-        <v>-34.606257</v>
+        <v>-34.627754</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1969,17 +1969,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>807187860</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5/26/2025</t>
+          <t>6/4/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>COCHABAMBA 4090</t>
+          <t>San Juan 3960</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>806926861</t>
+          <t>807187860</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Columna base podrida colocar r400 para pedir traspaso de fuente</t>
+          <t>Colocar columna contactar a Matias Tapia 1171744701 por si hay alguna duda o problema que surja en el momento ya que es para posterior tendido de ftth</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2026,10 +2026,10 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>-58.422268</v>
+        <v>-58.420909</v>
       </c>
       <c r="N19" t="n">
-        <v>-34.627754</v>
+        <v>-34.626221</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>PPT-R</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2055,17 +2055,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>807187860</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6/4/2025</t>
+          <t>6/5/2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Juan 3960</t>
+          <t>MAZA 181</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2075,12 +2075,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>807187860</t>
+          <t>807215439</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Colocar columna contactar a Matias Tapia 1171744701 por si hay alguna duda o problema que surja en el momento ya que es para posterior tendido de ftth</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2112,14 +2112,14 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>-58.420909</v>
+        <v>-58.416477</v>
       </c>
       <c r="N20" t="n">
-        <v>-34.626221</v>
+        <v>-34.61303</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>PPT-R</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2141,7 +2141,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MAZA 181</t>
+          <t>ESTADO DE PALESTINA 771</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>807215439</t>
+          <t>807215458</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada y mal ubicada ver con Pedro</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2198,10 +2198,10 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>-58.416477</v>
+        <v>-58.425478</v>
       </c>
       <c r="N21" t="n">
-        <v>-34.61303</v>
+        <v>-34.601865</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2227,22 +2227,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6/5/2025</t>
+          <t>6/9/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 771</t>
+          <t>ALBERTI 191</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>807215458</t>
+          <t>810533286</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Picada y mal ubicada ver con Pedro</t>
+          <t>Desmontar PRFV 400</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2284,10 +2284,10 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>-58.425478</v>
+        <v>-58.401624</v>
       </c>
       <c r="N22" t="n">
-        <v>-34.601865</v>
+        <v>-34.612001</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2313,17 +2313,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6/9/2025</t>
+          <t>6/24/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ALBERTI 191</t>
+          <t>MATHEU 727</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2333,12 +2333,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>810533286</t>
+          <t>ICD31456940</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2346,11 +2346,7 @@
           <t>FIBERWORK</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Desmontar PRFV 400</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -2358,7 +2354,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Nodo TLC</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2370,10 +2366,10 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-58.401624</v>
+        <v>-58.400169</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.612001</v>
+        <v>-34.617784</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2387,7 +2383,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>CEN-N</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2399,17 +2395,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6/24/2025</t>
+          <t>6/30/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MATHEU 727</t>
+          <t>CHILE 2561</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2424,7 +2420,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ICD31456940</t>
+          <t>807851584</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2440,7 +2436,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Nodo TLC</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2452,10 +2448,10 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.400169</v>
+        <v>-58.401827</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.617784</v>
+        <v>-34.617667</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2469,7 +2465,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>CEN-N</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2481,17 +2477,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>-510</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6/30/2025</t>
+          <t>7/14/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CHILE 2561</t>
+          <t>Larrea 590</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2501,12 +2497,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>807851584</t>
+          <t>808194254</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2514,7 +2510,11 @@
           <t>FIBERWORK</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Picada</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2534,10 +2534,10 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.401827</v>
+        <v>-58.402353</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.617667</v>
+        <v>-34.602205</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>CLI-E</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2563,7 +2563,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>-510</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Larrea 590</t>
+          <t>CASTELLI 304</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>808194254</t>
+          <t>808194260</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2620,10 +2620,10 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.402353</v>
+        <v>-58.404696</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.602205</v>
+        <v>-34.606337</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>CLI-E</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2649,17 +2649,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7/14/2025</t>
+          <t>7/15/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CASTELLI 304</t>
+          <t>TUCUMAN 3253</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>808194260</t>
+          <t>808373657</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2706,10 +2706,10 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.404696</v>
+        <v>-58.411609</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.606337</v>
+        <v>-34.600329</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CLI-F</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2735,17 +2735,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7/15/2025</t>
+          <t>7/29/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TUCUMAN 3253</t>
+          <t>CALLAO AV. 316</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>808373657</t>
+          <t>808579773</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2792,14 +2792,14 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.411609</v>
+        <v>-58.39231</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.600329</v>
+        <v>-34.605507</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>CLI-F</t>
+          <t>CEN-E</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2821,17 +2821,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7/29/2025</t>
+          <t>8/4/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CALLAO AV. 316</t>
+          <t>MITRE, BARTOLOME 2482</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>808579773</t>
+          <t>808703866</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2878,14 +2878,14 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.39231</v>
+        <v>-58.40161</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.605507</v>
+        <v>-34.608641</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>CEN-E</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2907,32 +2907,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>8/4/2025</t>
+          <t>8/12/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MITRE, BARTOLOME 2482</t>
+          <t>MARMOL, JOSE 228</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>808703866</t>
+          <t>808918687</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Se deriva directamente a traspaso de fuente ya que hay una columna existente</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2961,13 +2961,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.40161</v>
+        <v>-58.425858</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.608641</v>
+        <v>-34.61629</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2993,32 +2993,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8/12/2025</t>
+          <t>8/26/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MARMOL, JOSE 228</t>
+          <t>SARANDI 1011</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>808918687</t>
+          <t>809195660</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Se deriva directamente a traspaso de fuente ya que hay una columna existente</t>
+          <t>Picada entro tambien como caso 7209</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3047,17 +3047,17 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.425858</v>
+        <v>-58.394543</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.61629</v>
+        <v>-34.620732</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SARANDI 1011</t>
+          <t>PRINGLES 788</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>809195660</t>
+          <t>809195664</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Picada entro tambien como caso 7209</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3129,21 +3129,21 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L32" t="n">
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.394543</v>
+        <v>-58.427206</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.620732</v>
+        <v>-34.602914</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3165,17 +3165,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7050</t>
+          <t>-596</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8/26/2025</t>
+          <t>9/14/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PRINGLES 788</t>
+          <t>Humahuaca 3866</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>809195664</t>
+          <t>809732190</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3215,17 +3215,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L33" t="n">
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.427206</v>
+        <v>-58.418823</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.602914</v>
+        <v>-34.602148</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3251,22 +3251,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>-596</t>
+          <t>-597</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9/14/2025</t>
+          <t>9/16/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Humahuaca 3866</t>
+          <t>La Rioja 1261</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>809732190</t>
+          <t>809800215</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3308,14 +3308,14 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.418823</v>
+        <v>-58.407029</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.602148</v>
+        <v>-34.62526</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3337,17 +3337,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>-597</t>
+          <t>-603</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/22/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>La Rioja 1261</t>
+          <t>ANCHORENA, TOMAS MANUEL DE, DR. 821</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>809800215</t>
+          <t>809910086</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna chocada pendiente para instalar un corporativo</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3394,14 +3394,14 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.407029</v>
+        <v>-58.408551</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.62526</v>
+        <v>-34.599265</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>CLI-F</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3423,22 +3423,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>-603</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>9/22/2025</t>
+          <t>9/25/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ANCHORENA, TOMAS MANUEL DE, DR. 821</t>
+          <t>MARMOL, JOSE 588</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>809910086</t>
+          <t>809979740</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Columna chocada pendiente para instalar un corporativo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3480,10 +3480,10 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.408551</v>
+        <v>-58.425357</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.599265</v>
+        <v>-34.620223</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>CLI-F</t>
+          <t>ALM-B</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3509,22 +3509,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>-628</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>9/25/2025</t>
+          <t>10/1/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MARMOL, JOSE 588</t>
+          <t>Hipolito Yrigoyen 3250</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>809979740</t>
+          <t>810093628</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3566,10 +3566,10 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.425357</v>
+        <v>-58.412606</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.620223</v>
+        <v>-34.612353</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>ALM-B</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3595,17 +3595,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>-628</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10/1/2025</t>
+          <t>10/6/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hipolito Yrigoyen 3250</t>
+          <t>LARREA 320</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>810093628</t>
+          <t>810244454</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3652,10 +3652,10 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.412606</v>
+        <v>-58.402105</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.612353</v>
+        <v>-34.606071</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3681,7 +3681,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6404</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LARREA 320</t>
+          <t>RINCON 781</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>810244454</t>
+          <t>810244458</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3738,10 +3738,10 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.402105</v>
+        <v>-58.396055</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.606071</v>
+        <v>-34.618126</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3767,17 +3767,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7713</t>
+          <t>-633</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10/6/2025</t>
+          <t>10/8/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RINCON 781</t>
+          <t>Junin 74</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>810244458</t>
+          <t>ICD31464881</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R400</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3821,13 +3821,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.396055</v>
+        <v>-58.39641</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.618126</v>
+        <v>-34.608561</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>CLI-C</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3853,22 +3853,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>-633</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10/8/2025</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Junin 74</t>
+          <t>SAN JUAN AV. 4256</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ICD31464881</t>
+          <t>810394752</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Colocar R400</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3907,17 +3907,17 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.39641</v>
+        <v>-58.424867</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.608561</v>
+        <v>-34.626806</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>CLI-C</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3939,17 +3939,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>10/20/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 4256</t>
+          <t>CORRIENTES AV. 4515</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>810394752</t>
+          <t>810398934</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3996,14 +3996,14 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.424867</v>
+        <v>-58.428907</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.626806</v>
+        <v>-34.602301</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4025,17 +4025,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10/20/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CORRIENTES AV. 4515</t>
+          <t>SANCHEZ DE LORIA 1923</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>810398934</t>
+          <t>810416656</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>cambiar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4082,14 +4082,14 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.428907</v>
+        <v>-58.411426</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.602301</v>
+        <v>-34.633266</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4111,17 +4111,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1923</t>
+          <t>CALVO, CARLOS 3762</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>810416656</t>
+          <t>810451584</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4168,14 +4168,14 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.411426</v>
+        <v>-58.418542</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.633266</v>
+        <v>-34.624609</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4197,22 +4197,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3762</t>
+          <t>ALSINA, ADOLFO 2499</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>810451584</t>
+          <t>810487023</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4254,14 +4254,14 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.418542</v>
+        <v>-58.40129</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.624609</v>
+        <v>-34.612123</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ALSINA, ADOLFO 2499</t>
+          <t>LINIERS VIRREY 1142</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>810487023</t>
+          <t>810487035</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4340,14 +4340,14 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.40129</v>
+        <v>-58.413563</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.612123</v>
+        <v>-34.624645</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4369,17 +4369,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1142</t>
+          <t>SAN JUAN AV. 3741</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>810487035</t>
+          <t>810712796</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4426,10 +4426,10 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.413563</v>
+        <v>-58.418108</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.624645</v>
+        <v>-34.62564</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4455,22 +4455,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/17/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 3741</t>
+          <t>Paso 280</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>810712796</t>
+          <t>810787612</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>base picada</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4512,14 +4512,14 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.418108</v>
+        <v>-58.403566</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.62564</v>
+        <v>-34.606691</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4541,22 +4541,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>11/14/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Paso 280</t>
+          <t>DIAZ VELEZ AV. 3485</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>810787612</t>
+          <t>810787513</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>base picada</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4598,10 +4598,10 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.403566</v>
+        <v>-58.415838</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.606691</v>
+        <v>-34.608469</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CLI-J</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4627,17 +4627,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>S00110420</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11/14/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV. 3485</t>
+          <t>YATAY 760</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>810787513</t>
+          <t>810804303</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4684,10 +4684,10 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.415838</v>
+        <v>-58.428752</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.608469</v>
+        <v>-34.603273</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>CLI-J</t>
+          <t>ALM-M</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4713,17 +4713,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S00110420</t>
+          <t>S00921590</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>YATAY 760</t>
+          <t>CASEROS AV. 3621</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>810804303</t>
+          <t>810804462</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4770,14 +4770,14 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.428752</v>
+        <v>-58.416134</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.603273</v>
+        <v>-34.638879</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>ALM-M</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4799,7 +4799,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S00921590</t>
+          <t>S00921597</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CASEROS AV. 3621</t>
+          <t>CASEROS AV. 3507</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>810804462</t>
+          <t>810804451</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4856,10 +4856,10 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.416134</v>
+        <v>-58.414769</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.638879</v>
+        <v>-34.638638</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S00921597</t>
+          <t>S00921602</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CASEROS AV. 3507</t>
+          <t>CASEROS AV. 3411</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>810804451</t>
+          <t>810804383</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo TLC</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4942,10 +4942,10 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.414769</v>
+        <v>-58.413499</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.638638</v>
+        <v>-34.638416</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S00921602</t>
+          <t>S00942399</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CASEROS AV. 3411</t>
+          <t>ESTADOS UNIDOS 4030</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>810804383</t>
+          <t xml:space="preserve">01503983 </t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>base corroida Colocar PRFV 400</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Nodo TLC</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5028,14 +5028,14 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.413499</v>
+        <v>-58.422536</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.638416</v>
+        <v>-34.623094</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5057,7 +5057,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S00942399</t>
+          <t>01110546</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ESTADOS UNIDOS 4030</t>
+          <t>ALSINA, ADOLFO 2490</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">01503983 </t>
+          <t>810804369</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>base corroida Colocar PRFV 400</t>
+          <t>columna inclinada  base corroida</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5114,14 +5114,14 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.422536</v>
+        <v>-58.401266</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.623094</v>
+        <v>-34.612194</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5143,17 +5143,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>01110546</t>
+          <t>7874</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ALSINA, ADOLFO 2490</t>
+          <t>SAN LUIS 2488</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>810804369</t>
+          <t>810820592</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>columna inclinada  base corroida</t>
+          <t>base muy picada</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5200,10 +5200,10 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.401266</v>
+        <v>-58.402179</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.612194</v>
+        <v>-34.600152</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>CLI-E</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5229,17 +5229,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>-687</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SAN LUIS 2488</t>
+          <t>Junin 722</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>810820592</t>
+          <t>810862729</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>base muy picada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5286,10 +5286,10 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.402179</v>
+        <v>-58.397171</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.600152</v>
+        <v>-34.600729</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5303,34 +5303,34 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>CLI-E</t>
+          <t>RET-J</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>-687</t>
+          <t>900008882010</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Junin 722</t>
+          <t xml:space="preserve"> PAVON AV. 3707 </t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>810862729</t>
+          <t>810984598</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5372,14 +5372,14 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.397171</v>
+        <v>-58.416724</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.600729</v>
+        <v>-34.630181</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5389,29 +5389,29 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>RET-J</t>
+          <t>PPT-R</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>900008882010</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PAVON AV. 3707 </t>
+          <t>Querandíes 4220</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>810984598</t>
+          <t>810984700</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>correr, obstaculiza acceso a garage</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5451,21 +5451,21 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L59" t="n">
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.416724</v>
+        <v>-58.426168</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.630181</v>
+        <v>-34.611095</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>PPT-R</t>
+          <t>ALM-E</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5487,22 +5487,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Querandíes 4220</t>
+          <t xml:space="preserve">URQUIZA, GRAL. 779 </t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>810984700</t>
+          <t>811198737</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>correr, obstaculiza acceso a garage</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5537,17 +5537,17 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L60" t="n">
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.426168</v>
+        <v>-58.409318</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.611095</v>
+        <v>-34.619842</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>ALM-E</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5573,22 +5573,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>S01199412</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">URQUIZA, GRAL. 779 </t>
+          <t>ACUÑA DE FIGUEROA, FRANCISCO 1028</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>811198737</t>
+          <t>811198676</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5630,10 +5630,10 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.409318</v>
+        <v>-58.422033</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.619842</v>
+        <v>-34.598976</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>CLI-L</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5659,22 +5659,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S01199412</t>
+          <t>-705</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/22/2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ACUÑA DE FIGUEROA, FRANCISCO 1028</t>
+          <t>Larrea 370</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>811198676</t>
+          <t>02013924</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -5716,10 +5716,10 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.422033</v>
+        <v>-58.402154</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.598976</v>
+        <v>-34.605295</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>CLI-L</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5745,22 +5745,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>-705</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>12/22/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Larrea 370</t>
+          <t>BRAVO, MARIO 478</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>02013924</t>
+          <t>811299416</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -5802,10 +5802,10 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.402154</v>
+        <v>-58.416901</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.605295</v>
+        <v>-34.604236</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5831,17 +5831,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>-711</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BRAVO, MARIO 478</t>
+          <t>México 3306</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>811299416</t>
+          <t>811299443</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5888,10 +5888,10 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.416901</v>
+        <v>-58.412865</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.604236</v>
+        <v>-34.619484</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5917,17 +5917,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>-711</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>México 3306</t>
+          <t>LAMBARE 864</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>811299443</t>
+          <t>811453866</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5974,10 +5974,10 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.412865</v>
+        <v>-58.430579</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.619484</v>
+        <v>-34.604908</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>ALM-M</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6003,17 +6003,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>S00941232</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LAMBARE 864</t>
+          <t>TARIJA 3323</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>811453866</t>
+          <t>811453904</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6060,14 +6060,14 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.430579</v>
+        <v>-58.412204</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.604908</v>
+        <v>-34.628609</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>ALM-M</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6089,22 +6089,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S00941232</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TARIJA 3323</t>
+          <t>Catamarca 236</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>811453904</t>
+          <t xml:space="preserve">02511385 </t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6146,14 +6146,14 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.412204</v>
+        <v>-58.406807</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.628609</v>
+        <v>-34.612902</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6175,7 +6175,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>8124</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Catamarca 236</t>
+          <t xml:space="preserve"> DIAZ VELEZ AV. 4421</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">02511385 </t>
+          <t>811454440</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6232,10 +6232,10 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.406807</v>
+        <v>-58.429481</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.612902</v>
+        <v>-34.608647</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>ALM-K</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6261,22 +6261,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>S01432754</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/16/2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DIAZ VELEZ AV. 4421</t>
+          <t>MISIONES 242</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>811454440</t>
+          <t>811454538</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6318,10 +6318,10 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.429481</v>
+        <v>-58.404243</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.608647</v>
+        <v>-34.612859</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>ALM-K</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6347,7 +6347,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S01432754</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MISIONES 242</t>
+          <t>Castelli 60</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6367,12 +6367,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>811454538</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6382,32 +6382,20 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>corroida</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
+          <t>traspaso propio tlc coloco columna</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="n">
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.404243</v>
+        <v>-58.404691</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.612859</v>
+        <v>-34.609194</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -6421,7 +6409,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6433,17 +6421,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>S01408162</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1/16/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Castelli 60</t>
+          <t xml:space="preserve">GARAY, JUAN DE AV. 2871 </t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6453,12 +6441,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812439895</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6468,24 +6456,36 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>traspaso propio tlc coloco columna</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
       <c r="L71" t="n">
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.404691</v>
+        <v>-58.4048</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.609194</v>
+        <v>-34.629021</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6507,17 +6507,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S01408162</t>
+          <t>S00034481</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARAY, JUAN DE AV. 2871 </t>
+          <t xml:space="preserve">MITRE, BARTOLOME 2294 </t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>812439895</t>
+          <t>811626888</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6564,14 +6564,14 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.4048</v>
+        <v>-58.399059</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.629021</v>
+        <v>-34.608499</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>CLI-C</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6593,17 +6593,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S00034481</t>
+          <t>S01314715</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">MITRE, BARTOLOME 2294 </t>
+          <t xml:space="preserve"> CATAMARCA 919</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>811626888</t>
+          <t>811626986</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Corroida</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6650,14 +6650,14 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.399059</v>
+        <v>-58.404766</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.608499</v>
+        <v>-34.620521</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>CLI-C</t>
+          <t>CEN-K</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6679,7 +6679,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S01314715</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CATAMARCA 919</t>
+          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>811626986</t>
+          <t>811626981</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6736,14 +6736,14 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.404766</v>
+        <v>-58.423058</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.620521</v>
+        <v>-34.608916</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>CEN-K</t>
+          <t>ALM-E</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6765,22 +6765,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>8125</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
+          <t>COMBATE DE LOS POZOS 1103</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>811626981</t>
+          <t>811627014</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6822,14 +6822,14 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.423058</v>
+        <v>-58.393145</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.608916</v>
+        <v>-34.621778</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>ALM-E</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6851,17 +6851,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>S00022862</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>COMBATE DE LOS POZOS 1103</t>
+          <t>YRIGOYEN, HIPOLITO 2395</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>811627014</t>
+          <t>811627077</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6908,14 +6908,14 @@
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.393145</v>
+        <v>-58.400243</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.621778</v>
+        <v>-34.610864</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6937,7 +6937,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S00022862</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO 2395</t>
+          <t>PICHINCHA 89</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>811627077</t>
+          <t>811627062</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6994,10 +6994,10 @@
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.400243</v>
+        <v>-58.399124</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.610864</v>
+        <v>-34.610705</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -7023,22 +7023,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/6/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PICHINCHA 89</t>
+          <t>GALLO 77</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>811627062</t>
+          <t>811627128</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>tensor roto inclinada</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7073,17 +7073,17 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L78" t="n">
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.399124</v>
+        <v>-58.413979</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.610705</v>
+        <v>-34.607475</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7109,22 +7109,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>8296</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2/6/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GALLO 77</t>
+          <t>RINCON 1109</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>811627128</t>
+          <t>812439968</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>tensor roto inclinada</t>
+          <t>base quebrada</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7159,21 +7159,21 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L79" t="n">
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.413979</v>
+        <v>-58.395668</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.607475</v>
+        <v>-34.621926</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>CEN-N</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7195,17 +7195,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8329</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>RINCON 1109</t>
+          <t xml:space="preserve">ALBERTI 1055 </t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>812439968</t>
+          <t>812440156</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>base quebrada</t>
+          <t>base corroida inclinada</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7252,10 +7252,10 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.395668</v>
+        <v>-58.400774</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.621926</v>
+        <v>-34.621503</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -7281,17 +7281,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>S00136365</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/19/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALBERTI 1055 </t>
+          <t>PERON, JUAN DOMINGO, TTE. GENERAL 2697</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>812440156</t>
+          <t>812440173</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -7338,14 +7338,14 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.400774</v>
+        <v>-58.404576</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.621503</v>
+        <v>-34.607569</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>CEN-N</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7367,7 +7367,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S00136365</t>
+          <t>S00144805</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PERON, JUAN DOMINGO, TTE. GENERAL 2697</t>
+          <t>VIAMONTE 1990</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>812440173</t>
+          <t>812440165</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -7424,10 +7424,10 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.404576</v>
+        <v>-58.395384</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.607569</v>
+        <v>-34.600962</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -7441,29 +7441,29 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>RET-J</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S00144805</t>
+          <t>-749</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2/19/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>VIAMONTE 1990</t>
+          <t>Moreno 2965</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>812440165</t>
+          <t>812440614</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>base corroida inclinada</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7510,10 +7510,10 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.395384</v>
+        <v>-58.407758</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.600962</v>
+        <v>-34.613793</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -7527,19 +7527,19 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>RET-J</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>-749</t>
+          <t>-760</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Moreno 2965</t>
+          <t>MAZA 1615</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>812440614</t>
+          <t>812440354</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>base corroida e inclinada</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -7596,14 +7596,14 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.407758</v>
+        <v>-58.414586</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.613793</v>
+        <v>-34.630095</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -7625,7 +7625,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>-760</t>
+          <t>S00519068</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MAZA 1615</t>
+          <t>CALVO, CARLOS 3747</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>812440354</t>
+          <t>812440282</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>base corroida e inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7682,10 +7682,10 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.414586</v>
+        <v>-58.41859</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.630095</v>
+        <v>-34.624508</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -7711,17 +7711,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S00519068</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/27/2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3747</t>
+          <t xml:space="preserve">BRAVO, MARIO 836 </t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>812440282</t>
+          <t>812503638</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -7768,14 +7768,14 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.41859</v>
+        <v>-58.416187</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.624508</v>
+        <v>-34.600138</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CLI-G</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7797,17 +7797,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>S00100362</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2/27/2026</t>
+          <t>3/4/2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRAVO, MARIO 836 </t>
+          <t>RIO DE JANEIRO 901</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>812503638</t>
+          <t>814105603</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7854,10 +7854,10 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.416187</v>
+        <v>-58.431406</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.600138</v>
+        <v>-34.605009</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>CLI-G</t>
+          <t>ALM-M</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7883,17 +7883,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S00100362</t>
+          <t>-774</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>3/4/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO 901</t>
+          <t>CASEROS AV. 4131</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>814105603</t>
+          <t>814107131</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>mover a 4111</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7940,14 +7940,14 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.431406</v>
+        <v>-58.422741</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.605009</v>
+        <v>-34.639999</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>ALM-M</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7969,17 +7969,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>-774</t>
+          <t>00050599</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CASEROS AV. 4131</t>
+          <t xml:space="preserve">BELGRANO AV 3689 </t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>814107131</t>
+          <t>812879940</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>mover a 4111</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8026,14 +8026,14 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.422741</v>
+        <v>-58.418254</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.639999</v>
+        <v>-34.615692</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8055,7 +8055,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>00050599</t>
+          <t>00223191</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">BELGRANO AV 3689 </t>
+          <t>CATAMARCA 254</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>812879940</t>
+          <t>812879982</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -8112,10 +8112,10 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.418254</v>
+        <v>-58.406734</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.615692</v>
+        <v>-34.613107</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8141,7 +8141,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>00223191</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CATAMARCA 254</t>
+          <t>CORRIENTES AV 4073</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>812879982</t>
+          <t>812880406</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8198,10 +8198,10 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.406734</v>
+        <v>-58.422076</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.613107</v>
+        <v>-34.60298</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8227,7 +8227,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>00223023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8237,12 +8237,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CORRIENTES AV 4073</t>
+          <t>SAN JUAN AV. 2201</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>812880406</t>
+          <t>814109847</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -8284,14 +8284,14 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.422076</v>
+        <v>-58.396491</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.60298</v>
+        <v>-34.622986</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8313,22 +8313,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>00223023</t>
+          <t>00317296</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/23/2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 2201</t>
+          <t>AGRELO 3620</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>814109847</t>
+          <t>812880625</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -8370,14 +8370,14 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.396491</v>
+        <v>-58.417002</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.622986</v>
+        <v>-34.618613</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>ALM-B</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8399,7 +8399,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>00317296</t>
+          <t>00322642</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AGRELO 3620</t>
+          <t>ESTADO DE PALESTINA 727</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>812880625</t>
+          <t>812880655</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -8456,10 +8456,10 @@
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.417002</v>
+        <v>-58.425539</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.618613</v>
+        <v>-34.602286</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>ALM-B</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8485,7 +8485,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>00322642</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 727</t>
+          <t>MEXICO 3306</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>812880655</t>
+          <t>812880662</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -8542,10 +8542,10 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.425539</v>
+        <v>-58.412865</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.602286</v>
+        <v>-34.619484</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8571,22 +8571,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3/23/2026</t>
+          <t>3/28/2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MEXICO 3306</t>
+          <t>RIVADAVIA AV 1985</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>812880662</t>
+          <t>812880736</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -8606,17 +8606,17 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>APLOMAR COLUMNA</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -8628,10 +8628,10 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.412865</v>
+        <v>-58.394609</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.619484</v>
+        <v>-34.609304</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8657,22 +8657,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>M881</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>3/28/2026</t>
+          <t>4/1/2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>RIVADAVIA AV 1985</t>
+          <t>AV LA PLATA 2288</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>812880736</t>
+          <t>813046342</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -8692,17 +8692,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>APLOMAR COLUMNA</t>
+          <t>DESMONTAR COLUMNA Y  DESPLAZAR PCALOGERO</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -8714,14 +8714,14 @@
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.394609</v>
+        <v>-58.423203</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.609304</v>
+        <v>-34.640909</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8743,22 +8743,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>M881</t>
+          <t>8802</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>4/1/2026</t>
+          <t>4/11/2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AV LA PLATA 2288</t>
+          <t>RINCON 731</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>813046342</t>
+          <t>813046658</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>DESMONTAR COLUMNA Y  DESPLAZAR PCALOGERO</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -8800,14 +8800,14 @@
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.423203</v>
+        <v>-58.396088</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.640909</v>
+        <v>-34.617527</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8829,7 +8829,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>8802</t>
+          <t>S00374917</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>RINCON 731</t>
+          <t>24 DE NOVIEMBRE 695</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>813046658</t>
+          <t>813046791</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -8886,10 +8886,10 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.396088</v>
+        <v>-58.411053</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.617527</v>
+        <v>-34.618979</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8915,7 +8915,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S00374917</t>
+          <t>S00379764</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>24 DE NOVIEMBRE 695</t>
+          <t>JAURES JEAN 491</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>813046791</t>
+          <t>813046795</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -8972,10 +8972,10 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.411053</v>
+        <v>-58.408934</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.618979</v>
+        <v>-34.604273</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>CLI-H</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9001,7 +9001,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S00379764</t>
+          <t>S00379996</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>JAURES JEAN 491</t>
+          <t>SARANDI 1439</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>813046795</t>
+          <t>813046806</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -9058,14 +9058,14 @@
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.408934</v>
+        <v>-58.393455</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.604273</v>
+        <v>-34.625779</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>CLI-H</t>
+          <t>CON-C</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9087,7 +9087,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S00379996</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SARANDI 1439</t>
+          <t>SARMIENTO 2108</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>813046806</t>
+          <t>813046819</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -9144,14 +9144,14 @@
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.393455</v>
+        <v>-58.39675</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.625779</v>
+        <v>-34.605996</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>CON-C</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9173,7 +9173,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SARMIENTO 2108</t>
+          <t>SANCHEZ DE BUSTAMANTE 633</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>813046819</t>
+          <t>813046866</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -9230,10 +9230,10 @@
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.39675</v>
+        <v>-58.414203</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.605996</v>
+        <v>-34.602602</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>CLI-G</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9259,7 +9259,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SANCHEZ DE BUSTAMANTE 633</t>
+          <t>RIVADAVIA AV 4245</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>813046866</t>
+          <t>813046970</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -9316,10 +9316,10 @@
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.414203</v>
+        <v>-58.425567</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.602602</v>
+        <v>-34.613382</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>CLI-G</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9345,7 +9345,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>RIVADAVIA AV 4245</t>
+          <t>DIAZ VELEZ AV 4449</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>813046970</t>
+          <t>813046971</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -9402,10 +9402,10 @@
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.425567</v>
+        <v>-58.429714</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.613382</v>
+        <v>-34.608645</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>ALM-K</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9431,7 +9431,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV 4449</t>
+          <t>LAS CASAS 3989</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>813046971</t>
+          <t>813046994</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -9488,14 +9488,14 @@
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.429714</v>
+        <v>-58.421676</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.608645</v>
+        <v>-34.635878</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>ALM-K</t>
+          <t>PPT-R</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9517,7 +9517,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>8851</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LAS CASAS 3989</t>
+          <t>SALCEDO 3541</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>813046994</t>
+          <t>813047007</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -9574,10 +9574,10 @@
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.421676</v>
+        <v>-58.415121</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.635878</v>
+        <v>-34.633772</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>PPT-R</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -9603,7 +9603,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>8852</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SALCEDO 3541</t>
+          <t>TARIJA 4079</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>813047007</t>
+          <t>813047012</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -9660,10 +9660,10 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.415121</v>
+        <v>-58.421804</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.633772</v>
+        <v>-34.629558</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>PPT-R</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9689,7 +9689,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>8853</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>TARIJA 4079</t>
+          <t>TIMBUES 2086</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>813047012</t>
+          <t>813047017</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -9746,10 +9746,10 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.421804</v>
+        <v>-58.421835</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.629558</v>
+        <v>-34.63863</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>PPT-R</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9775,7 +9775,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>8855</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TIMBUES 2086</t>
+          <t>GOMEZ VALENTIN 3684</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>813047017</t>
+          <t>813047019</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -9832,14 +9832,14 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.421835</v>
+        <v>-58.416726</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.63863</v>
+        <v>-34.604773</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>CLI-K</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9861,7 +9861,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>S00390896</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>GOMEZ VALENTIN 3684</t>
+          <t>AV INDEPENDENCIA 2018</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>813047019</t>
+          <t>813047657</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -9918,10 +9918,10 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.416726</v>
+        <v>-58.39469</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.604773</v>
+        <v>-34.618394</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>CLI-K</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9947,22 +9947,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S00390896</t>
+          <t>RB00001</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>4/20/2026</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AV INDEPENDENCIA 2018</t>
+          <t>BELGRANO AV. 3715</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>813047657</t>
+          <t>813304903</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -10004,10 +10004,10 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.39469</v>
+        <v>-58.418851</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.618394</v>
+        <v>-34.615716</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10033,7 +10033,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>RB00001</t>
+          <t>AM00039</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BELGRANO AV. 3715</t>
+          <t>CASTRO BARROS 852</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>813304903</t>
+          <t>813304915</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -10090,14 +10090,14 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.418851</v>
+        <v>-58.419281</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.615716</v>
+        <v>-34.62215</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10119,7 +10119,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AM00039</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CASTRO BARROS 852</t>
+          <t>ALSINA, ADOLFO 3293</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10144,7 +10144,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>813304915</t>
+          <t>813350607</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -10176,14 +10176,14 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>-58.419281</v>
+        <v>-58.412936</v>
       </c>
       <c r="N114" t="n">
-        <v>-34.62215</v>
+        <v>-34.613332</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CEN-I</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10205,7 +10205,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>S00423738</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ALSINA, ADOLFO 3293</t>
+          <t>CATAMARCA 568</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>813350607</t>
+          <t>813350620</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -10262,10 +10262,10 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-58.412936</v>
+        <v>-58.405541</v>
       </c>
       <c r="N115" t="n">
-        <v>-34.613332</v>
+        <v>-34.616959</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>CEN-I</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10291,22 +10291,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S00423738</t>
+          <t>S00299569</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>4/20/2026</t>
+          <t>4/21/2026</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CATAMARCA 568</t>
+          <t>YRIGOYEN, HIPOLITO AV. 4156</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>813350620</t>
+          <t>813350953</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -10348,10 +10348,10 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>-58.405541</v>
+        <v>-58.425213</v>
       </c>
       <c r="N116" t="n">
-        <v>-34.616959</v>
+        <v>-34.614924</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10377,7 +10377,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S00299569</t>
+          <t>S004318770</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO AV. 4156</t>
+          <t>SARMIENTO 4290</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>813350953</t>
+          <t>813351576</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -10434,10 +10434,10 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>-58.425213</v>
+        <v>-58.425764</v>
       </c>
       <c r="N117" t="n">
-        <v>-34.614924</v>
+        <v>-34.604359</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>ALM-L</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10463,7 +10463,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S004318770</t>
+          <t>S00431893</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SARMIENTO 4290</t>
+          <t>MUÑIZ 1151</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>813351576</t>
+          <t>814105853</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -10520,14 +10520,14 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-58.425764</v>
+        <v>-58.425442</v>
       </c>
       <c r="N118" t="n">
-        <v>-34.604359</v>
+        <v>-34.627634</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>ALM-L</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10549,7 +10549,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S00431893</t>
+          <t>S00434849</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MUÑIZ 1151</t>
+          <t>YRIGOYEN, HIPOLITO AV. 3484</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>814105853</t>
+          <t>813352212</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -10606,14 +10606,14 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>-58.425442</v>
+        <v>-58.416028</v>
       </c>
       <c r="N119" t="n">
-        <v>-34.627634</v>
+        <v>-34.613538</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10635,7 +10635,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S00434849</t>
+          <t xml:space="preserve">9009 </t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO AV. 3484</t>
+          <t>SANCHEZ DE LORIA 1913</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>813352212</t>
+          <t>813352473</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -10692,14 +10692,14 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>-58.416028</v>
+        <v>-58.411474</v>
       </c>
       <c r="N120" t="n">
-        <v>-34.613538</v>
+        <v>-34.633143</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10721,7 +10721,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9009 </t>
+          <t xml:space="preserve">9011 </t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1913</t>
+          <t>SANCHEZ DE LORIA 1583</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>813352473</t>
+          <t>813352481</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -10778,14 +10778,14 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>-58.411474</v>
+        <v>-58.411926</v>
       </c>
       <c r="N121" t="n">
-        <v>-34.633143</v>
+        <v>-34.628861</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -10795,7 +10795,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10807,7 +10807,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">9011 </t>
+          <t xml:space="preserve">9012 </t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1583</t>
+          <t xml:space="preserve">LINIERS VIRREY 2315 </t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>813352481</t>
+          <t>813352482</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -10864,14 +10864,14 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>-58.411926</v>
+        <v>-58.41191</v>
       </c>
       <c r="N122" t="n">
-        <v>-34.628861</v>
+        <v>-34.637333</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -10893,7 +10893,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9012 </t>
+          <t xml:space="preserve">9014 </t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINIERS VIRREY 2315 </t>
+          <t>LINIERS VIRREY 896</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>813352482</t>
+          <t>813352486</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -10950,14 +10950,14 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-58.41191</v>
+        <v>-58.413645</v>
       </c>
       <c r="N123" t="n">
-        <v>-34.637333</v>
+        <v>-34.621935</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -10979,7 +10979,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9014 </t>
+          <t xml:space="preserve">9016 </t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 896</t>
+          <t>HUMBERTO 1° 3368</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>813352486</t>
+          <t>813352494</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -11036,10 +11036,10 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>-58.413645</v>
+        <v>-58.413189</v>
       </c>
       <c r="N124" t="n">
-        <v>-34.621935</v>
+        <v>-34.624187</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9016 </t>
+          <t xml:space="preserve">9017 </t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>HUMBERTO 1° 3368</t>
+          <t>MUÑIZ 1237</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>813352494</t>
+          <t>814105864</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -11122,10 +11122,10 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>-58.413189</v>
+        <v>-58.425206</v>
       </c>
       <c r="N125" t="n">
-        <v>-34.624187</v>
+        <v>-34.628705</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>PPT-P</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11151,7 +11151,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9017 </t>
+          <t xml:space="preserve">9020 </t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MUÑIZ 1237</t>
+          <t>TARIJA 3497</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>814105864</t>
+          <t>813352497</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -11208,10 +11208,10 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>-58.425206</v>
+        <v>-58.414424</v>
       </c>
       <c r="N126" t="n">
-        <v>-34.628705</v>
+        <v>-34.628778</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>PPT-P</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11237,17 +11237,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9020 </t>
+          <t>9028</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>4/21/2026</t>
+          <t>4/24/2026</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>TARIJA 3497</t>
+          <t>BRAVO, MARIO 740</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>813352497</t>
+          <t>813352774</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -11294,14 +11294,14 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-58.414424</v>
+        <v>-58.416308</v>
       </c>
       <c r="N127" t="n">
-        <v>-34.628778</v>
+        <v>-34.601047</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>CLI-G</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11323,7 +11323,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t>S00413025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11333,12 +11333,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BRAVO, MARIO 740</t>
+          <t>CHILE 2550</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>813352774</t>
+          <t>813352855</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -11380,10 +11380,10 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.416308</v>
+        <v>-58.40174</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.601047</v>
+        <v>-34.617754</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>CLI-G</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -11409,7 +11409,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S00413025</t>
+          <t>S00429731</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CHILE 2550</t>
+          <t xml:space="preserve">ALSINA, ADOLFO 2291 </t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>813352855</t>
+          <t>813352873</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -11466,10 +11466,10 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>-58.40174</v>
+        <v>-58.398771</v>
       </c>
       <c r="N129" t="n">
-        <v>-34.617754</v>
+        <v>-34.611932</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -11495,22 +11495,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S00429731</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/29/2026</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALSINA, ADOLFO 2291 </t>
+          <t xml:space="preserve">GALLEGOS 3443 </t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>813352873</t>
+          <t>813353299</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -11552,14 +11552,14 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.398771</v>
+        <v>-58.413647</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.611932</v>
+        <v>-34.631434</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>PPT-E</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11581,17 +11581,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t xml:space="preserve">9045 </t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>4/29/2026</t>
+          <t>4/30/2026</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALLEGOS 3443 </t>
+          <t>LINIERS VIRREY 1793</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>813353299</t>
+          <t>813631423</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -11638,14 +11638,14 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.413647</v>
+        <v>-58.413025</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.631434</v>
+        <v>-34.631929</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>PPT-E</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11667,7 +11667,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">9045 </t>
+          <t>9049</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1793</t>
+          <t>BATHURST 3377</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>813631423</t>
+          <t>813631424</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -11724,10 +11724,10 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.413025</v>
+        <v>-58.411896</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.631929</v>
+        <v>-34.636028</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -11753,22 +11753,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>S00215089</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>4/30/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>BATHURST 3377</t>
+          <t>LARREA 122</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>813631424</t>
+          <t>813631550</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -11810,14 +11810,14 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.411896</v>
+        <v>-58.401972</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.636028</v>
+        <v>-34.608317</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11839,7 +11839,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S00215089</t>
+          <t>S00401648</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>LARREA 122</t>
+          <t>JUNIN 312</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>813631550</t>
+          <t>813632251</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -11896,10 +11896,10 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.401972</v>
+        <v>-58.396676</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.608317</v>
+        <v>-34.605753</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -11925,7 +11925,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S00401648</t>
+          <t>S00465940</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>JUNIN 312</t>
+          <t>BELGRANO AV. 3669</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -11950,7 +11950,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>813632251</t>
+          <t>813632257</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -11970,7 +11970,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -11982,10 +11982,10 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.396676</v>
+        <v>-58.417949</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.605753</v>
+        <v>-34.615674</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -12011,7 +12011,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S00465940</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12021,12 +12021,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>BELGRANO AV. 3669</t>
+          <t>JAURES, JEAN 309</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>813632257</t>
+          <t>813632439</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -12068,10 +12068,10 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.417949</v>
+        <v>-58.409868</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.615674</v>
+        <v>-34.606562</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>CLI-H</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12097,22 +12097,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>S00364775</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>5/13/2026</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>JAURES, JEAN 309</t>
+          <t>CASTRO 511</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12120,11 +12120,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>813632439</t>
-        </is>
-      </c>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
           <t>FIBERWORK</t>
@@ -12132,12 +12128,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>NORMALIZAR RIENDA A PIQUE</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Tensor</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -12147,17 +12143,17 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.409868</v>
+        <v>-58.420597</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.606562</v>
+        <v>-34.617818</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -12171,7 +12167,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>CLI-H</t>
+          <t>ALM-B</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12183,7 +12179,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S00364775</t>
+          <t>S00493114</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12193,12 +12189,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CASTRO 511</t>
+          <t>ARENALES 3648</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12206,7 +12202,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>813352547</t>
+        </is>
+      </c>
       <c r="G138" t="inlineStr">
         <is>
           <t>FIBERWORK</t>
@@ -12214,36 +12214,36 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>NORMALIZAR RIENDA A PIQUE</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Tensor</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L138" t="n">
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.420597</v>
+        <v>-58.413656</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.617818</v>
+        <v>-34.585464</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>ALM-B</t>
+          <t>AGU-L</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12265,7 +12265,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S00493114</t>
+          <t xml:space="preserve">7880 </t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ARENALES 3648</t>
+          <t>MUÑIZ 16</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>813352547</t>
+          <t>814109709</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -12310,7 +12310,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -12322,14 +12322,14 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.413656</v>
+        <v>-58.427498</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.585464</v>
+        <v>-34.614599</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>AGU-L</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12351,7 +12351,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">7880 </t>
+          <t xml:space="preserve">9923 </t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MUÑIZ 16</t>
+          <t>PRINGLES 1094</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>814109709</t>
+          <t>814109753</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -12408,10 +12408,10 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.427498</v>
+        <v>-58.426722</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.614599</v>
+        <v>-34.599427</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12437,17 +12437,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">9923 </t>
+          <t xml:space="preserve">9019 </t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5/13/2026</t>
+          <t>5/14/2026</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PRINGLES 1094</t>
+          <t>CASTRO BARROS AV. 338</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>814109753</t>
+          <t>814108068</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -12494,10 +12494,10 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.426722</v>
+        <v>-58.419864</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.599427</v>
+        <v>-34.616375</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12523,7 +12523,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9019 </t>
+          <t xml:space="preserve">9031 </t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CASTRO BARROS AV. 338</t>
+          <t>YRIGOYEN, HIPOLITO 1938</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12546,11 +12546,7 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>814108068</t>
-        </is>
-      </c>
+      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
           <t>FIBERWORK</t>
@@ -12568,7 +12564,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -12580,10 +12576,10 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.419864</v>
+        <v>-58.394079</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.616375</v>
+        <v>-34.61051</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -12597,7 +12593,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12609,7 +12605,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">9031 </t>
+          <t xml:space="preserve">9088 </t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12619,12 +12615,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO 1938</t>
+          <t>HUMAHUACA 4296</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12632,7 +12628,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>814108086</t>
+        </is>
+      </c>
       <c r="G143" t="inlineStr">
         <is>
           <t>FIBERWORK</t>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -12662,10 +12662,10 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.394079</v>
+        <v>-58.425282</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.61051</v>
+        <v>-34.601504</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12691,7 +12691,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9088 </t>
+          <t xml:space="preserve">10059 </t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12701,12 +12701,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>HUMAHUACA 4296</t>
+          <t xml:space="preserve">SALGUERO, JERONIMO 2296 </t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>814108086</t>
+          <t>814111727</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -12748,14 +12748,14 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.425282</v>
+        <v>-58.411132</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.601504</v>
+        <v>-34.585267</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>AGU-K</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12777,17 +12777,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">10059 </t>
+          <t>-776</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5/14/2026</t>
+          <t>6/2/2026</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALGUERO, JERONIMO 2296 </t>
+          <t>ALSINA, ADOLFO 2457</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -12802,7 +12802,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>814111727</t>
+          <t>814125554</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -12834,14 +12834,14 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.411132</v>
+        <v>-58.401052</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.585267</v>
+        <v>-34.612103</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>AGU-K</t>
+          <t>CEN-H</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12863,7 +12863,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>-776</t>
+          <t>-801</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ALSINA, ADOLFO 2457</t>
+          <t>YRIGOYEN, HIPOLITO 2754</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>814125554</t>
+          <t>814125643</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -12920,10 +12920,10 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.401052</v>
+        <v>-58.405116</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.612103</v>
+        <v>-34.611253</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>-801</t>
+          <t>-810</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12959,7 +12959,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>YRIGOYEN, HIPOLITO 2754</t>
+          <t>MEXICO 2183</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>814125643</t>
+          <t>814125664</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -13006,10 +13006,10 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.405116</v>
+        <v>-58.397489</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.611253</v>
+        <v>-34.616089</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>CEN-H</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -13035,7 +13035,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>-810</t>
+          <t>-818</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13045,12 +13045,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>MEXICO 2183</t>
+          <t>PRINGLES 795</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>814125664</t>
+          <t>814125690</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base podrida</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -13092,10 +13092,10 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.397489</v>
+        <v>-58.427096</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.616089</v>
+        <v>-34.602833</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>CLI-M</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13121,7 +13121,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>-818</t>
+          <t>-820</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>PRINGLES 795</t>
+          <t>RIOBAMBA 558</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>814125690</t>
+          <t>814125697</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>base podrida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -13178,10 +13178,10 @@
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.427096</v>
+        <v>-58.394106</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.602833</v>
+        <v>-34.602514</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -13195,19 +13195,19 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>CLI-M</t>
+          <t>RET-J</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>-820</t>
+          <t>-828</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13217,7 +13217,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>RIOBAMBA 558</t>
+          <t>TUCUMAN 2074</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>814125697</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -13264,10 +13264,10 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.394106</v>
+        <v>-58.396631</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.602514</v>
+        <v>-34.60222</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -13285,92 +13285,6 @@
         </is>
       </c>
       <c r="R150" t="inlineStr">
-        <is>
-          <t>ARATO-25058.PO.1RET</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>-828</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>6/2/2026</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>TUCUMAN 2074</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>FIBERWORK</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L151" t="n">
-        <v>1</v>
-      </c>
-      <c r="M151" t="n">
-        <v>-58.396631</v>
-      </c>
-      <c r="N151" t="n">
-        <v>-34.60222</v>
-      </c>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>Almagro</t>
-        </is>
-      </c>
-      <c r="P151" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>RET-J</t>
-        </is>
-      </c>
-      <c r="R151" t="inlineStr">
         <is>
           <t>ARATO-25058.PO.1RET</t>
         </is>
